--- a/4기차세대경영자과정/차경 4기 정산서.xlsx
+++ b/4기차세대경영자과정/차경 4기 정산서.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Innobiz\Documents\innobiz-nextgen\4기차세대경영자과정\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAAFE48E-CDD8-4AEA-B3E0-ED799051C1F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A69BE70-B38A-4DE1-984C-41D63BDDCB4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{404CE508-8F71-4CA4-99F0-0EFB79DB1227}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{404CE508-8F71-4CA4-99F0-0EFB79DB1227}"/>
   </bookViews>
   <sheets>
     <sheet name="항목별(피벗)" sheetId="9" r:id="rId1"/>
@@ -1517,7 +1517,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="297">
   <si>
     <t>번호</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -2559,6 +2559,36 @@
   <si>
     <t>삼성웰스토리 이노밸리카페</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>강사비(김창원)</t>
+  </si>
+  <si>
+    <t>강의비</t>
+  </si>
+  <si>
+    <t>김창원</t>
+  </si>
+  <si>
+    <t>진행비(김창원)</t>
+  </si>
+  <si>
+    <t>진행비</t>
+  </si>
+  <si>
+    <t>식비(소호면가)</t>
+  </si>
+  <si>
+    <t>식비</t>
+  </si>
+  <si>
+    <t>소호면가 분당점</t>
+  </si>
+  <si>
+    <t>다과비</t>
+  </si>
+  <si>
+    <t>세븐일레븐 판교이노밸리점</t>
   </si>
 </sst>
 </file>
@@ -3080,13 +3110,13 @@
     <xf numFmtId="14" fontId="19" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3874,11 +3904,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="26.25">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="76" t="s">
         <v>105</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
     </row>
     <row r="2" spans="1:4" ht="21.6" customHeight="1">
       <c r="A2" s="3" t="s">
@@ -4298,15 +4328,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="26.25">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="76" t="s">
         <v>241</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
     </row>
     <row r="2" spans="1:7" ht="11.25" customHeight="1">
       <c r="A2" s="52"/>
@@ -4839,12 +4869,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="26.25">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="76" t="s">
         <v>105</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
     </row>
     <row r="3" spans="1:5" s="24" customFormat="1" ht="40.5" customHeight="1">
       <c r="A3" s="4" t="s">
@@ -5065,7 +5095,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{959FEF70-8578-4918-8CDC-E1B4AA8967DB}">
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="7.125" customWidth="1"/>
@@ -5078,15 +5108,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="26.25">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="76" t="s">
         <v>105</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
     </row>
     <row r="2" spans="1:7">
       <c r="F2" s="2"/>
@@ -5708,7 +5738,7 @@
       <c r="B29" s="74">
         <v>14266000</v>
       </c>
-      <c r="C29" s="77">
+      <c r="C29" s="75">
         <v>46175</v>
       </c>
       <c r="D29" s="3" t="s">
@@ -5883,6 +5913,98 @@
       </c>
       <c r="G36" s="2" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37">
+        <v>34</v>
+      </c>
+      <c r="B37" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="C37" s="35">
+        <v>46191</v>
+      </c>
+      <c r="D37" s="34" t="s">
+        <v>287</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="F37" s="34" t="s">
+        <v>289</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38">
+        <v>35</v>
+      </c>
+      <c r="B38" s="1">
+        <v>500000</v>
+      </c>
+      <c r="C38" s="35">
+        <v>46191</v>
+      </c>
+      <c r="D38" s="34" t="s">
+        <v>290</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="F38" s="34" t="s">
+        <v>289</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39">
+        <v>36</v>
+      </c>
+      <c r="B39" s="1">
+        <v>395000</v>
+      </c>
+      <c r="C39" s="35">
+        <v>46191</v>
+      </c>
+      <c r="D39" s="34" t="s">
+        <v>292</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="F39" s="34" t="s">
+        <v>294</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40">
+        <v>37</v>
+      </c>
+      <c r="B40" s="1">
+        <v>78100</v>
+      </c>
+      <c r="C40" s="35">
+        <v>46191</v>
+      </c>
+      <c r="D40" s="34" t="s">
+        <v>295</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="F40" s="34" t="s">
+        <v>296</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/4기차세대경영자과정/차경 4기 정산서.xlsx
+++ b/4기차세대경영자과정/차경 4기 정산서.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Innobiz\Documents\innobiz-nextgen\4기차세대경영자과정\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A69BE70-B38A-4DE1-984C-41D63BDDCB4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DA5450F-05A7-49C0-9A29-6461604080D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{404CE508-8F71-4CA4-99F0-0EFB79DB1227}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{404CE508-8F71-4CA4-99F0-0EFB79DB1227}"/>
   </bookViews>
   <sheets>
     <sheet name="항목별(피벗)" sheetId="9" r:id="rId1"/>
@@ -23,7 +23,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">실수입내역!$A$3:$C$46</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">지출세부내역서!$A$3:$G$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'회차별 출석현황'!$A$1:$L$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'회차별 출석현황'!$A$1:$O$31</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1517,7 +1517,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="292">
   <si>
     <t>번호</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -2493,10 +2493,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>강의비</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>SCG</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2509,14 +2505,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>진행비(유일한) *세금계산서 처리</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>진행비</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>주식회사 스마트에이엘</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2525,10 +2513,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>식비</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>스시가오</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2545,50 +2529,52 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>다과비</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>세븐일레븐 판교이노밸리점</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>다과비(음료)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>삼성웰스토리 이노밸리카페</t>
+    <t>5주차</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>6주차</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>강사비(김창원)</t>
-  </si>
-  <si>
-    <t>강의비</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>김창원</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>7주차</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>진행비(김창원)</t>
-  </si>
-  <si>
-    <t>진행비</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>식비(소호면가)</t>
-  </si>
-  <si>
-    <t>식비</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>소호면가 분당점</t>
-  </si>
-  <si>
-    <t>다과비</t>
-  </si>
-  <si>
-    <t>세븐일레븐 판교이노밸리점</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>5주(2026-06-03~06, 해외연수)</t>
+  </si>
+  <si>
+    <t>6주(2026-06-11)</t>
+  </si>
+  <si>
+    <t>7주(2026-06-18)</t>
+  </si>
+  <si>
+    <t>참가</t>
   </si>
 </sst>
 </file>
@@ -2888,7 +2874,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3000,9 +2986,6 @@
     <xf numFmtId="14" fontId="10" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -3099,18 +3082,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="42" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="19" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3904,11 +3875,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="26.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="71" t="s">
         <v>105</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
     </row>
     <row r="2" spans="1:4" ht="21.6" customHeight="1">
       <c r="A2" s="3" t="s">
@@ -4328,30 +4299,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="26.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="71" t="s">
         <v>241</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
     </row>
     <row r="2" spans="1:7" ht="11.25" customHeight="1">
-      <c r="A2" s="52"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
+      <c r="A2" s="51"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
     </row>
     <row r="3" spans="1:7" ht="19.5">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="53" t="s">
+      <c r="B3" s="52" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="3" t="s">
@@ -4359,10 +4330,10 @@
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="57">
+      <c r="A4" s="56">
         <v>2800000</v>
       </c>
-      <c r="B4" s="54" t="s">
+      <c r="B4" s="53" t="s">
         <v>161</v>
       </c>
       <c r="C4" t="s">
@@ -4370,10 +4341,10 @@
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="57">
+      <c r="A5" s="56">
         <v>2800000</v>
       </c>
-      <c r="B5" s="54" t="s">
+      <c r="B5" s="53" t="s">
         <v>163</v>
       </c>
       <c r="C5" t="s">
@@ -4381,10 +4352,10 @@
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="57">
+      <c r="A6" s="56">
         <v>2800000</v>
       </c>
-      <c r="B6" s="54" t="s">
+      <c r="B6" s="53" t="s">
         <v>165</v>
       </c>
       <c r="C6" t="s">
@@ -4392,10 +4363,10 @@
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="57">
+      <c r="A7" s="56">
         <v>2800000</v>
       </c>
-      <c r="B7" s="54" t="s">
+      <c r="B7" s="53" t="s">
         <v>168</v>
       </c>
       <c r="C7" t="s">
@@ -4403,10 +4374,10 @@
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="57">
+      <c r="A8" s="56">
         <v>2800000</v>
       </c>
-      <c r="B8" s="54" t="s">
+      <c r="B8" s="53" t="s">
         <v>171</v>
       </c>
       <c r="C8" t="s">
@@ -4414,10 +4385,10 @@
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="61">
+      <c r="A9" s="60">
         <v>2800000</v>
       </c>
-      <c r="B9" s="55" t="s">
+      <c r="B9" s="54" t="s">
         <v>175</v>
       </c>
       <c r="C9" t="s">
@@ -4425,10 +4396,10 @@
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="61">
+      <c r="A10" s="60">
         <v>2800000</v>
       </c>
-      <c r="B10" s="55" t="s">
+      <c r="B10" s="54" t="s">
         <v>243</v>
       </c>
       <c r="C10" t="s">
@@ -4436,10 +4407,10 @@
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="62">
+      <c r="A11" s="61">
         <v>2800000</v>
       </c>
-      <c r="B11" s="56" t="s">
+      <c r="B11" s="55" t="s">
         <v>244</v>
       </c>
       <c r="C11" t="s">
@@ -4447,10 +4418,10 @@
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="57">
+      <c r="A12" s="56">
         <v>2800000</v>
       </c>
-      <c r="B12" s="54" t="s">
+      <c r="B12" s="53" t="s">
         <v>180</v>
       </c>
       <c r="C12" t="s">
@@ -4458,10 +4429,10 @@
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="57">
+      <c r="A13" s="56">
         <v>3500000</v>
       </c>
-      <c r="B13" s="54" t="s">
+      <c r="B13" s="53" t="s">
         <v>183</v>
       </c>
       <c r="C13" t="s">
@@ -4469,10 +4440,10 @@
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="57">
+      <c r="A14" s="56">
         <v>2800000</v>
       </c>
-      <c r="B14" s="54" t="s">
+      <c r="B14" s="53" t="s">
         <v>186</v>
       </c>
       <c r="C14" t="s">
@@ -4480,10 +4451,10 @@
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="57">
+      <c r="A15" s="56">
         <v>2800000</v>
       </c>
-      <c r="B15" s="54" t="s">
+      <c r="B15" s="53" t="s">
         <v>188</v>
       </c>
       <c r="C15" t="s">
@@ -4491,10 +4462,10 @@
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="57">
+      <c r="A16" s="56">
         <v>3500000</v>
       </c>
-      <c r="B16" s="54" t="s">
+      <c r="B16" s="53" t="s">
         <v>189</v>
       </c>
       <c r="C16" t="s">
@@ -4502,10 +4473,10 @@
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="57">
+      <c r="A17" s="56">
         <v>2800000</v>
       </c>
-      <c r="B17" s="54" t="s">
+      <c r="B17" s="53" t="s">
         <v>192</v>
       </c>
       <c r="C17" t="s">
@@ -4513,10 +4484,10 @@
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="57">
+      <c r="A18" s="56">
         <v>3400000</v>
       </c>
-      <c r="B18" s="54" t="s">
+      <c r="B18" s="53" t="s">
         <v>195</v>
       </c>
       <c r="C18" t="s">
@@ -4524,10 +4495,10 @@
       </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="57">
+      <c r="A19" s="56">
         <v>2800000</v>
       </c>
-      <c r="B19" s="54" t="s">
+      <c r="B19" s="53" t="s">
         <v>204</v>
       </c>
       <c r="C19" t="s">
@@ -4535,10 +4506,10 @@
       </c>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="57">
+      <c r="A20" s="56">
         <v>2800000</v>
       </c>
-      <c r="B20" s="54" t="s">
+      <c r="B20" s="53" t="s">
         <v>206</v>
       </c>
       <c r="C20" t="s">
@@ -4546,10 +4517,10 @@
       </c>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="57">
+      <c r="A21" s="56">
         <v>2800000</v>
       </c>
-      <c r="B21" s="55" t="s">
+      <c r="B21" s="54" t="s">
         <v>245</v>
       </c>
       <c r="C21" t="s">
@@ -4557,10 +4528,10 @@
       </c>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="57">
+      <c r="A22" s="56">
         <v>2800000</v>
       </c>
-      <c r="B22" s="54" t="s">
+      <c r="B22" s="53" t="s">
         <v>208</v>
       </c>
       <c r="C22" t="s">
@@ -4568,10 +4539,10 @@
       </c>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="57">
+      <c r="A23" s="56">
         <v>2800000</v>
       </c>
-      <c r="B23" s="54" t="s">
+      <c r="B23" s="53" t="s">
         <v>211</v>
       </c>
       <c r="C23" t="s">
@@ -4579,10 +4550,10 @@
       </c>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="57">
+      <c r="A24" s="56">
         <v>2800000</v>
       </c>
-      <c r="B24" s="54" t="s">
+      <c r="B24" s="53" t="s">
         <v>213</v>
       </c>
       <c r="C24" t="s">
@@ -4590,10 +4561,10 @@
       </c>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="57">
+      <c r="A25" s="56">
         <v>2800000</v>
       </c>
-      <c r="B25" s="54" t="s">
+      <c r="B25" s="53" t="s">
         <v>215</v>
       </c>
       <c r="C25" t="s">
@@ -4601,10 +4572,10 @@
       </c>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="57">
+      <c r="A26" s="56">
         <v>2800000</v>
       </c>
-      <c r="B26" s="54" t="s">
+      <c r="B26" s="53" t="s">
         <v>218</v>
       </c>
       <c r="C26" t="s">
@@ -4612,10 +4583,10 @@
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="57">
+      <c r="A27" s="56">
         <v>2800000</v>
       </c>
-      <c r="B27" s="54" t="s">
+      <c r="B27" s="53" t="s">
         <v>220</v>
       </c>
       <c r="C27" t="s">
@@ -4623,10 +4594,10 @@
       </c>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="57">
+      <c r="A28" s="56">
         <v>2800000</v>
       </c>
-      <c r="B28" s="54" t="s">
+      <c r="B28" s="53" t="s">
         <v>222</v>
       </c>
       <c r="C28" t="s">
@@ -4634,10 +4605,10 @@
       </c>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="57">
+      <c r="A29" s="56">
         <v>3400000</v>
       </c>
-      <c r="B29" s="54" t="s">
+      <c r="B29" s="53" t="s">
         <v>224</v>
       </c>
       <c r="C29" t="s">
@@ -4645,10 +4616,10 @@
       </c>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="57">
+      <c r="A30" s="56">
         <v>2800000</v>
       </c>
-      <c r="B30" s="54" t="s">
+      <c r="B30" s="53" t="s">
         <v>226</v>
       </c>
       <c r="C30" t="s">
@@ -4656,10 +4627,10 @@
       </c>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="57">
+      <c r="A31" s="56">
         <v>2800000</v>
       </c>
-      <c r="B31" s="54" t="s">
+      <c r="B31" s="53" t="s">
         <v>228</v>
       </c>
       <c r="C31" t="s">
@@ -4667,10 +4638,10 @@
       </c>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="57">
+      <c r="A32" s="56">
         <v>1090000</v>
       </c>
-      <c r="B32" s="54" t="s">
+      <c r="B32" s="53" t="s">
         <v>161</v>
       </c>
       <c r="C32" t="s">
@@ -4678,10 +4649,10 @@
       </c>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="57">
+      <c r="A33" s="56">
         <v>1090000</v>
       </c>
-      <c r="B33" s="54" t="s">
+      <c r="B33" s="53" t="s">
         <v>163</v>
       </c>
       <c r="C33" t="s">
@@ -4689,10 +4660,10 @@
       </c>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="57">
+      <c r="A34" s="56">
         <v>990000</v>
       </c>
-      <c r="B34" s="54" t="s">
+      <c r="B34" s="53" t="s">
         <v>165</v>
       </c>
       <c r="C34" t="s">
@@ -4700,10 +4671,10 @@
       </c>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="57">
+      <c r="A35" s="56">
         <v>990000</v>
       </c>
-      <c r="B35" s="54" t="s">
+      <c r="B35" s="53" t="s">
         <v>168</v>
       </c>
       <c r="C35" t="s">
@@ -4711,10 +4682,10 @@
       </c>
     </row>
     <row r="36" spans="1:3">
-      <c r="A36" s="57">
+      <c r="A36" s="56">
         <v>990000</v>
       </c>
-      <c r="B36" s="54" t="s">
+      <c r="B36" s="53" t="s">
         <v>171</v>
       </c>
       <c r="C36" t="s">
@@ -4722,10 +4693,10 @@
       </c>
     </row>
     <row r="37" spans="1:3">
-      <c r="A37" s="58">
+      <c r="A37" s="57">
         <v>1090000</v>
       </c>
-      <c r="B37" s="55" t="s">
+      <c r="B37" s="54" t="s">
         <v>175</v>
       </c>
       <c r="C37" t="s">
@@ -4733,10 +4704,10 @@
       </c>
     </row>
     <row r="38" spans="1:3">
-      <c r="A38" s="57">
+      <c r="A38" s="56">
         <v>167000</v>
       </c>
-      <c r="B38" s="55" t="s">
+      <c r="B38" s="54" t="s">
         <v>243</v>
       </c>
       <c r="C38" t="s">
@@ -4744,10 +4715,10 @@
       </c>
     </row>
     <row r="39" spans="1:3">
-      <c r="A39" s="57">
+      <c r="A39" s="56">
         <v>1090000</v>
       </c>
-      <c r="B39" s="56" t="s">
+      <c r="B39" s="55" t="s">
         <v>244</v>
       </c>
       <c r="C39" t="s">
@@ -4755,10 +4726,10 @@
       </c>
     </row>
     <row r="40" spans="1:3">
-      <c r="A40" s="59">
+      <c r="A40" s="58">
         <v>1090000</v>
       </c>
-      <c r="B40" s="54" t="s">
+      <c r="B40" s="53" t="s">
         <v>180</v>
       </c>
       <c r="C40" t="s">
@@ -4766,10 +4737,10 @@
       </c>
     </row>
     <row r="41" spans="1:3">
-      <c r="A41" s="57">
+      <c r="A41" s="56">
         <v>1090000</v>
       </c>
-      <c r="B41" s="54" t="s">
+      <c r="B41" s="53" t="s">
         <v>195</v>
       </c>
       <c r="C41" t="s">
@@ -4777,10 +4748,10 @@
       </c>
     </row>
     <row r="42" spans="1:3">
-      <c r="A42" s="57">
+      <c r="A42" s="56">
         <v>1090000</v>
       </c>
-      <c r="B42" s="54" t="s">
+      <c r="B42" s="53" t="s">
         <v>204</v>
       </c>
       <c r="C42" t="s">
@@ -4788,10 +4759,10 @@
       </c>
     </row>
     <row r="43" spans="1:3">
-      <c r="A43" s="57">
+      <c r="A43" s="56">
         <v>1090000</v>
       </c>
-      <c r="B43" s="54" t="s">
+      <c r="B43" s="53" t="s">
         <v>218</v>
       </c>
       <c r="C43" t="s">
@@ -4799,10 +4770,10 @@
       </c>
     </row>
     <row r="44" spans="1:3">
-      <c r="A44" s="57">
+      <c r="A44" s="56">
         <v>1090000</v>
       </c>
-      <c r="B44" s="54" t="s">
+      <c r="B44" s="53" t="s">
         <v>220</v>
       </c>
       <c r="C44" t="s">
@@ -4810,10 +4781,10 @@
       </c>
     </row>
     <row r="45" spans="1:3">
-      <c r="A45" s="57">
+      <c r="A45" s="56">
         <v>448080</v>
       </c>
-      <c r="B45" s="54" t="s">
+      <c r="B45" s="53" t="s">
         <v>228</v>
       </c>
       <c r="C45" t="s">
@@ -4821,10 +4792,10 @@
       </c>
     </row>
     <row r="46" spans="1:3">
-      <c r="A46" s="60">
+      <c r="A46" s="59">
         <v>1600000</v>
       </c>
-      <c r="B46" s="63" t="s">
+      <c r="B46" s="62" t="s">
         <v>247</v>
       </c>
       <c r="C46" t="s">
@@ -4832,7 +4803,7 @@
       </c>
     </row>
     <row r="47" spans="1:3">
-      <c r="A47" s="68">
+      <c r="A47" s="67">
         <f>SUM(A4:A46)</f>
         <v>95995080</v>
       </c>
@@ -4869,12 +4840,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="26.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="71" t="s">
         <v>105</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
     </row>
     <row r="3" spans="1:5" s="24" customFormat="1" ht="40.5" customHeight="1">
       <c r="A3" s="4" t="s">
@@ -5108,48 +5079,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="26.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="71" t="s">
         <v>105</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
     </row>
     <row r="2" spans="1:7">
       <c r="F2" s="2"/>
     </row>
     <row r="3" spans="1:7" ht="30.75" customHeight="1">
-      <c r="A3" s="39" t="s">
+      <c r="A3" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="40" t="s">
+      <c r="B3" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="41" t="s">
+      <c r="C3" s="40" t="s">
         <v>108</v>
       </c>
-      <c r="D3" s="42" t="s">
+      <c r="D3" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="42" t="s">
+      <c r="E3" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="F3" s="42" t="s">
+      <c r="F3" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="43" t="s">
+      <c r="G3" s="42" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="30.75" customHeight="1">
-      <c r="A4" s="44">
+      <c r="A4" s="43">
         <f>ROW()-ROW($A$3)</f>
         <v>1</v>
       </c>
-      <c r="B4" s="45">
+      <c r="B4" s="44">
         <v>1144000</v>
       </c>
       <c r="C4" s="36">
@@ -5169,11 +5140,11 @@
       </c>
     </row>
     <row r="5" spans="1:7" ht="30.75" customHeight="1">
-      <c r="A5" s="44">
+      <c r="A5" s="43">
         <f t="shared" ref="A5:A6" si="0">ROW()-ROW($A$3)</f>
         <v>2</v>
       </c>
-      <c r="B5" s="45">
+      <c r="B5" s="44">
         <v>82200</v>
       </c>
       <c r="C5" s="36">
@@ -5193,11 +5164,11 @@
       </c>
     </row>
     <row r="6" spans="1:7" ht="30.75" customHeight="1">
-      <c r="A6" s="44">
+      <c r="A6" s="43">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B6" s="45">
+      <c r="B6" s="44">
         <v>61000</v>
       </c>
       <c r="C6" s="36">
@@ -5217,11 +5188,11 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="30.75" customHeight="1">
-      <c r="A7" s="44">
+      <c r="A7" s="43">
         <f t="shared" ref="A7:A11" si="1">ROW()-ROW($A$3)</f>
         <v>4</v>
       </c>
-      <c r="B7" s="45">
+      <c r="B7" s="44">
         <v>1193500</v>
       </c>
       <c r="C7" s="36">
@@ -5241,11 +5212,11 @@
       </c>
     </row>
     <row r="8" spans="1:7" ht="30.75" customHeight="1">
-      <c r="A8" s="44">
+      <c r="A8" s="43">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="B8" s="45">
+      <c r="B8" s="44">
         <v>3000000</v>
       </c>
       <c r="C8" s="36">
@@ -5263,11 +5234,11 @@
       </c>
     </row>
     <row r="9" spans="1:7" ht="30.75" customHeight="1">
-      <c r="A9" s="44">
+      <c r="A9" s="43">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="B9" s="45">
+      <c r="B9" s="44">
         <v>1000000</v>
       </c>
       <c r="C9" s="36">
@@ -5285,17 +5256,17 @@
       </c>
     </row>
     <row r="10" spans="1:7" ht="30.75" customHeight="1">
-      <c r="A10" s="44">
+      <c r="A10" s="43">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="B10" s="45">
+      <c r="B10" s="44">
         <v>464200</v>
       </c>
       <c r="C10" s="36">
         <v>46141</v>
       </c>
-      <c r="D10" s="38" t="s">
+      <c r="D10" s="37" t="s">
         <v>122</v>
       </c>
       <c r="E10" s="22" t="s">
@@ -5309,17 +5280,17 @@
       </c>
     </row>
     <row r="11" spans="1:7" ht="30.75" customHeight="1">
-      <c r="A11" s="44">
+      <c r="A11" s="43">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="B11" s="45">
+      <c r="B11" s="44">
         <v>52500</v>
       </c>
       <c r="C11" s="36">
         <v>46156</v>
       </c>
-      <c r="D11" s="38" t="s">
+      <c r="D11" s="37" t="s">
         <v>129</v>
       </c>
       <c r="E11" s="22" t="s">
@@ -5333,17 +5304,17 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="30.75" customHeight="1">
-      <c r="A12" s="44">
+      <c r="A12" s="43">
         <f t="shared" ref="A12:A16" si="2">ROW()-ROW($A$3)</f>
         <v>9</v>
       </c>
-      <c r="B12" s="45">
+      <c r="B12" s="44">
         <v>1000</v>
       </c>
       <c r="C12" s="36">
         <v>46156</v>
       </c>
-      <c r="D12" s="38" t="s">
+      <c r="D12" s="37" t="s">
         <v>133</v>
       </c>
       <c r="E12" s="22" t="s">
@@ -5357,17 +5328,17 @@
       </c>
     </row>
     <row r="13" spans="1:7" ht="30.75" customHeight="1">
-      <c r="A13" s="44">
+      <c r="A13" s="43">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="B13" s="45">
+      <c r="B13" s="44">
         <v>358000</v>
       </c>
       <c r="C13" s="36">
         <v>46156</v>
       </c>
-      <c r="D13" s="38" t="s">
+      <c r="D13" s="37" t="s">
         <v>132</v>
       </c>
       <c r="E13" s="22" t="s">
@@ -5381,17 +5352,17 @@
       </c>
     </row>
     <row r="14" spans="1:7" ht="30.75" customHeight="1">
-      <c r="A14" s="44">
+      <c r="A14" s="43">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
-      <c r="B14" s="45">
+      <c r="B14" s="44">
         <v>3000000</v>
       </c>
       <c r="C14" s="36">
         <v>46156</v>
       </c>
-      <c r="D14" s="38" t="s">
+      <c r="D14" s="37" t="s">
         <v>148</v>
       </c>
       <c r="E14" s="22" t="s">
@@ -5403,17 +5374,17 @@
       </c>
     </row>
     <row r="15" spans="1:7" ht="30.75" customHeight="1">
-      <c r="A15" s="44">
+      <c r="A15" s="43">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="B15" s="45">
+      <c r="B15" s="44">
         <v>14500</v>
       </c>
       <c r="C15" s="36">
         <v>46163</v>
       </c>
-      <c r="D15" s="38" t="s">
+      <c r="D15" s="37" t="s">
         <v>141</v>
       </c>
       <c r="E15" s="22" t="s">
@@ -5427,17 +5398,17 @@
       </c>
     </row>
     <row r="16" spans="1:7" ht="30.75" customHeight="1">
-      <c r="A16" s="44">
+      <c r="A16" s="43">
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
-      <c r="B16" s="45">
+      <c r="B16" s="44">
         <v>24000</v>
       </c>
       <c r="C16" s="36">
         <v>46163</v>
       </c>
-      <c r="D16" s="38" t="s">
+      <c r="D16" s="37" t="s">
         <v>142</v>
       </c>
       <c r="E16" s="22" t="s">
@@ -5451,17 +5422,17 @@
       </c>
     </row>
     <row r="17" spans="1:7" ht="30.75" customHeight="1">
-      <c r="A17" s="44">
+      <c r="A17" s="43">
         <f>ROW()-ROW($A$3)</f>
         <v>14</v>
       </c>
-      <c r="B17" s="45">
+      <c r="B17" s="44">
         <v>25600</v>
       </c>
       <c r="C17" s="36">
         <v>46163</v>
       </c>
-      <c r="D17" s="38" t="s">
+      <c r="D17" s="37" t="s">
         <v>140</v>
       </c>
       <c r="E17" s="22" t="s">
@@ -5475,17 +5446,17 @@
       </c>
     </row>
     <row r="18" spans="1:7" ht="30.75" customHeight="1">
-      <c r="A18" s="44">
+      <c r="A18" s="43">
         <f>ROW()-ROW($A$3)</f>
         <v>15</v>
       </c>
-      <c r="B18" s="45">
+      <c r="B18" s="44">
         <v>393000</v>
       </c>
       <c r="C18" s="36">
         <v>46163</v>
       </c>
-      <c r="D18" s="38" t="s">
+      <c r="D18" s="37" t="s">
         <v>143</v>
       </c>
       <c r="E18" s="22" t="s">
@@ -5499,17 +5470,17 @@
       </c>
     </row>
     <row r="19" spans="1:7" ht="30.75" customHeight="1">
-      <c r="A19" s="44">
+      <c r="A19" s="43">
         <f>ROW()-ROW($A$3)</f>
         <v>16</v>
       </c>
-      <c r="B19" s="45">
+      <c r="B19" s="44">
         <v>2750000</v>
       </c>
       <c r="C19" s="36">
         <v>46163</v>
       </c>
-      <c r="D19" s="38" t="s">
+      <c r="D19" s="37" t="s">
         <v>146</v>
       </c>
       <c r="E19" s="22" t="s">
@@ -5521,17 +5492,17 @@
       </c>
     </row>
     <row r="20" spans="1:7" ht="30.75" customHeight="1">
-      <c r="A20" s="44">
+      <c r="A20" s="43">
         <f>ROW()-ROW($A$3)</f>
         <v>17</v>
       </c>
-      <c r="B20" s="45">
+      <c r="B20" s="44">
         <v>1000000</v>
       </c>
       <c r="C20" s="36">
         <v>46163</v>
       </c>
-      <c r="D20" s="38" t="s">
+      <c r="D20" s="37" t="s">
         <v>147</v>
       </c>
       <c r="E20" s="22" t="s">
@@ -5543,468 +5514,468 @@
       </c>
     </row>
     <row r="21" spans="1:7" ht="30.75" customHeight="1">
-      <c r="A21" s="44">
+      <c r="A21" s="43">
         <f t="shared" ref="A21:A25" si="3">ROW()-ROW($A$3)</f>
         <v>18</v>
       </c>
-      <c r="B21" s="64">
+      <c r="B21" s="63">
         <v>1000000</v>
       </c>
-      <c r="C21" s="65">
+      <c r="C21" s="64">
         <v>46170</v>
       </c>
-      <c r="D21" s="38" t="s">
+      <c r="D21" s="37" t="s">
         <v>147</v>
       </c>
       <c r="E21" s="22" t="s">
         <v>121</v>
       </c>
-      <c r="F21" s="66"/>
-      <c r="G21" s="67" t="s">
+      <c r="F21" s="65"/>
+      <c r="G21" s="66" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="30.75" customHeight="1">
-      <c r="A22" s="44">
+      <c r="A22" s="43">
         <f t="shared" si="3"/>
         <v>19</v>
       </c>
-      <c r="B22" s="64">
+      <c r="B22" s="63">
         <v>2000000</v>
       </c>
-      <c r="C22" s="65">
+      <c r="C22" s="64">
         <v>46170</v>
       </c>
-      <c r="D22" s="66" t="s">
+      <c r="D22" s="65" t="s">
         <v>254</v>
       </c>
       <c r="E22" s="22" t="s">
         <v>120</v>
       </c>
-      <c r="F22" s="66"/>
-      <c r="G22" s="67" t="s">
+      <c r="F22" s="65"/>
+      <c r="G22" s="66" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="30.75" customHeight="1">
-      <c r="A23" s="44">
+      <c r="A23" s="43">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="B23" s="64">
+      <c r="B23" s="63">
         <v>380600</v>
       </c>
-      <c r="C23" s="65">
+      <c r="C23" s="64">
         <v>46170</v>
       </c>
-      <c r="D23" s="66" t="s">
+      <c r="D23" s="65" t="s">
         <v>255</v>
       </c>
-      <c r="E23" s="66" t="s">
+      <c r="E23" s="65" t="s">
         <v>256</v>
       </c>
-      <c r="F23" s="66" t="s">
+      <c r="F23" s="65" t="s">
         <v>127</v>
       </c>
-      <c r="G23" s="67" t="s">
+      <c r="G23" s="66" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="30.75" customHeight="1">
-      <c r="A24" s="44">
+      <c r="A24" s="43">
         <f t="shared" si="3"/>
         <v>21</v>
       </c>
-      <c r="B24" s="64">
+      <c r="B24" s="63">
         <v>22200</v>
       </c>
-      <c r="C24" s="65">
+      <c r="C24" s="64">
         <v>46170</v>
       </c>
-      <c r="D24" s="66" t="s">
+      <c r="D24" s="65" t="s">
         <v>258</v>
       </c>
-      <c r="E24" s="66" t="s">
+      <c r="E24" s="65" t="s">
         <v>257</v>
       </c>
-      <c r="F24" s="66" t="s">
+      <c r="F24" s="65" t="s">
         <v>110</v>
       </c>
-      <c r="G24" s="67" t="s">
+      <c r="G24" s="66" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="30.75" customHeight="1">
-      <c r="A25" s="44">
+      <c r="A25" s="43">
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
-      <c r="B25" s="64">
+      <c r="B25" s="63">
         <v>37000</v>
       </c>
-      <c r="C25" s="65">
+      <c r="C25" s="64">
         <v>46170</v>
       </c>
-      <c r="D25" s="66" t="s">
+      <c r="D25" s="65" t="s">
         <v>259</v>
       </c>
-      <c r="E25" s="66" t="s">
+      <c r="E25" s="65" t="s">
         <v>257</v>
       </c>
-      <c r="F25" s="66" t="s">
+      <c r="F25" s="65" t="s">
         <v>113</v>
       </c>
-      <c r="G25" s="67" t="s">
+      <c r="G25" s="66" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="30.75" customHeight="1">
-      <c r="A26" s="44">
+      <c r="A26" s="43">
         <f>ROW()-ROW($A$3)</f>
         <v>23</v>
       </c>
-      <c r="B26" s="71">
+      <c r="B26" s="70">
         <v>105000</v>
       </c>
-      <c r="C26" s="69">
+      <c r="C26" s="68">
         <v>46170</v>
       </c>
-      <c r="D26" s="70" t="s">
+      <c r="D26" s="69" t="s">
         <v>264</v>
       </c>
-      <c r="E26" s="70" t="s">
+      <c r="E26" s="69" t="s">
         <v>260</v>
       </c>
-      <c r="F26" s="70" t="s">
+      <c r="F26" s="69" t="s">
         <v>261</v>
       </c>
-      <c r="G26" s="70" t="s">
+      <c r="G26" s="69" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="30.75" customHeight="1">
-      <c r="A27" s="44">
+      <c r="A27" s="43">
         <f>ROW()-ROW($A$3)</f>
         <v>24</v>
       </c>
-      <c r="B27" s="71">
+      <c r="B27" s="70">
         <v>175100</v>
       </c>
-      <c r="C27" s="69">
+      <c r="C27" s="68">
         <v>46170</v>
       </c>
-      <c r="D27" s="70" t="s">
+      <c r="D27" s="69" t="s">
         <v>263</v>
       </c>
-      <c r="E27" s="70" t="s">
+      <c r="E27" s="69" t="s">
         <v>260</v>
       </c>
-      <c r="F27" s="70" t="s">
+      <c r="F27" s="69" t="s">
         <v>262</v>
       </c>
-      <c r="G27" s="70" t="s">
+      <c r="G27" s="69" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="30.75" customHeight="1">
-      <c r="A28" s="44">
+      <c r="A28" s="43">
         <f>ROW()-ROW($A$3)</f>
         <v>25</v>
       </c>
-      <c r="B28" s="71">
+      <c r="B28" s="70">
         <f>64600</f>
         <v>64600</v>
       </c>
-      <c r="C28" s="69">
+      <c r="C28" s="68">
         <v>46170</v>
       </c>
-      <c r="D28" s="70" t="s">
+      <c r="D28" s="69" t="s">
         <v>265</v>
       </c>
-      <c r="E28" s="70" t="s">
+      <c r="E28" s="69" t="s">
         <v>260</v>
       </c>
-      <c r="F28" s="70" t="s">
+      <c r="F28" s="69" t="s">
         <v>110</v>
       </c>
-      <c r="G28" s="70" t="s">
+      <c r="G28" s="69" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="19.5">
-      <c r="A29" s="3">
+      <c r="A29" s="43">
         <v>26</v>
       </c>
-      <c r="B29" s="74">
+      <c r="B29" s="70">
         <v>14266000</v>
       </c>
-      <c r="C29" s="75">
+      <c r="C29" s="68">
         <v>46175</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="D29" s="69" t="s">
         <v>266</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="E29" s="69" t="s">
         <v>267</v>
       </c>
-      <c r="F29" s="3" t="s">
+      <c r="F29" s="69" t="s">
         <v>268</v>
       </c>
-      <c r="G29" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
+      <c r="G29" s="69" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="19.5">
+      <c r="A30" s="43">
         <v>27</v>
       </c>
-      <c r="B30" s="72">
+      <c r="B30" s="70">
         <v>1500000</v>
       </c>
-      <c r="C30" s="72">
+      <c r="C30" s="68">
         <v>46176</v>
       </c>
-      <c r="D30" s="34" t="s">
+      <c r="D30" s="69" t="s">
         <v>269</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="E30" s="69" t="s">
+        <v>120</v>
+      </c>
+      <c r="F30" s="69" t="s">
         <v>270</v>
       </c>
-      <c r="F30" s="34" t="s">
+      <c r="G30" s="69" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="19.5">
+      <c r="A31" s="43">
+        <v>28</v>
+      </c>
+      <c r="B31" s="70">
+        <v>1000000</v>
+      </c>
+      <c r="C31" s="68">
+        <v>46184</v>
+      </c>
+      <c r="D31" s="69" t="s">
         <v>271</v>
       </c>
-      <c r="G30" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="19.5">
-      <c r="A31">
-        <v>28</v>
-      </c>
-      <c r="B31" s="37">
+      <c r="E31" s="69" t="s">
+        <v>120</v>
+      </c>
+      <c r="F31" s="69" t="s">
+        <v>272</v>
+      </c>
+      <c r="G31" s="69" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="19.5">
+      <c r="A32" s="43">
+        <v>29</v>
+      </c>
+      <c r="B32" s="70">
         <v>1000000</v>
       </c>
-      <c r="C31" s="37">
+      <c r="C32" s="68">
         <v>46184</v>
       </c>
-      <c r="D31" s="73" t="s">
-        <v>272</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="F31" s="34" t="s">
+      <c r="D32" s="69" t="s">
+        <v>147</v>
+      </c>
+      <c r="E32" s="69" t="s">
+        <v>121</v>
+      </c>
+      <c r="F32" s="69" t="s">
         <v>273</v>
       </c>
-      <c r="G31" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>29</v>
-      </c>
-      <c r="B32" s="72">
+      <c r="G32" s="69" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="19.5">
+      <c r="A33" s="43">
+        <v>30</v>
+      </c>
+      <c r="B33" s="70">
+        <v>670000</v>
+      </c>
+      <c r="C33" s="68">
+        <v>46184</v>
+      </c>
+      <c r="D33" s="69" t="s">
+        <v>274</v>
+      </c>
+      <c r="E33" s="69" t="s">
+        <v>25</v>
+      </c>
+      <c r="F33" s="69" t="s">
+        <v>275</v>
+      </c>
+      <c r="G33" s="69" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="19.5">
+      <c r="A34" s="43">
+        <v>31</v>
+      </c>
+      <c r="B34" s="70">
+        <v>70000</v>
+      </c>
+      <c r="C34" s="68">
+        <v>46184</v>
+      </c>
+      <c r="D34" s="69" t="s">
+        <v>276</v>
+      </c>
+      <c r="E34" s="69" t="s">
+        <v>277</v>
+      </c>
+      <c r="F34" s="69" t="s">
+        <v>278</v>
+      </c>
+      <c r="G34" s="69" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="19.5">
+      <c r="A35" s="43">
+        <v>32</v>
+      </c>
+      <c r="B35" s="70">
+        <v>50200</v>
+      </c>
+      <c r="C35" s="68">
+        <v>46184</v>
+      </c>
+      <c r="D35" s="69" t="s">
+        <v>109</v>
+      </c>
+      <c r="E35" s="69" t="s">
+        <v>109</v>
+      </c>
+      <c r="F35" s="69" t="s">
+        <v>110</v>
+      </c>
+      <c r="G35" s="69" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="19.5">
+      <c r="A36" s="43">
+        <v>33</v>
+      </c>
+      <c r="B36" s="70">
+        <v>29700</v>
+      </c>
+      <c r="C36" s="68">
+        <v>46184</v>
+      </c>
+      <c r="D36" s="69" t="s">
+        <v>279</v>
+      </c>
+      <c r="E36" s="69" t="s">
+        <v>109</v>
+      </c>
+      <c r="F36" s="69" t="s">
+        <v>113</v>
+      </c>
+      <c r="G36" s="69" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="19.5">
+      <c r="A37" s="43">
+        <v>34</v>
+      </c>
+      <c r="B37" s="70">
         <v>1000000</v>
       </c>
-      <c r="C32" s="72">
-        <v>46184</v>
-      </c>
-      <c r="D32" s="34" t="s">
-        <v>274</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="F32" s="34" t="s">
-        <v>276</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>30</v>
-      </c>
-      <c r="B33" s="72">
-        <v>670000</v>
-      </c>
-      <c r="C33" s="72">
-        <v>46184</v>
-      </c>
-      <c r="D33" s="34" t="s">
-        <v>277</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="F33" s="34" t="s">
-        <v>279</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>31</v>
-      </c>
-      <c r="B34" s="35">
-        <v>70000</v>
-      </c>
-      <c r="C34" s="35">
-        <v>46184</v>
-      </c>
-      <c r="D34" s="34" t="s">
-        <v>280</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="F34" s="34" t="s">
+      <c r="C37" s="68">
+        <v>46191</v>
+      </c>
+      <c r="D37" s="69" t="s">
         <v>282</v>
       </c>
-      <c r="G34" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>32</v>
-      </c>
-      <c r="B35" s="35">
-        <v>50200</v>
-      </c>
-      <c r="C35" s="35">
-        <v>46184</v>
-      </c>
-      <c r="D35" s="34" t="s">
+      <c r="E37" s="69" t="s">
+        <v>120</v>
+      </c>
+      <c r="F37" s="69" t="s">
         <v>283</v>
       </c>
-      <c r="E35" s="2" t="s">
+      <c r="G37" s="69" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="19.5">
+      <c r="A38" s="43">
+        <v>35</v>
+      </c>
+      <c r="B38" s="70">
+        <v>500000</v>
+      </c>
+      <c r="C38" s="68">
+        <v>46191</v>
+      </c>
+      <c r="D38" s="69" t="s">
+        <v>285</v>
+      </c>
+      <c r="E38" s="69" t="s">
+        <v>121</v>
+      </c>
+      <c r="F38" s="69" t="s">
         <v>283</v>
       </c>
-      <c r="F35" s="34" t="s">
+      <c r="G38" s="69" t="s">
         <v>284</v>
       </c>
-      <c r="G35" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36">
-        <v>33</v>
-      </c>
-      <c r="B36" s="35">
-        <v>29700</v>
-      </c>
-      <c r="C36" s="35">
-        <v>46184</v>
-      </c>
-      <c r="D36" s="34" t="s">
-        <v>285</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="F36" s="34" t="s">
+    </row>
+    <row r="39" spans="1:7" ht="19.5">
+      <c r="A39" s="43">
+        <v>36</v>
+      </c>
+      <c r="B39" s="70">
+        <v>395000</v>
+      </c>
+      <c r="C39" s="68">
+        <v>46191</v>
+      </c>
+      <c r="D39" s="69" t="s">
         <v>286</v>
       </c>
-      <c r="G36" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37">
-        <v>34</v>
-      </c>
-      <c r="B37" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="C37" s="35">
+      <c r="E39" s="69" t="s">
+        <v>25</v>
+      </c>
+      <c r="F39" s="69" t="s">
+        <v>287</v>
+      </c>
+      <c r="G39" s="69" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="19.5">
+      <c r="A40" s="43">
+        <v>37</v>
+      </c>
+      <c r="B40" s="70">
+        <v>78100</v>
+      </c>
+      <c r="C40" s="68">
         <v>46191</v>
       </c>
-      <c r="D37" s="34" t="s">
-        <v>287</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="F37" s="34" t="s">
-        <v>289</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38">
-        <v>35</v>
-      </c>
-      <c r="B38" s="1">
-        <v>500000</v>
-      </c>
-      <c r="C38" s="35">
-        <v>46191</v>
-      </c>
-      <c r="D38" s="34" t="s">
-        <v>290</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="F38" s="34" t="s">
-        <v>289</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39">
-        <v>36</v>
-      </c>
-      <c r="B39" s="1">
-        <v>395000</v>
-      </c>
-      <c r="C39" s="35">
-        <v>46191</v>
-      </c>
-      <c r="D39" s="34" t="s">
-        <v>292</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="F39" s="34" t="s">
-        <v>294</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40">
-        <v>37</v>
-      </c>
-      <c r="B40" s="1">
-        <v>78100</v>
-      </c>
-      <c r="C40" s="35">
-        <v>46191</v>
-      </c>
-      <c r="D40" s="34" t="s">
-        <v>295</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="F40" s="34" t="s">
-        <v>296</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>10</v>
+      <c r="D40" s="69" t="s">
+        <v>109</v>
+      </c>
+      <c r="E40" s="69" t="s">
+        <v>109</v>
+      </c>
+      <c r="F40" s="69" t="s">
+        <v>110</v>
+      </c>
+      <c r="G40" s="69" t="s">
+        <v>284</v>
       </c>
     </row>
   </sheetData>
@@ -6213,1196 +6184,1424 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0625D6E-2678-482C-88B1-4B31BC9434B5}">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:O31"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="8" style="47" customWidth="1"/>
-    <col min="2" max="2" width="34" style="47" customWidth="1"/>
-    <col min="3" max="4" width="12" style="47" customWidth="1"/>
-    <col min="5" max="8" width="16" style="47" customWidth="1"/>
-    <col min="9" max="10" width="12" style="47" customWidth="1"/>
-    <col min="11" max="11" width="10" style="47" customWidth="1"/>
-    <col min="12" max="12" width="30" style="47" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="47"/>
+    <col min="1" max="1" width="8" style="46" customWidth="1"/>
+    <col min="2" max="2" width="34" style="46" customWidth="1"/>
+    <col min="3" max="4" width="12" style="46" customWidth="1"/>
+    <col min="5" max="11" width="16" style="46" customWidth="1"/>
+    <col min="12" max="13" width="12" style="46" customWidth="1"/>
+    <col min="14" max="14" width="10" style="46" customWidth="1"/>
+    <col min="15" max="15" width="30" style="46" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="46"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15">
-      <c r="A1" s="46" t="s">
+    <row r="1" spans="1:15" ht="15">
+      <c r="A1" s="45" t="s">
         <v>149</v>
       </c>
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="45" t="s">
         <v>150</v>
       </c>
-      <c r="C1" s="46" t="s">
+      <c r="C1" s="45" t="s">
         <v>151</v>
       </c>
-      <c r="D1" s="46" t="s">
+      <c r="D1" s="45" t="s">
         <v>152</v>
       </c>
-      <c r="E1" s="46" t="s">
+      <c r="E1" s="45" t="s">
         <v>153</v>
       </c>
-      <c r="F1" s="46" t="s">
+      <c r="F1" s="45" t="s">
         <v>154</v>
       </c>
-      <c r="G1" s="46" t="s">
+      <c r="G1" s="45" t="s">
         <v>155</v>
       </c>
-      <c r="H1" s="46" t="s">
+      <c r="H1" s="45" t="s">
         <v>238</v>
       </c>
-      <c r="I1" s="46" t="s">
+      <c r="I1" s="45" t="s">
+        <v>288</v>
+      </c>
+      <c r="J1" s="45" t="s">
+        <v>289</v>
+      </c>
+      <c r="K1" s="45" t="s">
+        <v>290</v>
+      </c>
+      <c r="L1" s="45" t="s">
         <v>156</v>
       </c>
-      <c r="J1" s="46" t="s">
+      <c r="M1" s="45" t="s">
         <v>157</v>
       </c>
-      <c r="K1" s="46" t="s">
+      <c r="N1" s="45" t="s">
         <v>158</v>
       </c>
-      <c r="L1" s="46" t="s">
+      <c r="O1" s="45" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="16.5">
-      <c r="A2" s="48">
+    <row r="2" spans="1:15" ht="16.5">
+      <c r="A2" s="47">
         <v>1</v>
       </c>
-      <c r="B2" s="49" t="s">
+      <c r="B2" s="48" t="s">
         <v>160</v>
       </c>
-      <c r="C2" s="48" t="s">
+      <c r="C2" s="47" t="s">
         <v>161</v>
       </c>
-      <c r="D2" s="48" t="s">
+      <c r="D2" s="47" t="s">
         <v>162</v>
       </c>
-      <c r="E2" s="48" t="s">
-        <v>234</v>
-      </c>
-      <c r="F2" s="48" t="s">
-        <v>234</v>
-      </c>
-      <c r="G2" s="48" t="s">
-        <v>234</v>
-      </c>
-      <c r="H2" s="48" t="s">
+      <c r="E2" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="F2" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="G2" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="H2" s="47" t="s">
         <v>253</v>
       </c>
-      <c r="I2" s="48">
-        <f t="shared" ref="I2:I30" si="0">COUNTIF(E2:G2,"참석")</f>
+      <c r="I2" s="47" t="s">
+        <v>291</v>
+      </c>
+      <c r="J2" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="K2" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="L2" s="47">
+        <f>COUNTIF(E2:H2,"참석")+COUNTIF(J2:K2,"참석")</f>
+        <v>6</v>
+      </c>
+      <c r="M2" s="47">
+        <f>COUNTIF(E2:H2,"참석")+COUNTIF(E2:H2,"불참")+COUNTIF(J2:K2,"참석")+COUNTIF(J2:K2,"불참")</f>
+        <v>6</v>
+      </c>
+      <c r="N2" s="49">
+        <f>IF(M2=0,"",L2/M2)</f>
+        <v>1</v>
+      </c>
+      <c r="O2" s="48"/>
+    </row>
+    <row r="3" spans="1:15" ht="16.5">
+      <c r="A3" s="47">
+        <v>2</v>
+      </c>
+      <c r="B3" s="48" t="s">
+        <v>197</v>
+      </c>
+      <c r="C3" s="47" t="s">
+        <v>163</v>
+      </c>
+      <c r="D3" s="47" t="s">
+        <v>162</v>
+      </c>
+      <c r="E3" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="F3" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="G3" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="H3" s="47" t="s">
+        <v>253</v>
+      </c>
+      <c r="I3" s="47" t="s">
+        <v>291</v>
+      </c>
+      <c r="J3" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="K3" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="L3" s="47">
+        <f>COUNTIF(E3:H3,"참석")+COUNTIF(J3:K3,"참석")</f>
+        <v>6</v>
+      </c>
+      <c r="M3" s="47">
+        <f>COUNTIF(E3:H3,"참석")+COUNTIF(E3:H3,"불참")+COUNTIF(J3:K3,"참석")+COUNTIF(J3:K3,"불참")</f>
+        <v>6</v>
+      </c>
+      <c r="N3" s="49">
+        <f>IF(M3=0,"",L3/M3)</f>
+        <v>1</v>
+      </c>
+      <c r="O3" s="48"/>
+    </row>
+    <row r="4" spans="1:15" ht="16.5">
+      <c r="A4" s="47">
         <v>3</v>
       </c>
-      <c r="J2" s="48">
-        <f t="shared" ref="J2:J30" si="1">COUNTIF(E2:G2,"참석")+COUNTIF(E2:G2,"불참")</f>
+      <c r="B4" s="48" t="s">
+        <v>164</v>
+      </c>
+      <c r="C4" s="47" t="s">
+        <v>165</v>
+      </c>
+      <c r="D4" s="47" t="s">
+        <v>166</v>
+      </c>
+      <c r="E4" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="F4" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="G4" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="H4" s="47" t="s">
+        <v>253</v>
+      </c>
+      <c r="I4" s="47" t="s">
+        <v>291</v>
+      </c>
+      <c r="J4" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="K4" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="L4" s="47">
+        <f>COUNTIF(E4:H4,"참석")+COUNTIF(J4:K4,"참석")</f>
+        <v>6</v>
+      </c>
+      <c r="M4" s="47">
+        <f>COUNTIF(E4:H4,"참석")+COUNTIF(E4:H4,"불참")+COUNTIF(J4:K4,"참석")+COUNTIF(J4:K4,"불참")</f>
+        <v>6</v>
+      </c>
+      <c r="N4" s="49">
+        <f>IF(M4=0,"",L4/M4)</f>
+        <v>1</v>
+      </c>
+      <c r="O4" s="48"/>
+    </row>
+    <row r="5" spans="1:15" ht="16.5">
+      <c r="A5" s="47">
+        <v>4</v>
+      </c>
+      <c r="B5" s="48" t="s">
+        <v>167</v>
+      </c>
+      <c r="C5" s="47" t="s">
+        <v>168</v>
+      </c>
+      <c r="D5" s="47" t="s">
+        <v>169</v>
+      </c>
+      <c r="E5" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="F5" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="G5" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="H5" s="47" t="s">
+        <v>253</v>
+      </c>
+      <c r="I5" s="47"/>
+      <c r="J5" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="K5" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="L5" s="47">
+        <f>COUNTIF(E5:H5,"참석")+COUNTIF(J5:K5,"참석")</f>
+        <v>6</v>
+      </c>
+      <c r="M5" s="47">
+        <f>COUNTIF(E5:H5,"참석")+COUNTIF(E5:H5,"불참")+COUNTIF(J5:K5,"참석")+COUNTIF(J5:K5,"불참")</f>
+        <v>6</v>
+      </c>
+      <c r="N5" s="49">
+        <f>IF(M5=0,"",L5/M5)</f>
+        <v>1</v>
+      </c>
+      <c r="O5" s="48"/>
+    </row>
+    <row r="6" spans="1:15" ht="16.5">
+      <c r="A6" s="47">
+        <v>5</v>
+      </c>
+      <c r="B6" s="48" t="s">
+        <v>170</v>
+      </c>
+      <c r="C6" s="47" t="s">
+        <v>171</v>
+      </c>
+      <c r="D6" s="47" t="s">
+        <v>172</v>
+      </c>
+      <c r="E6" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="F6" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="G6" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="H6" s="47" t="s">
+        <v>253</v>
+      </c>
+      <c r="I6" s="47" t="s">
+        <v>291</v>
+      </c>
+      <c r="J6" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="K6" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="L6" s="47">
+        <f>COUNTIF(E6:H6,"참석")+COUNTIF(J6:K6,"참석")</f>
+        <v>4</v>
+      </c>
+      <c r="M6" s="47">
+        <f>COUNTIF(E6:H6,"참석")+COUNTIF(E6:H6,"불참")+COUNTIF(J6:K6,"참석")+COUNTIF(J6:K6,"불참")</f>
+        <v>6</v>
+      </c>
+      <c r="N6" s="49">
+        <f>IF(M6=0,"",L6/M6)</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="O6" s="48"/>
+    </row>
+    <row r="7" spans="1:15" ht="16.5">
+      <c r="A7" s="47">
+        <v>6</v>
+      </c>
+      <c r="B7" s="48" t="s">
+        <v>174</v>
+      </c>
+      <c r="C7" s="47" t="s">
+        <v>175</v>
+      </c>
+      <c r="D7" s="47" t="s">
+        <v>176</v>
+      </c>
+      <c r="E7" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="F7" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="G7" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="H7" s="47" t="s">
+        <v>253</v>
+      </c>
+      <c r="I7" s="47" t="s">
+        <v>291</v>
+      </c>
+      <c r="J7" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="K7" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="L7" s="47">
+        <f>COUNTIF(E7:H7,"참석")+COUNTIF(J7:K7,"참석")</f>
+        <v>6</v>
+      </c>
+      <c r="M7" s="47">
+        <f>COUNTIF(E7:H7,"참석")+COUNTIF(E7:H7,"불참")+COUNTIF(J7:K7,"참석")+COUNTIF(J7:K7,"불참")</f>
+        <v>6</v>
+      </c>
+      <c r="N7" s="49">
+        <f>IF(M7=0,"",L7/M7)</f>
+        <v>1</v>
+      </c>
+      <c r="O7" s="48"/>
+    </row>
+    <row r="8" spans="1:15" ht="16.5">
+      <c r="A8" s="47">
+        <v>7</v>
+      </c>
+      <c r="B8" s="48" t="s">
+        <v>177</v>
+      </c>
+      <c r="C8" s="47" t="s">
+        <v>178</v>
+      </c>
+      <c r="D8" s="47" t="s">
+        <v>179</v>
+      </c>
+      <c r="E8" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="F8" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="G8" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="H8" s="47" t="s">
+        <v>253</v>
+      </c>
+      <c r="I8" s="47"/>
+      <c r="J8" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="K8" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="L8" s="47">
+        <f>COUNTIF(E8:H8,"참석")+COUNTIF(J8:K8,"참석")</f>
         <v>3</v>
       </c>
-      <c r="K2" s="50">
-        <f t="shared" ref="K2:K31" si="2">IF(J2=0,"",I2/J2)</f>
+      <c r="M8" s="47">
+        <f>COUNTIF(E8:H8,"참석")+COUNTIF(E8:H8,"불참")+COUNTIF(J8:K8,"참석")+COUNTIF(J8:K8,"불참")</f>
+        <v>6</v>
+      </c>
+      <c r="N8" s="49">
+        <f>IF(M8=0,"",L8/M8)</f>
+        <v>0.5</v>
+      </c>
+      <c r="O8" s="48"/>
+    </row>
+    <row r="9" spans="1:15" ht="16.5">
+      <c r="A9" s="47">
+        <v>8</v>
+      </c>
+      <c r="B9" s="48" t="s">
+        <v>198</v>
+      </c>
+      <c r="C9" s="47" t="s">
+        <v>199</v>
+      </c>
+      <c r="D9" s="47" t="s">
+        <v>200</v>
+      </c>
+      <c r="E9" s="47" t="s">
+        <v>233</v>
+      </c>
+      <c r="F9" s="47" t="s">
+        <v>233</v>
+      </c>
+      <c r="G9" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="H9" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="I9" s="47" t="s">
+        <v>291</v>
+      </c>
+      <c r="J9" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="K9" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="L9" s="47">
+        <f>COUNTIF(E9:H9,"참석")+COUNTIF(J9:K9,"참석")</f>
+        <v>3</v>
+      </c>
+      <c r="M9" s="47">
+        <f>COUNTIF(E9:H9,"참석")+COUNTIF(E9:H9,"불참")+COUNTIF(J9:K9,"참석")+COUNTIF(J9:K9,"불참")</f>
+        <v>4</v>
+      </c>
+      <c r="N9" s="49">
+        <f>IF(M9=0,"",L9/M9)</f>
+        <v>0.75</v>
+      </c>
+      <c r="O9" s="48" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="16.5">
+      <c r="A10" s="47">
+        <v>9</v>
+      </c>
+      <c r="B10" s="48" t="s">
+        <v>201</v>
+      </c>
+      <c r="C10" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="D10" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="E10" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="F10" s="47" t="s">
+        <v>232</v>
+      </c>
+      <c r="G10" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="H10" s="47" t="s">
+        <v>253</v>
+      </c>
+      <c r="I10" s="47"/>
+      <c r="J10" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="K10" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="L10" s="47">
+        <f>COUNTIF(E10:H10,"참석")+COUNTIF(J10:K10,"참석")</f>
+        <v>3</v>
+      </c>
+      <c r="M10" s="47">
+        <f>COUNTIF(E10:H10,"참석")+COUNTIF(E10:H10,"불참")+COUNTIF(J10:K10,"참석")+COUNTIF(J10:K10,"불참")</f>
+        <v>6</v>
+      </c>
+      <c r="N10" s="49">
+        <f>IF(M10=0,"",L10/M10)</f>
+        <v>0.5</v>
+      </c>
+      <c r="O10" s="48"/>
+    </row>
+    <row r="11" spans="1:15" ht="16.5">
+      <c r="A11" s="47">
+        <v>10</v>
+      </c>
+      <c r="B11" s="48" t="s">
+        <v>182</v>
+      </c>
+      <c r="C11" s="47" t="s">
+        <v>183</v>
+      </c>
+      <c r="D11" s="47" t="s">
+        <v>184</v>
+      </c>
+      <c r="E11" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="F11" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="G11" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="H11" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="I11" s="47"/>
+      <c r="J11" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="K11" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="L11" s="47">
+        <f>COUNTIF(E11:H11,"참석")+COUNTIF(J11:K11,"참석")</f>
+        <v>3</v>
+      </c>
+      <c r="M11" s="47">
+        <f>COUNTIF(E11:H11,"참석")+COUNTIF(E11:H11,"불참")+COUNTIF(J11:K11,"참석")+COUNTIF(J11:K11,"불참")</f>
+        <v>6</v>
+      </c>
+      <c r="N11" s="49">
+        <f>IF(M11=0,"",L11/M11)</f>
+        <v>0.5</v>
+      </c>
+      <c r="O11" s="48"/>
+    </row>
+    <row r="12" spans="1:15" ht="16.5">
+      <c r="A12" s="47">
+        <v>11</v>
+      </c>
+      <c r="B12" s="48" t="s">
+        <v>185</v>
+      </c>
+      <c r="C12" s="47" t="s">
+        <v>186</v>
+      </c>
+      <c r="D12" s="47" t="s">
+        <v>179</v>
+      </c>
+      <c r="E12" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="F12" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="G12" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="H12" s="47" t="s">
+        <v>253</v>
+      </c>
+      <c r="I12" s="47"/>
+      <c r="J12" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="K12" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="L12" s="47">
+        <f>COUNTIF(E12:H12,"참석")+COUNTIF(J12:K12,"참석")</f>
+        <v>4</v>
+      </c>
+      <c r="M12" s="47">
+        <f>COUNTIF(E12:H12,"참석")+COUNTIF(E12:H12,"불참")+COUNTIF(J12:K12,"참석")+COUNTIF(J12:K12,"불참")</f>
+        <v>6</v>
+      </c>
+      <c r="N12" s="49">
+        <f>IF(M12=0,"",L12/M12)</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="O12" s="48"/>
+    </row>
+    <row r="13" spans="1:15" ht="16.5">
+      <c r="A13" s="47">
+        <v>12</v>
+      </c>
+      <c r="B13" s="48" t="s">
+        <v>187</v>
+      </c>
+      <c r="C13" s="47" t="s">
+        <v>188</v>
+      </c>
+      <c r="D13" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="E13" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="F13" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="G13" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="H13" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="I13" s="47"/>
+      <c r="J13" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="K13" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="L13" s="47">
+        <f>COUNTIF(E13:H13,"참석")+COUNTIF(J13:K13,"참석")</f>
+        <v>2</v>
+      </c>
+      <c r="M13" s="47">
+        <f>COUNTIF(E13:H13,"참석")+COUNTIF(E13:H13,"불참")+COUNTIF(J13:K13,"참석")+COUNTIF(J13:K13,"불참")</f>
+        <v>6</v>
+      </c>
+      <c r="N13" s="49">
+        <f>IF(M13=0,"",L13/M13)</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="O13" s="48"/>
+    </row>
+    <row r="14" spans="1:15" ht="16.5">
+      <c r="A14" s="47">
+        <v>13</v>
+      </c>
+      <c r="B14" s="48" t="s">
+        <v>202</v>
+      </c>
+      <c r="C14" s="47" t="s">
+        <v>189</v>
+      </c>
+      <c r="D14" s="47" t="s">
+        <v>190</v>
+      </c>
+      <c r="E14" s="47" t="s">
+        <v>232</v>
+      </c>
+      <c r="F14" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="G14" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="H14" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="I14" s="47"/>
+      <c r="J14" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="K14" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="L14" s="47">
+        <f>COUNTIF(E14:H14,"참석")+COUNTIF(J14:K14,"참석")</f>
+        <v>2</v>
+      </c>
+      <c r="M14" s="47">
+        <f>COUNTIF(E14:H14,"참석")+COUNTIF(E14:H14,"불참")+COUNTIF(J14:K14,"참석")+COUNTIF(J14:K14,"불참")</f>
+        <v>6</v>
+      </c>
+      <c r="N14" s="49">
+        <f>IF(M14=0,"",L14/M14)</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="O14" s="48"/>
+    </row>
+    <row r="15" spans="1:15" ht="16.5">
+      <c r="A15" s="47">
+        <v>14</v>
+      </c>
+      <c r="B15" s="48" t="s">
+        <v>191</v>
+      </c>
+      <c r="C15" s="47" t="s">
+        <v>192</v>
+      </c>
+      <c r="D15" s="47" t="s">
+        <v>193</v>
+      </c>
+      <c r="E15" s="47" t="s">
+        <v>235</v>
+      </c>
+      <c r="F15" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="G15" s="47" t="s">
+        <v>232</v>
+      </c>
+      <c r="H15" s="47" t="s">
+        <v>253</v>
+      </c>
+      <c r="I15" s="47"/>
+      <c r="J15" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="K15" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="L15" s="47">
+        <f>COUNTIF(E15:H15,"참석")+COUNTIF(J15:K15,"참석")</f>
+        <v>5</v>
+      </c>
+      <c r="M15" s="47">
+        <f>COUNTIF(E15:H15,"참석")+COUNTIF(E15:H15,"불참")+COUNTIF(J15:K15,"참석")+COUNTIF(J15:K15,"불참")</f>
+        <v>6</v>
+      </c>
+      <c r="N15" s="49">
+        <f>IF(M15=0,"",L15/M15)</f>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="O15" s="48"/>
+    </row>
+    <row r="16" spans="1:15" ht="16.5">
+      <c r="A16" s="47">
+        <v>15</v>
+      </c>
+      <c r="B16" s="46" t="s">
+        <v>194</v>
+      </c>
+      <c r="C16" s="50" t="s">
+        <v>195</v>
+      </c>
+      <c r="D16" s="50" t="s">
+        <v>196</v>
+      </c>
+      <c r="E16" s="46" t="s">
+        <v>232</v>
+      </c>
+      <c r="F16" s="46" t="s">
+        <v>234</v>
+      </c>
+      <c r="G16" s="47" t="s">
+        <v>232</v>
+      </c>
+      <c r="H16" s="47" t="s">
+        <v>253</v>
+      </c>
+      <c r="I16" s="47" t="s">
+        <v>291</v>
+      </c>
+      <c r="J16" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="K16" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="L16" s="47">
+        <f>COUNTIF(E16:H16,"참석")+COUNTIF(J16:K16,"참석")</f>
+        <v>3</v>
+      </c>
+      <c r="M16" s="47">
+        <f>COUNTIF(E16:H16,"참석")+COUNTIF(E16:H16,"불참")+COUNTIF(J16:K16,"참석")+COUNTIF(J16:K16,"불참")</f>
+        <v>6</v>
+      </c>
+      <c r="N16" s="49">
+        <f>IF(M16=0,"",L16/M16)</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="16.5">
+      <c r="A17" s="47">
+        <v>16</v>
+      </c>
+      <c r="B17" s="46" t="s">
+        <v>203</v>
+      </c>
+      <c r="C17" s="50" t="s">
+        <v>204</v>
+      </c>
+      <c r="D17" s="50" t="s">
+        <v>162</v>
+      </c>
+      <c r="E17" s="46" t="s">
+        <v>235</v>
+      </c>
+      <c r="F17" s="46" t="s">
+        <v>234</v>
+      </c>
+      <c r="G17" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="H17" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="I17" s="47"/>
+      <c r="J17" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="K17" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="L17" s="47">
+        <f>COUNTIF(E17:H17,"참석")+COUNTIF(J17:K17,"참석")</f>
+        <v>5</v>
+      </c>
+      <c r="M17" s="47">
+        <f>COUNTIF(E17:H17,"참석")+COUNTIF(E17:H17,"불참")+COUNTIF(J17:K17,"참석")+COUNTIF(J17:K17,"불참")</f>
+        <v>6</v>
+      </c>
+      <c r="N17" s="49">
+        <f>IF(M17=0,"",L17/M17)</f>
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="16.5">
+      <c r="A18" s="47">
+        <v>17</v>
+      </c>
+      <c r="B18" s="46" t="s">
+        <v>205</v>
+      </c>
+      <c r="C18" s="50" t="s">
+        <v>206</v>
+      </c>
+      <c r="D18" s="50" t="s">
+        <v>162</v>
+      </c>
+      <c r="E18" s="46" t="s">
+        <v>235</v>
+      </c>
+      <c r="F18" s="46" t="s">
+        <v>234</v>
+      </c>
+      <c r="G18" s="47" t="s">
+        <v>232</v>
+      </c>
+      <c r="H18" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="I18" s="47"/>
+      <c r="J18" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="K18" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="L18" s="47">
+        <f>COUNTIF(E18:H18,"참석")+COUNTIF(J18:K18,"참석")</f>
+        <v>2</v>
+      </c>
+      <c r="M18" s="47">
+        <f>COUNTIF(E18:H18,"참석")+COUNTIF(E18:H18,"불참")+COUNTIF(J18:K18,"참석")+COUNTIF(J18:K18,"불참")</f>
+        <v>6</v>
+      </c>
+      <c r="N18" s="49">
+        <f>IF(M18=0,"",L18/M18)</f>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="16.5">
+      <c r="A19" s="47">
+        <v>18</v>
+      </c>
+      <c r="B19" s="46" t="s">
+        <v>251</v>
+      </c>
+      <c r="C19" s="50" t="s">
+        <v>236</v>
+      </c>
+      <c r="D19" s="50" t="s">
+        <v>252</v>
+      </c>
+      <c r="E19" s="46" t="s">
+        <v>237</v>
+      </c>
+      <c r="F19" s="46" t="s">
+        <v>237</v>
+      </c>
+      <c r="G19" s="47" t="s">
+        <v>237</v>
+      </c>
+      <c r="H19" s="47" t="s">
+        <v>253</v>
+      </c>
+      <c r="I19" s="47"/>
+      <c r="J19" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="K19" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="L19" s="47">
+        <f>COUNTIF(E19:H19,"참석")+COUNTIF(J19:K19,"참석")</f>
+        <v>3</v>
+      </c>
+      <c r="M19" s="47">
+        <f>COUNTIF(E19:H19,"참석")+COUNTIF(E19:H19,"불참")+COUNTIF(J19:K19,"참석")+COUNTIF(J19:K19,"불참")</f>
+        <v>3</v>
+      </c>
+      <c r="N19" s="49">
+        <f>IF(M19=0,"",L19/M19)</f>
         <v>1</v>
       </c>
-      <c r="L2" s="49"/>
-    </row>
-    <row r="3" spans="1:12" ht="16.5">
-      <c r="A3" s="48">
+      <c r="O19" s="46" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="16.5">
+      <c r="A20" s="47">
+        <v>19</v>
+      </c>
+      <c r="B20" s="46" t="s">
+        <v>207</v>
+      </c>
+      <c r="C20" s="50" t="s">
+        <v>208</v>
+      </c>
+      <c r="D20" s="50" t="s">
+        <v>209</v>
+      </c>
+      <c r="E20" s="46" t="s">
+        <v>235</v>
+      </c>
+      <c r="F20" s="46" t="s">
+        <v>234</v>
+      </c>
+      <c r="G20" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="H20" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="I20" s="47"/>
+      <c r="J20" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="K20" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="L20" s="47">
+        <f>COUNTIF(E20:H20,"참석")+COUNTIF(J20:K20,"참석")</f>
+        <v>5</v>
+      </c>
+      <c r="M20" s="47">
+        <f>COUNTIF(E20:H20,"참석")+COUNTIF(E20:H20,"불참")+COUNTIF(J20:K20,"참석")+COUNTIF(J20:K20,"불참")</f>
+        <v>6</v>
+      </c>
+      <c r="N20" s="49">
+        <f>IF(M20=0,"",L20/M20)</f>
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" ht="16.5">
+      <c r="A21" s="47">
+        <v>20</v>
+      </c>
+      <c r="B21" s="46" t="s">
+        <v>210</v>
+      </c>
+      <c r="C21" s="50" t="s">
+        <v>211</v>
+      </c>
+      <c r="D21" s="50" t="s">
+        <v>166</v>
+      </c>
+      <c r="E21" s="46" t="s">
+        <v>232</v>
+      </c>
+      <c r="F21" s="46" t="s">
+        <v>234</v>
+      </c>
+      <c r="G21" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="H21" s="47" t="s">
+        <v>253</v>
+      </c>
+      <c r="I21" s="47"/>
+      <c r="J21" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="K21" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="L21" s="47">
+        <f>COUNTIF(E21:H21,"참석")+COUNTIF(J21:K21,"참석")</f>
+        <v>5</v>
+      </c>
+      <c r="M21" s="47">
+        <f>COUNTIF(E21:H21,"참석")+COUNTIF(E21:H21,"불참")+COUNTIF(J21:K21,"참석")+COUNTIF(J21:K21,"불참")</f>
+        <v>6</v>
+      </c>
+      <c r="N21" s="49">
+        <f>IF(M21=0,"",L21/M21)</f>
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" ht="16.5">
+      <c r="A22" s="47">
+        <v>21</v>
+      </c>
+      <c r="B22" s="46" t="s">
+        <v>212</v>
+      </c>
+      <c r="C22" s="50" t="s">
+        <v>213</v>
+      </c>
+      <c r="D22" s="50" t="s">
+        <v>169</v>
+      </c>
+      <c r="E22" s="46" t="s">
+        <v>235</v>
+      </c>
+      <c r="F22" s="46" t="s">
+        <v>232</v>
+      </c>
+      <c r="G22" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="H22" s="47" t="s">
+        <v>253</v>
+      </c>
+      <c r="I22" s="47"/>
+      <c r="J22" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="K22" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="L22" s="47">
+        <f>COUNTIF(E22:H22,"참석")+COUNTIF(J22:K22,"참석")</f>
+        <v>3</v>
+      </c>
+      <c r="M22" s="47">
+        <f>COUNTIF(E22:H22,"참석")+COUNTIF(E22:H22,"불참")+COUNTIF(J22:K22,"참석")+COUNTIF(J22:K22,"불참")</f>
+        <v>6</v>
+      </c>
+      <c r="N22" s="49">
+        <f>IF(M22=0,"",L22/M22)</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" ht="16.5">
+      <c r="A23" s="47">
+        <v>22</v>
+      </c>
+      <c r="B23" s="46" t="s">
+        <v>214</v>
+      </c>
+      <c r="C23" s="50" t="s">
+        <v>215</v>
+      </c>
+      <c r="D23" s="50" t="s">
+        <v>216</v>
+      </c>
+      <c r="E23" s="46" t="s">
+        <v>235</v>
+      </c>
+      <c r="F23" s="46" t="s">
+        <v>234</v>
+      </c>
+      <c r="G23" s="47" t="s">
+        <v>232</v>
+      </c>
+      <c r="H23" s="47" t="s">
+        <v>253</v>
+      </c>
+      <c r="I23" s="47"/>
+      <c r="J23" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="K23" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="L23" s="47">
+        <f>COUNTIF(E23:H23,"참석")+COUNTIF(J23:K23,"참석")</f>
+        <v>4</v>
+      </c>
+      <c r="M23" s="47">
+        <f>COUNTIF(E23:H23,"참석")+COUNTIF(E23:H23,"불참")+COUNTIF(J23:K23,"참석")+COUNTIF(J23:K23,"불참")</f>
+        <v>6</v>
+      </c>
+      <c r="N23" s="49">
+        <f>IF(M23=0,"",L23/M23)</f>
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" ht="16.5">
+      <c r="A24" s="47">
+        <v>23</v>
+      </c>
+      <c r="B24" s="46" t="s">
+        <v>217</v>
+      </c>
+      <c r="C24" s="50" t="s">
+        <v>218</v>
+      </c>
+      <c r="D24" s="50" t="s">
+        <v>190</v>
+      </c>
+      <c r="E24" s="46" t="s">
+        <v>232</v>
+      </c>
+      <c r="F24" s="46" t="s">
+        <v>232</v>
+      </c>
+      <c r="G24" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="H24" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="I24" s="47" t="s">
+        <v>291</v>
+      </c>
+      <c r="J24" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="K24" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="L24" s="47">
+        <f>COUNTIF(E24:H24,"참석")+COUNTIF(J24:K24,"참석")</f>
         <v>2</v>
       </c>
-      <c r="B3" s="49" t="s">
-        <v>197</v>
-      </c>
-      <c r="C3" s="48" t="s">
-        <v>163</v>
-      </c>
-      <c r="D3" s="48" t="s">
-        <v>162</v>
-      </c>
-      <c r="E3" s="48" t="s">
-        <v>234</v>
-      </c>
-      <c r="F3" s="48" t="s">
-        <v>234</v>
-      </c>
-      <c r="G3" s="48" t="s">
-        <v>234</v>
-      </c>
-      <c r="H3" s="48" t="s">
+      <c r="M24" s="47">
+        <f>COUNTIF(E24:H24,"참석")+COUNTIF(E24:H24,"불참")+COUNTIF(J24:K24,"참석")+COUNTIF(J24:K24,"불참")</f>
+        <v>6</v>
+      </c>
+      <c r="N24" s="49">
+        <f>IF(M24=0,"",L24/M24)</f>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" ht="16.5">
+      <c r="A25" s="47">
+        <v>24</v>
+      </c>
+      <c r="B25" s="46" t="s">
+        <v>219</v>
+      </c>
+      <c r="C25" s="50" t="s">
+        <v>220</v>
+      </c>
+      <c r="D25" s="50" t="s">
+        <v>196</v>
+      </c>
+      <c r="E25" s="46" t="s">
+        <v>235</v>
+      </c>
+      <c r="F25" s="46" t="s">
+        <v>234</v>
+      </c>
+      <c r="G25" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="H25" s="47" t="s">
         <v>253</v>
       </c>
-      <c r="I3" s="48">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="J3" s="48">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="K3" s="50">
-        <f t="shared" si="2"/>
+      <c r="I25" s="47"/>
+      <c r="J25" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="K25" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="L25" s="47">
+        <f>COUNTIF(E25:H25,"참석")+COUNTIF(J25:K25,"참석")</f>
+        <v>6</v>
+      </c>
+      <c r="M25" s="47">
+        <f>COUNTIF(E25:H25,"참석")+COUNTIF(E25:H25,"불참")+COUNTIF(J25:K25,"참석")+COUNTIF(J25:K25,"불참")</f>
+        <v>6</v>
+      </c>
+      <c r="N25" s="49">
+        <f>IF(M25=0,"",L25/M25)</f>
         <v>1</v>
       </c>
-      <c r="L3" s="49"/>
-    </row>
-    <row r="4" spans="1:12" ht="16.5">
-      <c r="A4" s="48">
-        <v>3</v>
-      </c>
-      <c r="B4" s="49" t="s">
-        <v>164</v>
-      </c>
-      <c r="C4" s="48" t="s">
-        <v>165</v>
-      </c>
-      <c r="D4" s="48" t="s">
-        <v>166</v>
-      </c>
-      <c r="E4" s="48" t="s">
-        <v>234</v>
-      </c>
-      <c r="F4" s="48" t="s">
-        <v>234</v>
-      </c>
-      <c r="G4" s="48" t="s">
-        <v>234</v>
-      </c>
-      <c r="H4" s="48" t="s">
+    </row>
+    <row r="26" spans="1:15" ht="16.5">
+      <c r="A26" s="47">
+        <v>25</v>
+      </c>
+      <c r="B26" s="46" t="s">
+        <v>221</v>
+      </c>
+      <c r="C26" s="50" t="s">
+        <v>222</v>
+      </c>
+      <c r="D26" s="50" t="s">
+        <v>196</v>
+      </c>
+      <c r="E26" s="46" t="s">
+        <v>232</v>
+      </c>
+      <c r="F26" s="46" t="s">
+        <v>234</v>
+      </c>
+      <c r="G26" s="47" t="s">
+        <v>232</v>
+      </c>
+      <c r="H26" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="I26" s="47"/>
+      <c r="J26" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="K26" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="L26" s="47">
+        <f>COUNTIF(E26:H26,"참석")+COUNTIF(J26:K26,"참석")</f>
+        <v>1</v>
+      </c>
+      <c r="M26" s="47">
+        <f>COUNTIF(E26:H26,"참석")+COUNTIF(E26:H26,"불참")+COUNTIF(J26:K26,"참석")+COUNTIF(J26:K26,"불참")</f>
+        <v>6</v>
+      </c>
+      <c r="N26" s="49">
+        <f>IF(M26=0,"",L26/M26)</f>
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" ht="16.5">
+      <c r="A27" s="47">
+        <v>26</v>
+      </c>
+      <c r="B27" s="46" t="s">
+        <v>223</v>
+      </c>
+      <c r="C27" s="50" t="s">
+        <v>224</v>
+      </c>
+      <c r="D27" s="50" t="s">
+        <v>200</v>
+      </c>
+      <c r="E27" s="46" t="s">
+        <v>235</v>
+      </c>
+      <c r="F27" s="46" t="s">
+        <v>234</v>
+      </c>
+      <c r="G27" s="47" t="s">
+        <v>232</v>
+      </c>
+      <c r="H27" s="47" t="s">
         <v>253</v>
       </c>
-      <c r="I4" s="48">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="J4" s="48">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="K4" s="50">
-        <f t="shared" si="2"/>
+      <c r="I27" s="47"/>
+      <c r="J27" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="K27" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="L27" s="47">
+        <f>COUNTIF(E27:H27,"참석")+COUNTIF(J27:K27,"참석")</f>
+        <v>5</v>
+      </c>
+      <c r="M27" s="47">
+        <f>COUNTIF(E27:H27,"참석")+COUNTIF(E27:H27,"불참")+COUNTIF(J27:K27,"참석")+COUNTIF(J27:K27,"불참")</f>
+        <v>6</v>
+      </c>
+      <c r="N27" s="49">
+        <f>IF(M27=0,"",L27/M27)</f>
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" ht="16.5">
+      <c r="A28" s="47">
+        <v>27</v>
+      </c>
+      <c r="B28" s="46" t="s">
+        <v>225</v>
+      </c>
+      <c r="C28" s="50" t="s">
+        <v>226</v>
+      </c>
+      <c r="D28" s="50" t="s">
+        <v>181</v>
+      </c>
+      <c r="E28" s="46" t="s">
+        <v>235</v>
+      </c>
+      <c r="F28" s="46" t="s">
+        <v>234</v>
+      </c>
+      <c r="G28" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="H28" s="47" t="s">
+        <v>253</v>
+      </c>
+      <c r="I28" s="47"/>
+      <c r="J28" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="K28" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="L28" s="47">
+        <f>COUNTIF(E28:H28,"참석")+COUNTIF(J28:K28,"참석")</f>
+        <v>6</v>
+      </c>
+      <c r="M28" s="47">
+        <f>COUNTIF(E28:H28,"참석")+COUNTIF(E28:H28,"불참")+COUNTIF(J28:K28,"참석")+COUNTIF(J28:K28,"불참")</f>
+        <v>6</v>
+      </c>
+      <c r="N28" s="49">
+        <f>IF(M28=0,"",L28/M28)</f>
         <v>1</v>
       </c>
-      <c r="L4" s="49"/>
-    </row>
-    <row r="5" spans="1:12" ht="16.5">
-      <c r="A5" s="48">
-        <v>4</v>
-      </c>
-      <c r="B5" s="49" t="s">
-        <v>167</v>
-      </c>
-      <c r="C5" s="48" t="s">
-        <v>168</v>
-      </c>
-      <c r="D5" s="48" t="s">
-        <v>169</v>
-      </c>
-      <c r="E5" s="48" t="s">
-        <v>234</v>
-      </c>
-      <c r="F5" s="48" t="s">
-        <v>234</v>
-      </c>
-      <c r="G5" s="48" t="s">
-        <v>234</v>
-      </c>
-      <c r="H5" s="48" t="s">
+    </row>
+    <row r="29" spans="1:15" ht="16.5">
+      <c r="A29" s="47">
+        <v>28</v>
+      </c>
+      <c r="B29" s="46" t="s">
+        <v>227</v>
+      </c>
+      <c r="C29" s="50" t="s">
+        <v>228</v>
+      </c>
+      <c r="D29" s="50" t="s">
+        <v>229</v>
+      </c>
+      <c r="E29" s="46" t="s">
+        <v>235</v>
+      </c>
+      <c r="F29" s="46" t="s">
+        <v>232</v>
+      </c>
+      <c r="G29" s="47" t="s">
+        <v>232</v>
+      </c>
+      <c r="H29" s="47" t="s">
         <v>253</v>
       </c>
-      <c r="I5" s="48">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="J5" s="48">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="K5" s="50">
-        <f t="shared" si="2"/>
+      <c r="I29" s="47"/>
+      <c r="J29" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="K29" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="L29" s="47">
+        <f>COUNTIF(E29:H29,"참석")+COUNTIF(J29:K29,"참석")</f>
+        <v>2</v>
+      </c>
+      <c r="M29" s="47">
+        <f>COUNTIF(E29:H29,"참석")+COUNTIF(E29:H29,"불참")+COUNTIF(J29:K29,"참석")+COUNTIF(J29:K29,"불참")</f>
+        <v>6</v>
+      </c>
+      <c r="N29" s="49">
+        <f>IF(M29=0,"",L29/M29)</f>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" ht="16.5">
+      <c r="A30" s="47">
+        <v>29</v>
+      </c>
+      <c r="C30" s="50" t="s">
+        <v>230</v>
+      </c>
+      <c r="D30" s="50" t="s">
+        <v>231</v>
+      </c>
+      <c r="E30" s="46" t="s">
+        <v>234</v>
+      </c>
+      <c r="F30" s="46" t="s">
+        <v>232</v>
+      </c>
+      <c r="G30" s="47" t="s">
+        <v>232</v>
+      </c>
+      <c r="H30" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="I30" s="47"/>
+      <c r="J30" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="K30" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="L30" s="47">
+        <f>COUNTIF(E30:H30,"참석")+COUNTIF(J30:K30,"참석")</f>
         <v>1</v>
       </c>
-      <c r="L5" s="49"/>
-    </row>
-    <row r="6" spans="1:12" ht="16.5">
-      <c r="A6" s="48">
-        <v>5</v>
-      </c>
-      <c r="B6" s="49" t="s">
-        <v>170</v>
-      </c>
-      <c r="C6" s="48" t="s">
-        <v>171</v>
-      </c>
-      <c r="D6" s="48" t="s">
-        <v>172</v>
-      </c>
-      <c r="E6" s="48" t="s">
-        <v>234</v>
-      </c>
-      <c r="F6" s="48" t="s">
-        <v>173</v>
-      </c>
-      <c r="G6" s="48" t="s">
-        <v>234</v>
-      </c>
-      <c r="H6" s="48" t="s">
-        <v>253</v>
-      </c>
-      <c r="I6" s="48">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="J6" s="48">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="K6" s="50">
-        <f t="shared" si="2"/>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="L6" s="49"/>
-    </row>
-    <row r="7" spans="1:12" ht="16.5">
-      <c r="A7" s="48">
+      <c r="M30" s="47">
+        <f>COUNTIF(E30:H30,"참석")+COUNTIF(E30:H30,"불참")+COUNTIF(J30:K30,"참석")+COUNTIF(J30:K30,"불참")</f>
         <v>6</v>
       </c>
-      <c r="B7" s="49" t="s">
-        <v>174</v>
-      </c>
-      <c r="C7" s="48" t="s">
-        <v>175</v>
-      </c>
-      <c r="D7" s="48" t="s">
-        <v>176</v>
-      </c>
-      <c r="E7" s="48" t="s">
-        <v>234</v>
-      </c>
-      <c r="F7" s="48" t="s">
-        <v>234</v>
-      </c>
-      <c r="G7" s="48" t="s">
-        <v>234</v>
-      </c>
-      <c r="H7" s="48" t="s">
-        <v>253</v>
-      </c>
-      <c r="I7" s="48">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="J7" s="48">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="K7" s="50">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="L7" s="49"/>
-    </row>
-    <row r="8" spans="1:12" ht="16.5">
-      <c r="A8" s="48">
-        <v>7</v>
-      </c>
-      <c r="B8" s="49" t="s">
-        <v>177</v>
-      </c>
-      <c r="C8" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="D8" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="E8" s="48" t="s">
-        <v>173</v>
-      </c>
-      <c r="F8" s="48" t="s">
-        <v>234</v>
-      </c>
-      <c r="G8" s="48" t="s">
-        <v>173</v>
-      </c>
-      <c r="H8" s="48" t="s">
-        <v>253</v>
-      </c>
-      <c r="I8" s="48">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J8" s="48">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="K8" s="50">
-        <f t="shared" si="2"/>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="L8" s="49"/>
-    </row>
-    <row r="9" spans="1:12" ht="16.5">
-      <c r="A9" s="48">
-        <v>8</v>
-      </c>
-      <c r="B9" s="49" t="s">
-        <v>198</v>
-      </c>
-      <c r="C9" s="48" t="s">
-        <v>199</v>
-      </c>
-      <c r="D9" s="48" t="s">
-        <v>200</v>
-      </c>
-      <c r="E9" s="48" t="s">
-        <v>233</v>
-      </c>
-      <c r="F9" s="48" t="s">
-        <v>233</v>
-      </c>
-      <c r="G9" s="48" t="s">
-        <v>234</v>
-      </c>
-      <c r="H9" s="48" t="s">
-        <v>173</v>
-      </c>
-      <c r="I9" s="48">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J9" s="48">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="K9" s="50">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="L9" s="49" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="16.5">
-      <c r="A10" s="48">
-        <v>9</v>
-      </c>
-      <c r="B10" s="49" t="s">
-        <v>201</v>
-      </c>
-      <c r="C10" s="48" t="s">
-        <v>180</v>
-      </c>
-      <c r="D10" s="48" t="s">
-        <v>181</v>
-      </c>
-      <c r="E10" s="48" t="s">
-        <v>234</v>
-      </c>
-      <c r="F10" s="48" t="s">
-        <v>232</v>
-      </c>
-      <c r="G10" s="48" t="s">
-        <v>234</v>
-      </c>
-      <c r="H10" s="48" t="s">
-        <v>253</v>
-      </c>
-      <c r="I10" s="48">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="J10" s="48">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="K10" s="50">
-        <f t="shared" si="2"/>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="L10" s="49"/>
-    </row>
-    <row r="11" spans="1:12" ht="16.5">
-      <c r="A11" s="48">
-        <v>10</v>
-      </c>
-      <c r="B11" s="49" t="s">
-        <v>182</v>
-      </c>
-      <c r="C11" s="48" t="s">
-        <v>183</v>
-      </c>
-      <c r="D11" s="48" t="s">
-        <v>184</v>
-      </c>
-      <c r="E11" s="48" t="s">
-        <v>234</v>
-      </c>
-      <c r="F11" s="48" t="s">
-        <v>234</v>
-      </c>
-      <c r="G11" s="48" t="s">
-        <v>234</v>
-      </c>
-      <c r="H11" s="48" t="s">
-        <v>173</v>
-      </c>
-      <c r="I11" s="48">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="J11" s="48">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="K11" s="50">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="L11" s="49"/>
-    </row>
-    <row r="12" spans="1:12" ht="16.5">
-      <c r="A12" s="48">
-        <v>11</v>
-      </c>
-      <c r="B12" s="49" t="s">
-        <v>185</v>
-      </c>
-      <c r="C12" s="48" t="s">
-        <v>186</v>
-      </c>
-      <c r="D12" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="E12" s="48" t="s">
-        <v>234</v>
-      </c>
-      <c r="F12" s="48" t="s">
-        <v>234</v>
-      </c>
-      <c r="G12" s="48" t="s">
-        <v>234</v>
-      </c>
-      <c r="H12" s="48" t="s">
-        <v>253</v>
-      </c>
-      <c r="I12" s="48">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="J12" s="48">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="K12" s="50">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="L12" s="49"/>
-    </row>
-    <row r="13" spans="1:12" ht="16.5">
-      <c r="A13" s="48">
-        <v>12</v>
-      </c>
-      <c r="B13" s="49" t="s">
-        <v>187</v>
-      </c>
-      <c r="C13" s="48" t="s">
-        <v>188</v>
-      </c>
-      <c r="D13" s="48" t="s">
-        <v>181</v>
-      </c>
-      <c r="E13" s="48" t="s">
-        <v>173</v>
-      </c>
-      <c r="F13" s="48" t="s">
-        <v>234</v>
-      </c>
-      <c r="G13" s="48" t="s">
-        <v>234</v>
-      </c>
-      <c r="H13" s="48" t="s">
-        <v>173</v>
-      </c>
-      <c r="I13" s="48">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="J13" s="48">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="K13" s="50">
-        <f t="shared" si="2"/>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="L13" s="49"/>
-    </row>
-    <row r="14" spans="1:12" ht="16.5">
-      <c r="A14" s="48">
-        <v>13</v>
-      </c>
-      <c r="B14" s="49" t="s">
-        <v>202</v>
-      </c>
-      <c r="C14" s="48" t="s">
-        <v>189</v>
-      </c>
-      <c r="D14" s="48" t="s">
-        <v>190</v>
-      </c>
-      <c r="E14" s="48" t="s">
-        <v>232</v>
-      </c>
-      <c r="F14" s="48" t="s">
-        <v>234</v>
-      </c>
-      <c r="G14" s="48" t="s">
-        <v>234</v>
-      </c>
-      <c r="H14" s="48" t="s">
-        <v>173</v>
-      </c>
-      <c r="I14" s="48">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="J14" s="48">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="K14" s="50">
-        <f t="shared" si="2"/>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="L14" s="49"/>
-    </row>
-    <row r="15" spans="1:12" ht="16.5">
-      <c r="A15" s="48">
-        <v>14</v>
-      </c>
-      <c r="B15" s="49" t="s">
-        <v>191</v>
-      </c>
-      <c r="C15" s="48" t="s">
-        <v>192</v>
-      </c>
-      <c r="D15" s="48" t="s">
-        <v>193</v>
-      </c>
-      <c r="E15" s="48" t="s">
-        <v>235</v>
-      </c>
-      <c r="F15" s="48" t="s">
-        <v>234</v>
-      </c>
-      <c r="G15" s="48" t="s">
-        <v>232</v>
-      </c>
-      <c r="H15" s="48" t="s">
-        <v>253</v>
-      </c>
-      <c r="I15" s="48">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="J15" s="48">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="K15" s="50">
-        <f t="shared" si="2"/>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="L15" s="49"/>
-    </row>
-    <row r="16" spans="1:12" ht="16.5">
-      <c r="A16" s="48">
-        <v>15</v>
-      </c>
-      <c r="B16" s="47" t="s">
-        <v>194</v>
-      </c>
-      <c r="C16" s="51" t="s">
-        <v>195</v>
-      </c>
-      <c r="D16" s="51" t="s">
-        <v>196</v>
-      </c>
-      <c r="E16" s="47" t="s">
-        <v>232</v>
-      </c>
-      <c r="F16" s="47" t="s">
-        <v>234</v>
-      </c>
-      <c r="G16" s="48" t="s">
-        <v>232</v>
-      </c>
-      <c r="H16" s="48" t="s">
-        <v>253</v>
-      </c>
-      <c r="I16" s="48">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J16" s="48">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="K16" s="50">
-        <f t="shared" si="2"/>
-        <v>0.33333333333333331</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="16.5">
-      <c r="A17" s="48">
-        <v>16</v>
-      </c>
-      <c r="B17" s="47" t="s">
-        <v>203</v>
-      </c>
-      <c r="C17" s="51" t="s">
-        <v>204</v>
-      </c>
-      <c r="D17" s="51" t="s">
-        <v>162</v>
-      </c>
-      <c r="E17" s="47" t="s">
-        <v>235</v>
-      </c>
-      <c r="F17" s="47" t="s">
-        <v>234</v>
-      </c>
-      <c r="G17" s="48" t="s">
-        <v>234</v>
-      </c>
-      <c r="H17" s="48" t="s">
-        <v>173</v>
-      </c>
-      <c r="I17" s="48">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="J17" s="48">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="K17" s="50">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" ht="16.5">
-      <c r="A18" s="48">
-        <v>17</v>
-      </c>
-      <c r="B18" s="47" t="s">
-        <v>205</v>
-      </c>
-      <c r="C18" s="51" t="s">
-        <v>206</v>
-      </c>
-      <c r="D18" s="51" t="s">
-        <v>162</v>
-      </c>
-      <c r="E18" s="47" t="s">
-        <v>235</v>
-      </c>
-      <c r="F18" s="47" t="s">
-        <v>234</v>
-      </c>
-      <c r="G18" s="48" t="s">
-        <v>232</v>
-      </c>
-      <c r="H18" s="48" t="s">
-        <v>173</v>
-      </c>
-      <c r="I18" s="48">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="J18" s="48">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="K18" s="50">
-        <f t="shared" si="2"/>
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="16.5">
-      <c r="A19" s="48">
-        <v>18</v>
-      </c>
-      <c r="B19" s="47" t="s">
-        <v>251</v>
-      </c>
-      <c r="C19" s="51" t="s">
-        <v>236</v>
-      </c>
-      <c r="D19" s="51" t="s">
-        <v>252</v>
-      </c>
-      <c r="E19" s="47" t="s">
-        <v>237</v>
-      </c>
-      <c r="F19" s="47" t="s">
-        <v>237</v>
-      </c>
-      <c r="G19" s="48" t="s">
-        <v>237</v>
-      </c>
-      <c r="H19" s="48" t="s">
-        <v>253</v>
-      </c>
-      <c r="I19" s="48">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J19" s="48">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K19" s="50" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L19" s="47" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="16.5">
-      <c r="A20" s="48">
-        <v>19</v>
-      </c>
-      <c r="B20" s="47" t="s">
-        <v>207</v>
-      </c>
-      <c r="C20" s="51" t="s">
-        <v>208</v>
-      </c>
-      <c r="D20" s="51" t="s">
-        <v>209</v>
-      </c>
-      <c r="E20" s="47" t="s">
-        <v>235</v>
-      </c>
-      <c r="F20" s="47" t="s">
-        <v>234</v>
-      </c>
-      <c r="G20" s="48" t="s">
-        <v>234</v>
-      </c>
-      <c r="H20" s="48" t="s">
-        <v>173</v>
-      </c>
-      <c r="I20" s="48">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="J20" s="48">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="K20" s="50">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="16.5">
-      <c r="A21" s="48">
-        <v>20</v>
-      </c>
-      <c r="B21" s="47" t="s">
-        <v>210</v>
-      </c>
-      <c r="C21" s="51" t="s">
-        <v>211</v>
-      </c>
-      <c r="D21" s="51" t="s">
-        <v>166</v>
-      </c>
-      <c r="E21" s="47" t="s">
-        <v>232</v>
-      </c>
-      <c r="F21" s="47" t="s">
-        <v>234</v>
-      </c>
-      <c r="G21" s="48" t="s">
-        <v>234</v>
-      </c>
-      <c r="H21" s="48" t="s">
-        <v>253</v>
-      </c>
-      <c r="I21" s="48">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="J21" s="48">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="K21" s="50">
-        <f t="shared" si="2"/>
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="16.5">
-      <c r="A22" s="48">
-        <v>21</v>
-      </c>
-      <c r="B22" s="47" t="s">
-        <v>212</v>
-      </c>
-      <c r="C22" s="51" t="s">
-        <v>213</v>
-      </c>
-      <c r="D22" s="51" t="s">
-        <v>169</v>
-      </c>
-      <c r="E22" s="47" t="s">
-        <v>235</v>
-      </c>
-      <c r="F22" s="47" t="s">
-        <v>232</v>
-      </c>
-      <c r="G22" s="48" t="s">
-        <v>234</v>
-      </c>
-      <c r="H22" s="48" t="s">
-        <v>253</v>
-      </c>
-      <c r="I22" s="48">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="J22" s="48">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="K22" s="50">
-        <f t="shared" si="2"/>
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="16.5">
-      <c r="A23" s="48">
-        <v>22</v>
-      </c>
-      <c r="B23" s="47" t="s">
-        <v>214</v>
-      </c>
-      <c r="C23" s="51" t="s">
-        <v>215</v>
-      </c>
-      <c r="D23" s="51" t="s">
-        <v>216</v>
-      </c>
-      <c r="E23" s="47" t="s">
-        <v>235</v>
-      </c>
-      <c r="F23" s="47" t="s">
-        <v>234</v>
-      </c>
-      <c r="G23" s="48" t="s">
-        <v>232</v>
-      </c>
-      <c r="H23" s="48" t="s">
-        <v>253</v>
-      </c>
-      <c r="I23" s="48">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="J23" s="48">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="K23" s="50">
-        <f t="shared" si="2"/>
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" ht="16.5">
-      <c r="A24" s="48">
-        <v>23</v>
-      </c>
-      <c r="B24" s="47" t="s">
-        <v>217</v>
-      </c>
-      <c r="C24" s="51" t="s">
-        <v>218</v>
-      </c>
-      <c r="D24" s="51" t="s">
-        <v>190</v>
-      </c>
-      <c r="E24" s="47" t="s">
-        <v>232</v>
-      </c>
-      <c r="F24" s="47" t="s">
-        <v>232</v>
-      </c>
-      <c r="G24" s="48" t="s">
-        <v>234</v>
-      </c>
-      <c r="H24" s="48" t="s">
-        <v>173</v>
-      </c>
-      <c r="I24" s="48">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J24" s="48">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="K24" s="50">
-        <f t="shared" si="2"/>
-        <v>0.33333333333333331</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" ht="16.5">
-      <c r="A25" s="48">
-        <v>24</v>
-      </c>
-      <c r="B25" s="47" t="s">
-        <v>219</v>
-      </c>
-      <c r="C25" s="51" t="s">
-        <v>220</v>
-      </c>
-      <c r="D25" s="51" t="s">
-        <v>196</v>
-      </c>
-      <c r="E25" s="47" t="s">
-        <v>235</v>
-      </c>
-      <c r="F25" s="47" t="s">
-        <v>234</v>
-      </c>
-      <c r="G25" s="48" t="s">
-        <v>234</v>
-      </c>
-      <c r="H25" s="48" t="s">
-        <v>253</v>
-      </c>
-      <c r="I25" s="48">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="J25" s="48">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="K25" s="50">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" ht="16.5">
-      <c r="A26" s="48">
-        <v>25</v>
-      </c>
-      <c r="B26" s="47" t="s">
-        <v>221</v>
-      </c>
-      <c r="C26" s="51" t="s">
-        <v>222</v>
-      </c>
-      <c r="D26" s="51" t="s">
-        <v>196</v>
-      </c>
-      <c r="E26" s="47" t="s">
-        <v>232</v>
-      </c>
-      <c r="F26" s="47" t="s">
-        <v>234</v>
-      </c>
-      <c r="G26" s="48" t="s">
-        <v>232</v>
-      </c>
-      <c r="H26" s="48" t="s">
-        <v>173</v>
-      </c>
-      <c r="I26" s="48">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J26" s="48">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="K26" s="50">
-        <f t="shared" si="2"/>
-        <v>0.33333333333333331</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" ht="16.5">
-      <c r="A27" s="48">
-        <v>26</v>
-      </c>
-      <c r="B27" s="47" t="s">
-        <v>223</v>
-      </c>
-      <c r="C27" s="51" t="s">
-        <v>224</v>
-      </c>
-      <c r="D27" s="51" t="s">
-        <v>200</v>
-      </c>
-      <c r="E27" s="47" t="s">
-        <v>235</v>
-      </c>
-      <c r="F27" s="47" t="s">
-        <v>234</v>
-      </c>
-      <c r="G27" s="48" t="s">
-        <v>232</v>
-      </c>
-      <c r="H27" s="48" t="s">
-        <v>253</v>
-      </c>
-      <c r="I27" s="48">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="J27" s="48">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="K27" s="50">
-        <f t="shared" si="2"/>
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" ht="16.5">
-      <c r="A28" s="48">
-        <v>27</v>
-      </c>
-      <c r="B28" s="47" t="s">
-        <v>225</v>
-      </c>
-      <c r="C28" s="51" t="s">
-        <v>226</v>
-      </c>
-      <c r="D28" s="51" t="s">
-        <v>181</v>
-      </c>
-      <c r="E28" s="47" t="s">
-        <v>235</v>
-      </c>
-      <c r="F28" s="47" t="s">
-        <v>234</v>
-      </c>
-      <c r="G28" s="48" t="s">
-        <v>234</v>
-      </c>
-      <c r="H28" s="48" t="s">
-        <v>253</v>
-      </c>
-      <c r="I28" s="48">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="J28" s="48">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="K28" s="50">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" ht="16.5">
-      <c r="A29" s="48">
-        <v>28</v>
-      </c>
-      <c r="B29" s="47" t="s">
-        <v>227</v>
-      </c>
-      <c r="C29" s="51" t="s">
-        <v>228</v>
-      </c>
-      <c r="D29" s="51" t="s">
-        <v>229</v>
-      </c>
-      <c r="E29" s="47" t="s">
-        <v>235</v>
-      </c>
-      <c r="F29" s="47" t="s">
-        <v>232</v>
-      </c>
-      <c r="G29" s="48" t="s">
-        <v>232</v>
-      </c>
-      <c r="H29" s="48" t="s">
-        <v>253</v>
-      </c>
-      <c r="I29" s="48">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J29" s="48">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="K29" s="50">
-        <f t="shared" si="2"/>
-        <v>0.33333333333333331</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" ht="16.5">
-      <c r="A30" s="48">
-        <v>29</v>
-      </c>
-      <c r="C30" s="51" t="s">
-        <v>230</v>
-      </c>
-      <c r="D30" s="51" t="s">
-        <v>231</v>
-      </c>
-      <c r="E30" s="47" t="s">
-        <v>234</v>
-      </c>
-      <c r="F30" s="47" t="s">
-        <v>232</v>
-      </c>
-      <c r="G30" s="48" t="s">
-        <v>232</v>
-      </c>
-      <c r="H30" s="48" t="s">
-        <v>173</v>
-      </c>
-      <c r="I30" s="48">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J30" s="48">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="K30" s="50">
-        <f t="shared" si="2"/>
-        <v>0.33333333333333331</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" ht="16.5">
-      <c r="E31" s="47">
+      <c r="N30" s="49">
+        <f>IF(M30=0,"",L30/M30)</f>
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" ht="16.5">
+      <c r="E31" s="46">
         <f>COUNTIF(E2:E29,"참석")</f>
         <v>19</v>
       </c>
-      <c r="F31" s="47">
+      <c r="F31" s="46">
         <f>COUNTIF(F2:F29,"참석")</f>
         <v>21</v>
       </c>
-      <c r="G31" s="47">
+      <c r="G31" s="46">
         <f>COUNTIF(G2:G29,"참석")</f>
         <v>19</v>
       </c>
-      <c r="K31" s="50" t="str">
-        <f t="shared" si="2"/>
+      <c r="N31" s="49" t="str">
+        <f t="shared" ref="N2:N31" si="0">IF(M31=0,"",L31/M31)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L31" xr:uid="{C0625D6E-2678-482C-88B1-4B31BC9434B5}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L31">
+  <autoFilter ref="A1:O31" xr:uid="{C0625D6E-2678-482C-88B1-4B31BC9434B5}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O31">
       <sortCondition ref="C1:C31"/>
     </sortState>
   </autoFilter>

--- a/4기차세대경영자과정/차경 4기 정산서.xlsx
+++ b/4기차세대경영자과정/차경 4기 정산서.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Innobiz\Documents\innobiz-nextgen\4기차세대경영자과정\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DA5450F-05A7-49C0-9A29-6461604080D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29E14D24-D74E-4034-BF7B-A67A8FEDED64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{404CE508-8F71-4CA4-99F0-0EFB79DB1227}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{404CE508-8F71-4CA4-99F0-0EFB79DB1227}"/>
   </bookViews>
   <sheets>
     <sheet name="항목별(피벗)" sheetId="9" r:id="rId1"/>
@@ -23,7 +23,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">실수입내역!$A$3:$C$46</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">지출세부내역서!$A$3:$G$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'회차별 출석현황'!$A$1:$O$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'회차별 출석현황'!$A$1:$P$31</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1517,7 +1517,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="306">
   <si>
     <t>번호</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -2575,6 +2575,48 @@
   </si>
   <si>
     <t>참가</t>
+  </si>
+  <si>
+    <t>강사비(고영)</t>
+  </si>
+  <si>
+    <t>강의비</t>
+  </si>
+  <si>
+    <t>고영</t>
+  </si>
+  <si>
+    <t>진행비(고영)</t>
+  </si>
+  <si>
+    <t>진행비</t>
+  </si>
+  <si>
+    <t>교재 인쇄(3권), 회원수첩</t>
+  </si>
+  <si>
+    <t>준비비</t>
+  </si>
+  <si>
+    <t>(주)행일미디어</t>
+  </si>
+  <si>
+    <t>다과비</t>
+  </si>
+  <si>
+    <t>세븐일레븐 판교이노밸리점</t>
+  </si>
+  <si>
+    <t>식비(끌리마)</t>
+  </si>
+  <si>
+    <t>식비</t>
+  </si>
+  <si>
+    <t>끌리마</t>
+  </si>
+  <si>
+    <t>8주(2026-06-25)</t>
   </si>
 </sst>
 </file>
@@ -2874,7 +2916,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3083,6 +3125,9 @@
     </xf>
     <xf numFmtId="42" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3875,11 +3920,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="26.25">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="72" t="s">
         <v>105</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
     </row>
     <row r="2" spans="1:4" ht="21.6" customHeight="1">
       <c r="A2" s="3" t="s">
@@ -4299,15 +4344,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="26.25">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="72" t="s">
         <v>241</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
     </row>
     <row r="2" spans="1:7" ht="11.25" customHeight="1">
       <c r="A2" s="51"/>
@@ -4840,12 +4885,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="26.25">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="72" t="s">
         <v>105</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
     </row>
     <row r="3" spans="1:5" s="24" customFormat="1" ht="40.5" customHeight="1">
       <c r="A3" s="4" t="s">
@@ -5066,7 +5111,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{959FEF70-8578-4918-8CDC-E1B4AA8967DB}">
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="7.125" customWidth="1"/>
@@ -5079,15 +5124,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="26.25">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="72" t="s">
         <v>105</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
     </row>
     <row r="2" spans="1:7">
       <c r="F2" s="2"/>
@@ -5976,6 +6021,121 @@
       </c>
       <c r="G40" s="69" t="s">
         <v>284</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41">
+        <v>38</v>
+      </c>
+      <c r="B41" s="71">
+        <v>1500000</v>
+      </c>
+      <c r="C41" s="35">
+        <v>46198</v>
+      </c>
+      <c r="D41" s="34" t="s">
+        <v>292</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="F41" s="34" t="s">
+        <v>294</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42">
+        <v>39</v>
+      </c>
+      <c r="B42" s="71">
+        <v>500000</v>
+      </c>
+      <c r="C42" s="35">
+        <v>46198</v>
+      </c>
+      <c r="D42" s="34" t="s">
+        <v>295</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="F42" s="34" t="s">
+        <v>294</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43">
+        <v>40</v>
+      </c>
+      <c r="B43" s="71">
+        <v>576400</v>
+      </c>
+      <c r="C43" s="35">
+        <v>46199</v>
+      </c>
+      <c r="D43" s="34" t="s">
+        <v>297</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="F43" s="34" t="s">
+        <v>299</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44">
+        <v>41</v>
+      </c>
+      <c r="B44" s="71">
+        <v>72700</v>
+      </c>
+      <c r="C44" s="35">
+        <v>46197</v>
+      </c>
+      <c r="D44" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="F44" s="34" t="s">
+        <v>301</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45">
+        <v>42</v>
+      </c>
+      <c r="B45" s="71">
+        <v>153000</v>
+      </c>
+      <c r="C45" s="35">
+        <v>46198</v>
+      </c>
+      <c r="D45" s="34" t="s">
+        <v>302</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="F45" s="34" t="s">
+        <v>304</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -6184,20 +6344,20 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0625D6E-2678-482C-88B1-4B31BC9434B5}">
-  <dimension ref="A1:O31"/>
+  <dimension ref="A1:P31"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="8" style="46" customWidth="1"/>
     <col min="2" max="2" width="34" style="46" customWidth="1"/>
     <col min="3" max="4" width="12" style="46" customWidth="1"/>
-    <col min="5" max="11" width="16" style="46" customWidth="1"/>
-    <col min="12" max="13" width="12" style="46" customWidth="1"/>
-    <col min="14" max="14" width="10" style="46" customWidth="1"/>
-    <col min="15" max="15" width="30" style="46" customWidth="1"/>
-    <col min="16" max="16384" width="9" style="46"/>
+    <col min="5" max="12" width="16" style="46" customWidth="1"/>
+    <col min="13" max="14" width="12" style="46" customWidth="1"/>
+    <col min="15" max="15" width="10" style="46" customWidth="1"/>
+    <col min="16" max="16" width="30" style="46" customWidth="1"/>
+    <col min="17" max="16384" width="9" style="46"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15">
+    <row r="1" spans="1:16" ht="15">
       <c r="A1" s="45" t="s">
         <v>149</v>
       </c>
@@ -6232,19 +6392,22 @@
         <v>290</v>
       </c>
       <c r="L1" s="45" t="s">
+        <v>305</v>
+      </c>
+      <c r="M1" s="45" t="s">
         <v>156</v>
       </c>
-      <c r="M1" s="45" t="s">
+      <c r="N1" s="45" t="s">
         <v>157</v>
       </c>
-      <c r="N1" s="45" t="s">
+      <c r="O1" s="45" t="s">
         <v>158</v>
       </c>
-      <c r="O1" s="45" t="s">
+      <c r="P1" s="45" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="16.5">
+    <row r="2" spans="1:16" ht="16.5">
       <c r="A2" s="47">
         <v>1</v>
       </c>
@@ -6278,21 +6441,24 @@
       <c r="K2" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="L2" s="47">
-        <f>COUNTIF(E2:H2,"참석")+COUNTIF(J2:K2,"참석")</f>
-        <v>6</v>
+      <c r="L2" s="47" t="s">
+        <v>234</v>
       </c>
       <c r="M2" s="47">
-        <f>COUNTIF(E2:H2,"참석")+COUNTIF(E2:H2,"불참")+COUNTIF(J2:K2,"참석")+COUNTIF(J2:K2,"불참")</f>
-        <v>6</v>
-      </c>
-      <c r="N2" s="49">
-        <f>IF(M2=0,"",L2/M2)</f>
+        <f>COUNTIF(E2:H2,"참석")+COUNTIF(J2:L2,"참석")</f>
+        <v>7</v>
+      </c>
+      <c r="N2" s="47">
+        <f>COUNTIF(E2:H2,"참석")+COUNTIF(E2:H2,"불참")+COUNTIF(J2:L2,"참석")+COUNTIF(J2:L2,"불참")</f>
+        <v>7</v>
+      </c>
+      <c r="O2" s="49">
+        <f>IF(N2=0,"",M2/N2)</f>
         <v>1</v>
       </c>
-      <c r="O2" s="48"/>
-    </row>
-    <row r="3" spans="1:15" ht="16.5">
+      <c r="P2" s="48"/>
+    </row>
+    <row r="3" spans="1:16" ht="16.5">
       <c r="A3" s="47">
         <v>2</v>
       </c>
@@ -6326,21 +6492,24 @@
       <c r="K3" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="L3" s="47">
-        <f>COUNTIF(E3:H3,"참석")+COUNTIF(J3:K3,"참석")</f>
-        <v>6</v>
+      <c r="L3" s="47" t="s">
+        <v>234</v>
       </c>
       <c r="M3" s="47">
-        <f>COUNTIF(E3:H3,"참석")+COUNTIF(E3:H3,"불참")+COUNTIF(J3:K3,"참석")+COUNTIF(J3:K3,"불참")</f>
-        <v>6</v>
-      </c>
-      <c r="N3" s="49">
-        <f>IF(M3=0,"",L3/M3)</f>
+        <f>COUNTIF(E3:H3,"참석")+COUNTIF(J3:L3,"참석")</f>
+        <v>7</v>
+      </c>
+      <c r="N3" s="47">
+        <f>COUNTIF(E3:H3,"참석")+COUNTIF(E3:H3,"불참")+COUNTIF(J3:L3,"참석")+COUNTIF(J3:L3,"불참")</f>
+        <v>7</v>
+      </c>
+      <c r="O3" s="49">
+        <f>IF(N3=0,"",M3/N3)</f>
         <v>1</v>
       </c>
-      <c r="O3" s="48"/>
-    </row>
-    <row r="4" spans="1:15" ht="16.5">
+      <c r="P3" s="48"/>
+    </row>
+    <row r="4" spans="1:16" ht="16.5">
       <c r="A4" s="47">
         <v>3</v>
       </c>
@@ -6374,21 +6543,24 @@
       <c r="K4" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="L4" s="47">
-        <f>COUNTIF(E4:H4,"참석")+COUNTIF(J4:K4,"참석")</f>
-        <v>6</v>
+      <c r="L4" s="47" t="s">
+        <v>234</v>
       </c>
       <c r="M4" s="47">
-        <f>COUNTIF(E4:H4,"참석")+COUNTIF(E4:H4,"불참")+COUNTIF(J4:K4,"참석")+COUNTIF(J4:K4,"불참")</f>
-        <v>6</v>
-      </c>
-      <c r="N4" s="49">
-        <f>IF(M4=0,"",L4/M4)</f>
+        <f>COUNTIF(E4:H4,"참석")+COUNTIF(J4:L4,"참석")</f>
+        <v>7</v>
+      </c>
+      <c r="N4" s="47">
+        <f>COUNTIF(E4:H4,"참석")+COUNTIF(E4:H4,"불참")+COUNTIF(J4:L4,"참석")+COUNTIF(J4:L4,"불참")</f>
+        <v>7</v>
+      </c>
+      <c r="O4" s="49">
+        <f>IF(N4=0,"",M4/N4)</f>
         <v>1</v>
       </c>
-      <c r="O4" s="48"/>
-    </row>
-    <row r="5" spans="1:15" ht="16.5">
+      <c r="P4" s="48"/>
+    </row>
+    <row r="5" spans="1:16" ht="16.5">
       <c r="A5" s="47">
         <v>4</v>
       </c>
@@ -6420,21 +6592,24 @@
       <c r="K5" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="L5" s="47">
-        <f>COUNTIF(E5:H5,"참석")+COUNTIF(J5:K5,"참석")</f>
-        <v>6</v>
+      <c r="L5" s="47" t="s">
+        <v>234</v>
       </c>
       <c r="M5" s="47">
-        <f>COUNTIF(E5:H5,"참석")+COUNTIF(E5:H5,"불참")+COUNTIF(J5:K5,"참석")+COUNTIF(J5:K5,"불참")</f>
-        <v>6</v>
-      </c>
-      <c r="N5" s="49">
-        <f>IF(M5=0,"",L5/M5)</f>
+        <f>COUNTIF(E5:H5,"참석")+COUNTIF(J5:L5,"참석")</f>
+        <v>7</v>
+      </c>
+      <c r="N5" s="47">
+        <f>COUNTIF(E5:H5,"참석")+COUNTIF(E5:H5,"불참")+COUNTIF(J5:L5,"참석")+COUNTIF(J5:L5,"불참")</f>
+        <v>7</v>
+      </c>
+      <c r="O5" s="49">
+        <f>IF(N5=0,"",M5/N5)</f>
         <v>1</v>
       </c>
-      <c r="O5" s="48"/>
-    </row>
-    <row r="6" spans="1:15" ht="16.5">
+      <c r="P5" s="48"/>
+    </row>
+    <row r="6" spans="1:16" ht="16.5">
       <c r="A6" s="47">
         <v>5</v>
       </c>
@@ -6468,21 +6643,24 @@
       <c r="K6" s="47" t="s">
         <v>173</v>
       </c>
-      <c r="L6" s="47">
-        <f>COUNTIF(E6:H6,"참석")+COUNTIF(J6:K6,"참석")</f>
-        <v>4</v>
+      <c r="L6" s="47" t="s">
+        <v>234</v>
       </c>
       <c r="M6" s="47">
-        <f>COUNTIF(E6:H6,"참석")+COUNTIF(E6:H6,"불참")+COUNTIF(J6:K6,"참석")+COUNTIF(J6:K6,"불참")</f>
-        <v>6</v>
-      </c>
-      <c r="N6" s="49">
-        <f>IF(M6=0,"",L6/M6)</f>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="O6" s="48"/>
-    </row>
-    <row r="7" spans="1:15" ht="16.5">
+        <f>COUNTIF(E6:H6,"참석")+COUNTIF(J6:L6,"참석")</f>
+        <v>5</v>
+      </c>
+      <c r="N6" s="47">
+        <f>COUNTIF(E6:H6,"참석")+COUNTIF(E6:H6,"불참")+COUNTIF(J6:L6,"참석")+COUNTIF(J6:L6,"불참")</f>
+        <v>7</v>
+      </c>
+      <c r="O6" s="49">
+        <f>IF(N6=0,"",M6/N6)</f>
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="P6" s="48"/>
+    </row>
+    <row r="7" spans="1:16" ht="16.5">
       <c r="A7" s="47">
         <v>6</v>
       </c>
@@ -6516,21 +6694,24 @@
       <c r="K7" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="L7" s="47">
-        <f>COUNTIF(E7:H7,"참석")+COUNTIF(J7:K7,"참석")</f>
-        <v>6</v>
+      <c r="L7" s="47" t="s">
+        <v>234</v>
       </c>
       <c r="M7" s="47">
-        <f>COUNTIF(E7:H7,"참석")+COUNTIF(E7:H7,"불참")+COUNTIF(J7:K7,"참석")+COUNTIF(J7:K7,"불참")</f>
-        <v>6</v>
-      </c>
-      <c r="N7" s="49">
-        <f>IF(M7=0,"",L7/M7)</f>
+        <f>COUNTIF(E7:H7,"참석")+COUNTIF(J7:L7,"참석")</f>
+        <v>7</v>
+      </c>
+      <c r="N7" s="47">
+        <f>COUNTIF(E7:H7,"참석")+COUNTIF(E7:H7,"불참")+COUNTIF(J7:L7,"참석")+COUNTIF(J7:L7,"불참")</f>
+        <v>7</v>
+      </c>
+      <c r="O7" s="49">
+        <f>IF(N7=0,"",M7/N7)</f>
         <v>1</v>
       </c>
-      <c r="O7" s="48"/>
-    </row>
-    <row r="8" spans="1:15" ht="16.5">
+      <c r="P7" s="48"/>
+    </row>
+    <row r="8" spans="1:16" ht="16.5">
       <c r="A8" s="47">
         <v>7</v>
       </c>
@@ -6562,21 +6743,24 @@
       <c r="K8" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="L8" s="47">
-        <f>COUNTIF(E8:H8,"참석")+COUNTIF(J8:K8,"참석")</f>
+      <c r="L8" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="M8" s="47">
+        <f>COUNTIF(E8:H8,"참석")+COUNTIF(J8:L8,"참석")</f>
         <v>3</v>
       </c>
-      <c r="M8" s="47">
-        <f>COUNTIF(E8:H8,"참석")+COUNTIF(E8:H8,"불참")+COUNTIF(J8:K8,"참석")+COUNTIF(J8:K8,"불참")</f>
-        <v>6</v>
-      </c>
-      <c r="N8" s="49">
-        <f>IF(M8=0,"",L8/M8)</f>
-        <v>0.5</v>
-      </c>
-      <c r="O8" s="48"/>
-    </row>
-    <row r="9" spans="1:15" ht="16.5">
+      <c r="N8" s="47">
+        <f>COUNTIF(E8:H8,"참석")+COUNTIF(E8:H8,"불참")+COUNTIF(J8:L8,"참석")+COUNTIF(J8:L8,"불참")</f>
+        <v>7</v>
+      </c>
+      <c r="O8" s="49">
+        <f>IF(N8=0,"",M8/N8)</f>
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="P8" s="48"/>
+    </row>
+    <row r="9" spans="1:16" ht="16.5">
       <c r="A9" s="47">
         <v>8</v>
       </c>
@@ -6610,23 +6794,26 @@
       <c r="K9" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="L9" s="47">
-        <f>COUNTIF(E9:H9,"참석")+COUNTIF(J9:K9,"참석")</f>
-        <v>3</v>
+      <c r="L9" s="47" t="s">
+        <v>234</v>
       </c>
       <c r="M9" s="47">
-        <f>COUNTIF(E9:H9,"참석")+COUNTIF(E9:H9,"불참")+COUNTIF(J9:K9,"참석")+COUNTIF(J9:K9,"불참")</f>
+        <f>COUNTIF(E9:H9,"참석")+COUNTIF(J9:L9,"참석")</f>
         <v>4</v>
       </c>
-      <c r="N9" s="49">
-        <f>IF(M9=0,"",L9/M9)</f>
-        <v>0.75</v>
-      </c>
-      <c r="O9" s="48" t="s">
+      <c r="N9" s="47">
+        <f>COUNTIF(E9:H9,"참석")+COUNTIF(E9:H9,"불참")+COUNTIF(J9:L9,"참석")+COUNTIF(J9:L9,"불참")</f>
+        <v>5</v>
+      </c>
+      <c r="O9" s="49">
+        <f>IF(N9=0,"",M9/N9)</f>
+        <v>0.8</v>
+      </c>
+      <c r="P9" s="48" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="16.5">
+    <row r="10" spans="1:16" ht="16.5">
       <c r="A10" s="47">
         <v>9</v>
       </c>
@@ -6658,21 +6845,24 @@
       <c r="K10" s="47" t="s">
         <v>173</v>
       </c>
-      <c r="L10" s="47">
-        <f>COUNTIF(E10:H10,"참석")+COUNTIF(J10:K10,"참석")</f>
-        <v>3</v>
+      <c r="L10" s="47" t="s">
+        <v>234</v>
       </c>
       <c r="M10" s="47">
-        <f>COUNTIF(E10:H10,"참석")+COUNTIF(E10:H10,"불참")+COUNTIF(J10:K10,"참석")+COUNTIF(J10:K10,"불참")</f>
-        <v>6</v>
-      </c>
-      <c r="N10" s="49">
-        <f>IF(M10=0,"",L10/M10)</f>
-        <v>0.5</v>
-      </c>
-      <c r="O10" s="48"/>
-    </row>
-    <row r="11" spans="1:15" ht="16.5">
+        <f>COUNTIF(E10:H10,"참석")+COUNTIF(J10:L10,"참석")</f>
+        <v>4</v>
+      </c>
+      <c r="N10" s="47">
+        <f>COUNTIF(E10:H10,"참석")+COUNTIF(E10:H10,"불참")+COUNTIF(J10:L10,"참석")+COUNTIF(J10:L10,"불참")</f>
+        <v>7</v>
+      </c>
+      <c r="O10" s="49">
+        <f>IF(N10=0,"",M10/N10)</f>
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="P10" s="48"/>
+    </row>
+    <row r="11" spans="1:16" ht="16.5">
       <c r="A11" s="47">
         <v>10</v>
       </c>
@@ -6704,21 +6894,24 @@
       <c r="K11" s="47" t="s">
         <v>173</v>
       </c>
-      <c r="L11" s="47">
-        <f>COUNTIF(E11:H11,"참석")+COUNTIF(J11:K11,"참석")</f>
+      <c r="L11" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="M11" s="47">
+        <f>COUNTIF(E11:H11,"참석")+COUNTIF(J11:L11,"참석")</f>
         <v>3</v>
       </c>
-      <c r="M11" s="47">
-        <f>COUNTIF(E11:H11,"참석")+COUNTIF(E11:H11,"불참")+COUNTIF(J11:K11,"참석")+COUNTIF(J11:K11,"불참")</f>
-        <v>6</v>
-      </c>
-      <c r="N11" s="49">
-        <f>IF(M11=0,"",L11/M11)</f>
-        <v>0.5</v>
-      </c>
-      <c r="O11" s="48"/>
-    </row>
-    <row r="12" spans="1:15" ht="16.5">
+      <c r="N11" s="47">
+        <f>COUNTIF(E11:H11,"참석")+COUNTIF(E11:H11,"불참")+COUNTIF(J11:L11,"참석")+COUNTIF(J11:L11,"불참")</f>
+        <v>7</v>
+      </c>
+      <c r="O11" s="49">
+        <f>IF(N11=0,"",M11/N11)</f>
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="P11" s="48"/>
+    </row>
+    <row r="12" spans="1:16" ht="16.5">
       <c r="A12" s="47">
         <v>11</v>
       </c>
@@ -6750,21 +6943,24 @@
       <c r="K12" s="47" t="s">
         <v>173</v>
       </c>
-      <c r="L12" s="47">
-        <f>COUNTIF(E12:H12,"참석")+COUNTIF(J12:K12,"참석")</f>
-        <v>4</v>
+      <c r="L12" s="47" t="s">
+        <v>234</v>
       </c>
       <c r="M12" s="47">
-        <f>COUNTIF(E12:H12,"참석")+COUNTIF(E12:H12,"불참")+COUNTIF(J12:K12,"참석")+COUNTIF(J12:K12,"불참")</f>
-        <v>6</v>
-      </c>
-      <c r="N12" s="49">
-        <f>IF(M12=0,"",L12/M12)</f>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="O12" s="48"/>
-    </row>
-    <row r="13" spans="1:15" ht="16.5">
+        <f>COUNTIF(E12:H12,"참석")+COUNTIF(J12:L12,"참석")</f>
+        <v>5</v>
+      </c>
+      <c r="N12" s="47">
+        <f>COUNTIF(E12:H12,"참석")+COUNTIF(E12:H12,"불참")+COUNTIF(J12:L12,"참석")+COUNTIF(J12:L12,"불참")</f>
+        <v>7</v>
+      </c>
+      <c r="O12" s="49">
+        <f>IF(N12=0,"",M12/N12)</f>
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="P12" s="48"/>
+    </row>
+    <row r="13" spans="1:16" ht="16.5">
       <c r="A13" s="47">
         <v>12</v>
       </c>
@@ -6796,21 +6992,24 @@
       <c r="K13" s="47" t="s">
         <v>173</v>
       </c>
-      <c r="L13" s="47">
-        <f>COUNTIF(E13:H13,"참석")+COUNTIF(J13:K13,"참석")</f>
+      <c r="L13" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="M13" s="47">
+        <f>COUNTIF(E13:H13,"참석")+COUNTIF(J13:L13,"참석")</f>
         <v>2</v>
       </c>
-      <c r="M13" s="47">
-        <f>COUNTIF(E13:H13,"참석")+COUNTIF(E13:H13,"불참")+COUNTIF(J13:K13,"참석")+COUNTIF(J13:K13,"불참")</f>
-        <v>6</v>
-      </c>
-      <c r="N13" s="49">
-        <f>IF(M13=0,"",L13/M13)</f>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="O13" s="48"/>
-    </row>
-    <row r="14" spans="1:15" ht="16.5">
+      <c r="N13" s="47">
+        <f>COUNTIF(E13:H13,"참석")+COUNTIF(E13:H13,"불참")+COUNTIF(J13:L13,"참석")+COUNTIF(J13:L13,"불참")</f>
+        <v>7</v>
+      </c>
+      <c r="O13" s="49">
+        <f>IF(N13=0,"",M13/N13)</f>
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="P13" s="48"/>
+    </row>
+    <row r="14" spans="1:16" ht="16.5">
       <c r="A14" s="47">
         <v>13</v>
       </c>
@@ -6842,21 +7041,24 @@
       <c r="K14" s="47" t="s">
         <v>173</v>
       </c>
-      <c r="L14" s="47">
-        <f>COUNTIF(E14:H14,"참석")+COUNTIF(J14:K14,"참석")</f>
+      <c r="L14" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="M14" s="47">
+        <f>COUNTIF(E14:H14,"참석")+COUNTIF(J14:L14,"참석")</f>
         <v>2</v>
       </c>
-      <c r="M14" s="47">
-        <f>COUNTIF(E14:H14,"참석")+COUNTIF(E14:H14,"불참")+COUNTIF(J14:K14,"참석")+COUNTIF(J14:K14,"불참")</f>
-        <v>6</v>
-      </c>
-      <c r="N14" s="49">
-        <f>IF(M14=0,"",L14/M14)</f>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="O14" s="48"/>
-    </row>
-    <row r="15" spans="1:15" ht="16.5">
+      <c r="N14" s="47">
+        <f>COUNTIF(E14:H14,"참석")+COUNTIF(E14:H14,"불참")+COUNTIF(J14:L14,"참석")+COUNTIF(J14:L14,"불참")</f>
+        <v>7</v>
+      </c>
+      <c r="O14" s="49">
+        <f>IF(N14=0,"",M14/N14)</f>
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="P14" s="48"/>
+    </row>
+    <row r="15" spans="1:16" ht="16.5">
       <c r="A15" s="47">
         <v>14</v>
       </c>
@@ -6888,21 +7090,24 @@
       <c r="K15" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="L15" s="47">
-        <f>COUNTIF(E15:H15,"참석")+COUNTIF(J15:K15,"참석")</f>
-        <v>5</v>
+      <c r="L15" s="47" t="s">
+        <v>234</v>
       </c>
       <c r="M15" s="47">
-        <f>COUNTIF(E15:H15,"참석")+COUNTIF(E15:H15,"불참")+COUNTIF(J15:K15,"참석")+COUNTIF(J15:K15,"불참")</f>
+        <f>COUNTIF(E15:H15,"참석")+COUNTIF(J15:L15,"참석")</f>
         <v>6</v>
       </c>
-      <c r="N15" s="49">
-        <f>IF(M15=0,"",L15/M15)</f>
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="O15" s="48"/>
-    </row>
-    <row r="16" spans="1:15" ht="16.5">
+      <c r="N15" s="47">
+        <f>COUNTIF(E15:H15,"참석")+COUNTIF(E15:H15,"불참")+COUNTIF(J15:L15,"참석")+COUNTIF(J15:L15,"불참")</f>
+        <v>7</v>
+      </c>
+      <c r="O15" s="49">
+        <f>IF(N15=0,"",M15/N15)</f>
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="P15" s="48"/>
+    </row>
+    <row r="16" spans="1:16" ht="16.5">
       <c r="A16" s="47">
         <v>15</v>
       </c>
@@ -6936,20 +7141,23 @@
       <c r="K16" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="L16" s="47">
-        <f>COUNTIF(E16:H16,"참석")+COUNTIF(J16:K16,"참석")</f>
+      <c r="L16" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="M16" s="47">
+        <f>COUNTIF(E16:H16,"참석")+COUNTIF(J16:L16,"참석")</f>
         <v>3</v>
       </c>
-      <c r="M16" s="47">
-        <f>COUNTIF(E16:H16,"참석")+COUNTIF(E16:H16,"불참")+COUNTIF(J16:K16,"참석")+COUNTIF(J16:K16,"불참")</f>
-        <v>6</v>
-      </c>
-      <c r="N16" s="49">
-        <f>IF(M16=0,"",L16/M16)</f>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" ht="16.5">
+      <c r="N16" s="47">
+        <f>COUNTIF(E16:H16,"참석")+COUNTIF(E16:H16,"불참")+COUNTIF(J16:L16,"참석")+COUNTIF(J16:L16,"불참")</f>
+        <v>7</v>
+      </c>
+      <c r="O16" s="49">
+        <f>IF(N16=0,"",M16/N16)</f>
+        <v>0.42857142857142855</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="16.5">
       <c r="A17" s="47">
         <v>16</v>
       </c>
@@ -6981,20 +7189,23 @@
       <c r="K17" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="L17" s="47">
-        <f>COUNTIF(E17:H17,"참석")+COUNTIF(J17:K17,"참석")</f>
+      <c r="L17" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="M17" s="47">
+        <f>COUNTIF(E17:H17,"참석")+COUNTIF(J17:L17,"참석")</f>
         <v>5</v>
       </c>
-      <c r="M17" s="47">
-        <f>COUNTIF(E17:H17,"참석")+COUNTIF(E17:H17,"불참")+COUNTIF(J17:K17,"참석")+COUNTIF(J17:K17,"불참")</f>
-        <v>6</v>
-      </c>
-      <c r="N17" s="49">
-        <f>IF(M17=0,"",L17/M17)</f>
-        <v>0.83333333333333337</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" ht="16.5">
+      <c r="N17" s="47">
+        <f>COUNTIF(E17:H17,"참석")+COUNTIF(E17:H17,"불참")+COUNTIF(J17:L17,"참석")+COUNTIF(J17:L17,"불참")</f>
+        <v>7</v>
+      </c>
+      <c r="O17" s="49">
+        <f>IF(N17=0,"",M17/N17)</f>
+        <v>0.7142857142857143</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="16.5">
       <c r="A18" s="47">
         <v>17</v>
       </c>
@@ -7026,20 +7237,23 @@
       <c r="K18" s="47" t="s">
         <v>173</v>
       </c>
-      <c r="L18" s="47">
-        <f>COUNTIF(E18:H18,"참석")+COUNTIF(J18:K18,"참석")</f>
-        <v>2</v>
+      <c r="L18" s="47" t="s">
+        <v>234</v>
       </c>
       <c r="M18" s="47">
-        <f>COUNTIF(E18:H18,"참석")+COUNTIF(E18:H18,"불참")+COUNTIF(J18:K18,"참석")+COUNTIF(J18:K18,"불참")</f>
-        <v>6</v>
-      </c>
-      <c r="N18" s="49">
-        <f>IF(M18=0,"",L18/M18)</f>
-        <v>0.33333333333333331</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" ht="16.5">
+        <f>COUNTIF(E18:H18,"참석")+COUNTIF(J18:L18,"참석")</f>
+        <v>3</v>
+      </c>
+      <c r="N18" s="47">
+        <f>COUNTIF(E18:H18,"참석")+COUNTIF(E18:H18,"불참")+COUNTIF(J18:L18,"참석")+COUNTIF(J18:L18,"불참")</f>
+        <v>7</v>
+      </c>
+      <c r="O18" s="49">
+        <f>IF(N18=0,"",M18/N18)</f>
+        <v>0.42857142857142855</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" ht="16.5">
       <c r="A19" s="47">
         <v>18</v>
       </c>
@@ -7071,23 +7285,26 @@
       <c r="K19" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="L19" s="47">
-        <f>COUNTIF(E19:H19,"참석")+COUNTIF(J19:K19,"참석")</f>
-        <v>3</v>
+      <c r="L19" s="47" t="s">
+        <v>234</v>
       </c>
       <c r="M19" s="47">
-        <f>COUNTIF(E19:H19,"참석")+COUNTIF(E19:H19,"불참")+COUNTIF(J19:K19,"참석")+COUNTIF(J19:K19,"불참")</f>
-        <v>3</v>
-      </c>
-      <c r="N19" s="49">
-        <f>IF(M19=0,"",L19/M19)</f>
+        <f>COUNTIF(E19:H19,"참석")+COUNTIF(J19:L19,"참석")</f>
+        <v>4</v>
+      </c>
+      <c r="N19" s="47">
+        <f>COUNTIF(E19:H19,"참석")+COUNTIF(E19:H19,"불참")+COUNTIF(J19:L19,"참석")+COUNTIF(J19:L19,"불참")</f>
+        <v>4</v>
+      </c>
+      <c r="O19" s="49">
+        <f>IF(N19=0,"",M19/N19)</f>
         <v>1</v>
       </c>
-      <c r="O19" s="46" t="s">
+      <c r="P19" s="46" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="16.5">
+    <row r="20" spans="1:16" ht="16.5">
       <c r="A20" s="47">
         <v>19</v>
       </c>
@@ -7119,20 +7336,23 @@
       <c r="K20" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="L20" s="47">
-        <f>COUNTIF(E20:H20,"참석")+COUNTIF(J20:K20,"참석")</f>
+      <c r="L20" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="M20" s="47">
+        <f>COUNTIF(E20:H20,"참석")+COUNTIF(J20:L20,"참석")</f>
         <v>5</v>
       </c>
-      <c r="M20" s="47">
-        <f>COUNTIF(E20:H20,"참석")+COUNTIF(E20:H20,"불참")+COUNTIF(J20:K20,"참석")+COUNTIF(J20:K20,"불참")</f>
-        <v>6</v>
-      </c>
-      <c r="N20" s="49">
-        <f>IF(M20=0,"",L20/M20)</f>
-        <v>0.83333333333333337</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" ht="16.5">
+      <c r="N20" s="47">
+        <f>COUNTIF(E20:H20,"참석")+COUNTIF(E20:H20,"불참")+COUNTIF(J20:L20,"참석")+COUNTIF(J20:L20,"불참")</f>
+        <v>7</v>
+      </c>
+      <c r="O20" s="49">
+        <f>IF(N20=0,"",M20/N20)</f>
+        <v>0.7142857142857143</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" ht="16.5">
       <c r="A21" s="47">
         <v>20</v>
       </c>
@@ -7164,20 +7384,23 @@
       <c r="K21" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="L21" s="47">
-        <f>COUNTIF(E21:H21,"참석")+COUNTIF(J21:K21,"참석")</f>
-        <v>5</v>
+      <c r="L21" s="47" t="s">
+        <v>234</v>
       </c>
       <c r="M21" s="47">
-        <f>COUNTIF(E21:H21,"참석")+COUNTIF(E21:H21,"불참")+COUNTIF(J21:K21,"참석")+COUNTIF(J21:K21,"불참")</f>
+        <f>COUNTIF(E21:H21,"참석")+COUNTIF(J21:L21,"참석")</f>
         <v>6</v>
       </c>
-      <c r="N21" s="49">
-        <f>IF(M21=0,"",L21/M21)</f>
-        <v>0.83333333333333337</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" ht="16.5">
+      <c r="N21" s="47">
+        <f>COUNTIF(E21:H21,"참석")+COUNTIF(E21:H21,"불참")+COUNTIF(J21:L21,"참석")+COUNTIF(J21:L21,"불참")</f>
+        <v>7</v>
+      </c>
+      <c r="O21" s="49">
+        <f>IF(N21=0,"",M21/N21)</f>
+        <v>0.8571428571428571</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" ht="16.5">
       <c r="A22" s="47">
         <v>21</v>
       </c>
@@ -7209,20 +7432,23 @@
       <c r="K22" s="47" t="s">
         <v>173</v>
       </c>
-      <c r="L22" s="47">
-        <f>COUNTIF(E22:H22,"참석")+COUNTIF(J22:K22,"참석")</f>
+      <c r="L22" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="M22" s="47">
+        <f>COUNTIF(E22:H22,"참석")+COUNTIF(J22:L22,"참석")</f>
         <v>3</v>
       </c>
-      <c r="M22" s="47">
-        <f>COUNTIF(E22:H22,"참석")+COUNTIF(E22:H22,"불참")+COUNTIF(J22:K22,"참석")+COUNTIF(J22:K22,"불참")</f>
-        <v>6</v>
-      </c>
-      <c r="N22" s="49">
-        <f>IF(M22=0,"",L22/M22)</f>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" ht="16.5">
+      <c r="N22" s="47">
+        <f>COUNTIF(E22:H22,"참석")+COUNTIF(E22:H22,"불참")+COUNTIF(J22:L22,"참석")+COUNTIF(J22:L22,"불참")</f>
+        <v>7</v>
+      </c>
+      <c r="O22" s="49">
+        <f>IF(N22=0,"",M22/N22)</f>
+        <v>0.42857142857142855</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" ht="16.5">
       <c r="A23" s="47">
         <v>22</v>
       </c>
@@ -7254,20 +7480,23 @@
       <c r="K23" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="L23" s="47">
-        <f>COUNTIF(E23:H23,"참석")+COUNTIF(J23:K23,"참석")</f>
-        <v>4</v>
+      <c r="L23" s="47" t="s">
+        <v>234</v>
       </c>
       <c r="M23" s="47">
-        <f>COUNTIF(E23:H23,"참석")+COUNTIF(E23:H23,"불참")+COUNTIF(J23:K23,"참석")+COUNTIF(J23:K23,"불참")</f>
-        <v>6</v>
-      </c>
-      <c r="N23" s="49">
-        <f>IF(M23=0,"",L23/M23)</f>
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" ht="16.5">
+        <f>COUNTIF(E23:H23,"참석")+COUNTIF(J23:L23,"참석")</f>
+        <v>5</v>
+      </c>
+      <c r="N23" s="47">
+        <f>COUNTIF(E23:H23,"참석")+COUNTIF(E23:H23,"불참")+COUNTIF(J23:L23,"참석")+COUNTIF(J23:L23,"불참")</f>
+        <v>7</v>
+      </c>
+      <c r="O23" s="49">
+        <f>IF(N23=0,"",M23/N23)</f>
+        <v>0.7142857142857143</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" ht="16.5">
       <c r="A24" s="47">
         <v>23</v>
       </c>
@@ -7301,20 +7530,23 @@
       <c r="K24" s="47" t="s">
         <v>173</v>
       </c>
-      <c r="L24" s="47">
-        <f>COUNTIF(E24:H24,"참석")+COUNTIF(J24:K24,"참석")</f>
+      <c r="L24" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="M24" s="47">
+        <f>COUNTIF(E24:H24,"참석")+COUNTIF(J24:L24,"참석")</f>
         <v>2</v>
       </c>
-      <c r="M24" s="47">
-        <f>COUNTIF(E24:H24,"참석")+COUNTIF(E24:H24,"불참")+COUNTIF(J24:K24,"참석")+COUNTIF(J24:K24,"불참")</f>
-        <v>6</v>
-      </c>
-      <c r="N24" s="49">
-        <f>IF(M24=0,"",L24/M24)</f>
-        <v>0.33333333333333331</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" ht="16.5">
+      <c r="N24" s="47">
+        <f>COUNTIF(E24:H24,"참석")+COUNTIF(E24:H24,"불참")+COUNTIF(J24:L24,"참석")+COUNTIF(J24:L24,"불참")</f>
+        <v>7</v>
+      </c>
+      <c r="O24" s="49">
+        <f>IF(N24=0,"",M24/N24)</f>
+        <v>0.2857142857142857</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" ht="16.5">
       <c r="A25" s="47">
         <v>24</v>
       </c>
@@ -7346,20 +7578,23 @@
       <c r="K25" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="L25" s="47">
-        <f>COUNTIF(E25:H25,"참석")+COUNTIF(J25:K25,"참석")</f>
-        <v>6</v>
+      <c r="L25" s="47" t="s">
+        <v>234</v>
       </c>
       <c r="M25" s="47">
-        <f>COUNTIF(E25:H25,"참석")+COUNTIF(E25:H25,"불참")+COUNTIF(J25:K25,"참석")+COUNTIF(J25:K25,"불참")</f>
-        <v>6</v>
-      </c>
-      <c r="N25" s="49">
-        <f>IF(M25=0,"",L25/M25)</f>
+        <f>COUNTIF(E25:H25,"참석")+COUNTIF(J25:L25,"참석")</f>
+        <v>7</v>
+      </c>
+      <c r="N25" s="47">
+        <f>COUNTIF(E25:H25,"참석")+COUNTIF(E25:H25,"불참")+COUNTIF(J25:L25,"참석")+COUNTIF(J25:L25,"불참")</f>
+        <v>7</v>
+      </c>
+      <c r="O25" s="49">
+        <f>IF(N25=0,"",M25/N25)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="16.5">
+    <row r="26" spans="1:16" ht="16.5">
       <c r="A26" s="47">
         <v>25</v>
       </c>
@@ -7391,20 +7626,23 @@
       <c r="K26" s="47" t="s">
         <v>173</v>
       </c>
-      <c r="L26" s="47">
-        <f>COUNTIF(E26:H26,"참석")+COUNTIF(J26:K26,"참석")</f>
+      <c r="L26" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="M26" s="47">
+        <f>COUNTIF(E26:H26,"참석")+COUNTIF(J26:L26,"참석")</f>
         <v>1</v>
       </c>
-      <c r="M26" s="47">
-        <f>COUNTIF(E26:H26,"참석")+COUNTIF(E26:H26,"불참")+COUNTIF(J26:K26,"참석")+COUNTIF(J26:K26,"불참")</f>
-        <v>6</v>
-      </c>
-      <c r="N26" s="49">
-        <f>IF(M26=0,"",L26/M26)</f>
-        <v>0.16666666666666666</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" ht="16.5">
+      <c r="N26" s="47">
+        <f>COUNTIF(E26:H26,"참석")+COUNTIF(E26:H26,"불참")+COUNTIF(J26:L26,"참석")+COUNTIF(J26:L26,"불참")</f>
+        <v>7</v>
+      </c>
+      <c r="O26" s="49">
+        <f>IF(N26=0,"",M26/N26)</f>
+        <v>0.14285714285714285</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" ht="16.5">
       <c r="A27" s="47">
         <v>26</v>
       </c>
@@ -7436,20 +7674,23 @@
       <c r="K27" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="L27" s="47">
-        <f>COUNTIF(E27:H27,"참석")+COUNTIF(J27:K27,"참석")</f>
-        <v>5</v>
+      <c r="L27" s="47" t="s">
+        <v>234</v>
       </c>
       <c r="M27" s="47">
-        <f>COUNTIF(E27:H27,"참석")+COUNTIF(E27:H27,"불참")+COUNTIF(J27:K27,"참석")+COUNTIF(J27:K27,"불참")</f>
+        <f>COUNTIF(E27:H27,"참석")+COUNTIF(J27:L27,"참석")</f>
         <v>6</v>
       </c>
-      <c r="N27" s="49">
-        <f>IF(M27=0,"",L27/M27)</f>
-        <v>0.83333333333333337</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" ht="16.5">
+      <c r="N27" s="47">
+        <f>COUNTIF(E27:H27,"참석")+COUNTIF(E27:H27,"불참")+COUNTIF(J27:L27,"참석")+COUNTIF(J27:L27,"불참")</f>
+        <v>7</v>
+      </c>
+      <c r="O27" s="49">
+        <f>IF(N27=0,"",M27/N27)</f>
+        <v>0.8571428571428571</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" ht="16.5">
       <c r="A28" s="47">
         <v>27</v>
       </c>
@@ -7481,20 +7722,23 @@
       <c r="K28" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="L28" s="47">
-        <f>COUNTIF(E28:H28,"참석")+COUNTIF(J28:K28,"참석")</f>
-        <v>6</v>
+      <c r="L28" s="47" t="s">
+        <v>234</v>
       </c>
       <c r="M28" s="47">
-        <f>COUNTIF(E28:H28,"참석")+COUNTIF(E28:H28,"불참")+COUNTIF(J28:K28,"참석")+COUNTIF(J28:K28,"불참")</f>
-        <v>6</v>
-      </c>
-      <c r="N28" s="49">
-        <f>IF(M28=0,"",L28/M28)</f>
+        <f>COUNTIF(E28:H28,"참석")+COUNTIF(J28:L28,"참석")</f>
+        <v>7</v>
+      </c>
+      <c r="N28" s="47">
+        <f>COUNTIF(E28:H28,"참석")+COUNTIF(E28:H28,"불참")+COUNTIF(J28:L28,"참석")+COUNTIF(J28:L28,"불참")</f>
+        <v>7</v>
+      </c>
+      <c r="O28" s="49">
+        <f>IF(N28=0,"",M28/N28)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:15" ht="16.5">
+    <row r="29" spans="1:16" ht="16.5">
       <c r="A29" s="47">
         <v>28</v>
       </c>
@@ -7526,20 +7770,23 @@
       <c r="K29" s="47" t="s">
         <v>173</v>
       </c>
-      <c r="L29" s="47">
-        <f>COUNTIF(E29:H29,"참석")+COUNTIF(J29:K29,"참석")</f>
+      <c r="L29" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="M29" s="47">
+        <f>COUNTIF(E29:H29,"참석")+COUNTIF(J29:L29,"참석")</f>
         <v>2</v>
       </c>
-      <c r="M29" s="47">
-        <f>COUNTIF(E29:H29,"참석")+COUNTIF(E29:H29,"불참")+COUNTIF(J29:K29,"참석")+COUNTIF(J29:K29,"불참")</f>
-        <v>6</v>
-      </c>
-      <c r="N29" s="49">
-        <f>IF(M29=0,"",L29/M29)</f>
-        <v>0.33333333333333331</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" ht="16.5">
+      <c r="N29" s="47">
+        <f>COUNTIF(E29:H29,"참석")+COUNTIF(E29:H29,"불참")+COUNTIF(J29:L29,"참석")+COUNTIF(J29:L29,"불참")</f>
+        <v>7</v>
+      </c>
+      <c r="O29" s="49">
+        <f>IF(N29=0,"",M29/N29)</f>
+        <v>0.2857142857142857</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" ht="16.5">
       <c r="A30" s="47">
         <v>29</v>
       </c>
@@ -7568,20 +7815,23 @@
       <c r="K30" s="47" t="s">
         <v>173</v>
       </c>
-      <c r="L30" s="47">
-        <f>COUNTIF(E30:H30,"참석")+COUNTIF(J30:K30,"참석")</f>
+      <c r="L30" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="M30" s="47">
+        <f>COUNTIF(E30:H30,"참석")+COUNTIF(J30:L30,"참석")</f>
         <v>1</v>
       </c>
-      <c r="M30" s="47">
-        <f>COUNTIF(E30:H30,"참석")+COUNTIF(E30:H30,"불참")+COUNTIF(J30:K30,"참석")+COUNTIF(J30:K30,"불참")</f>
-        <v>6</v>
-      </c>
-      <c r="N30" s="49">
-        <f>IF(M30=0,"",L30/M30)</f>
-        <v>0.16666666666666666</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" ht="16.5">
+      <c r="N30" s="47">
+        <f>COUNTIF(E30:H30,"참석")+COUNTIF(E30:H30,"불참")+COUNTIF(J30:L30,"참석")+COUNTIF(J30:L30,"불참")</f>
+        <v>7</v>
+      </c>
+      <c r="O30" s="49">
+        <f>IF(N30=0,"",M30/N30)</f>
+        <v>0.14285714285714285</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" ht="16.5">
       <c r="E31" s="46">
         <f>COUNTIF(E2:E29,"참석")</f>
         <v>19</v>
@@ -7594,14 +7844,14 @@
         <f>COUNTIF(G2:G29,"참석")</f>
         <v>19</v>
       </c>
-      <c r="N31" s="49" t="str">
-        <f t="shared" ref="N2:N31" si="0">IF(M31=0,"",L31/M31)</f>
+      <c r="O31" s="49" t="str">
+        <f t="shared" ref="O31" si="0">IF(N31=0,"",M31/N31)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O31" xr:uid="{C0625D6E-2678-482C-88B1-4B31BC9434B5}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O31">
+  <autoFilter ref="A1:P31" xr:uid="{C0625D6E-2678-482C-88B1-4B31BC9434B5}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P31">
       <sortCondition ref="C1:C31"/>
     </sortState>
   </autoFilter>

--- a/4기차세대경영자과정/차경 4기 정산서.xlsx
+++ b/4기차세대경영자과정/차경 4기 정산서.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Innobiz\Documents\innobiz-nextgen\4기차세대경영자과정\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29E14D24-D74E-4034-BF7B-A67A8FEDED64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D52EA5E7-A981-4E32-91EF-F23ED3CE7924}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{404CE508-8F71-4CA4-99F0-0EFB79DB1227}"/>
   </bookViews>
@@ -6028,7 +6028,7 @@
         <v>38</v>
       </c>
       <c r="B41" s="71">
-        <v>1500000</v>
+        <v>1000000</v>
       </c>
       <c r="C41" s="35">
         <v>46198</v>
@@ -6445,15 +6445,15 @@
         <v>234</v>
       </c>
       <c r="M2" s="47">
-        <f>COUNTIF(E2:H2,"참석")+COUNTIF(J2:L2,"참석")</f>
+        <f t="shared" ref="M2:M30" si="0">COUNTIF(E2:H2,"참석")+COUNTIF(J2:L2,"참석")</f>
         <v>7</v>
       </c>
       <c r="N2" s="47">
-        <f>COUNTIF(E2:H2,"참석")+COUNTIF(E2:H2,"불참")+COUNTIF(J2:L2,"참석")+COUNTIF(J2:L2,"불참")</f>
+        <f t="shared" ref="N2:N30" si="1">COUNTIF(E2:H2,"참석")+COUNTIF(E2:H2,"불참")+COUNTIF(J2:L2,"참석")+COUNTIF(J2:L2,"불참")</f>
         <v>7</v>
       </c>
       <c r="O2" s="49">
-        <f>IF(N2=0,"",M2/N2)</f>
+        <f t="shared" ref="O2:O30" si="2">IF(N2=0,"",M2/N2)</f>
         <v>1</v>
       </c>
       <c r="P2" s="48"/>
@@ -6496,15 +6496,15 @@
         <v>234</v>
       </c>
       <c r="M3" s="47">
-        <f>COUNTIF(E3:H3,"참석")+COUNTIF(J3:L3,"참석")</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="N3" s="47">
-        <f>COUNTIF(E3:H3,"참석")+COUNTIF(E3:H3,"불참")+COUNTIF(J3:L3,"참석")+COUNTIF(J3:L3,"불참")</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="O3" s="49">
-        <f>IF(N3=0,"",M3/N3)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="P3" s="48"/>
@@ -6547,15 +6547,15 @@
         <v>234</v>
       </c>
       <c r="M4" s="47">
-        <f>COUNTIF(E4:H4,"참석")+COUNTIF(J4:L4,"참석")</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="N4" s="47">
-        <f>COUNTIF(E4:H4,"참석")+COUNTIF(E4:H4,"불참")+COUNTIF(J4:L4,"참석")+COUNTIF(J4:L4,"불참")</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="O4" s="49">
-        <f>IF(N4=0,"",M4/N4)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="P4" s="48"/>
@@ -6596,15 +6596,15 @@
         <v>234</v>
       </c>
       <c r="M5" s="47">
-        <f>COUNTIF(E5:H5,"참석")+COUNTIF(J5:L5,"참석")</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="N5" s="47">
-        <f>COUNTIF(E5:H5,"참석")+COUNTIF(E5:H5,"불참")+COUNTIF(J5:L5,"참석")+COUNTIF(J5:L5,"불참")</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="O5" s="49">
-        <f>IF(N5=0,"",M5/N5)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="P5" s="48"/>
@@ -6647,15 +6647,15 @@
         <v>234</v>
       </c>
       <c r="M6" s="47">
-        <f>COUNTIF(E6:H6,"참석")+COUNTIF(J6:L6,"참석")</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="N6" s="47">
-        <f>COUNTIF(E6:H6,"참석")+COUNTIF(E6:H6,"불참")+COUNTIF(J6:L6,"참석")+COUNTIF(J6:L6,"불참")</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="O6" s="49">
-        <f>IF(N6=0,"",M6/N6)</f>
+        <f t="shared" si="2"/>
         <v>0.7142857142857143</v>
       </c>
       <c r="P6" s="48"/>
@@ -6698,15 +6698,15 @@
         <v>234</v>
       </c>
       <c r="M7" s="47">
-        <f>COUNTIF(E7:H7,"참석")+COUNTIF(J7:L7,"참석")</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="N7" s="47">
-        <f>COUNTIF(E7:H7,"참석")+COUNTIF(E7:H7,"불참")+COUNTIF(J7:L7,"참석")+COUNTIF(J7:L7,"불참")</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="O7" s="49">
-        <f>IF(N7=0,"",M7/N7)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="P7" s="48"/>
@@ -6747,15 +6747,15 @@
         <v>173</v>
       </c>
       <c r="M8" s="47">
-        <f>COUNTIF(E8:H8,"참석")+COUNTIF(J8:L8,"참석")</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="N8" s="47">
-        <f>COUNTIF(E8:H8,"참석")+COUNTIF(E8:H8,"불참")+COUNTIF(J8:L8,"참석")+COUNTIF(J8:L8,"불참")</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="O8" s="49">
-        <f>IF(N8=0,"",M8/N8)</f>
+        <f t="shared" si="2"/>
         <v>0.42857142857142855</v>
       </c>
       <c r="P8" s="48"/>
@@ -6798,15 +6798,15 @@
         <v>234</v>
       </c>
       <c r="M9" s="47">
-        <f>COUNTIF(E9:H9,"참석")+COUNTIF(J9:L9,"참석")</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="N9" s="47">
-        <f>COUNTIF(E9:H9,"참석")+COUNTIF(E9:H9,"불참")+COUNTIF(J9:L9,"참석")+COUNTIF(J9:L9,"불참")</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="O9" s="49">
-        <f>IF(N9=0,"",M9/N9)</f>
+        <f t="shared" si="2"/>
         <v>0.8</v>
       </c>
       <c r="P9" s="48" t="s">
@@ -6849,15 +6849,15 @@
         <v>234</v>
       </c>
       <c r="M10" s="47">
-        <f>COUNTIF(E10:H10,"참석")+COUNTIF(J10:L10,"참석")</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="N10" s="47">
-        <f>COUNTIF(E10:H10,"참석")+COUNTIF(E10:H10,"불참")+COUNTIF(J10:L10,"참석")+COUNTIF(J10:L10,"불참")</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="O10" s="49">
-        <f>IF(N10=0,"",M10/N10)</f>
+        <f t="shared" si="2"/>
         <v>0.5714285714285714</v>
       </c>
       <c r="P10" s="48"/>
@@ -6898,15 +6898,15 @@
         <v>173</v>
       </c>
       <c r="M11" s="47">
-        <f>COUNTIF(E11:H11,"참석")+COUNTIF(J11:L11,"참석")</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="N11" s="47">
-        <f>COUNTIF(E11:H11,"참석")+COUNTIF(E11:H11,"불참")+COUNTIF(J11:L11,"참석")+COUNTIF(J11:L11,"불참")</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="O11" s="49">
-        <f>IF(N11=0,"",M11/N11)</f>
+        <f t="shared" si="2"/>
         <v>0.42857142857142855</v>
       </c>
       <c r="P11" s="48"/>
@@ -6947,15 +6947,15 @@
         <v>234</v>
       </c>
       <c r="M12" s="47">
-        <f>COUNTIF(E12:H12,"참석")+COUNTIF(J12:L12,"참석")</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="N12" s="47">
-        <f>COUNTIF(E12:H12,"참석")+COUNTIF(E12:H12,"불참")+COUNTIF(J12:L12,"참석")+COUNTIF(J12:L12,"불참")</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="O12" s="49">
-        <f>IF(N12=0,"",M12/N12)</f>
+        <f t="shared" si="2"/>
         <v>0.7142857142857143</v>
       </c>
       <c r="P12" s="48"/>
@@ -6996,15 +6996,15 @@
         <v>173</v>
       </c>
       <c r="M13" s="47">
-        <f>COUNTIF(E13:H13,"참석")+COUNTIF(J13:L13,"참석")</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="N13" s="47">
-        <f>COUNTIF(E13:H13,"참석")+COUNTIF(E13:H13,"불참")+COUNTIF(J13:L13,"참석")+COUNTIF(J13:L13,"불참")</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="O13" s="49">
-        <f>IF(N13=0,"",M13/N13)</f>
+        <f t="shared" si="2"/>
         <v>0.2857142857142857</v>
       </c>
       <c r="P13" s="48"/>
@@ -7045,15 +7045,15 @@
         <v>173</v>
       </c>
       <c r="M14" s="47">
-        <f>COUNTIF(E14:H14,"참석")+COUNTIF(J14:L14,"참석")</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="N14" s="47">
-        <f>COUNTIF(E14:H14,"참석")+COUNTIF(E14:H14,"불참")+COUNTIF(J14:L14,"참석")+COUNTIF(J14:L14,"불참")</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="O14" s="49">
-        <f>IF(N14=0,"",M14/N14)</f>
+        <f t="shared" si="2"/>
         <v>0.2857142857142857</v>
       </c>
       <c r="P14" s="48"/>
@@ -7094,15 +7094,15 @@
         <v>234</v>
       </c>
       <c r="M15" s="47">
-        <f>COUNTIF(E15:H15,"참석")+COUNTIF(J15:L15,"참석")</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="N15" s="47">
-        <f>COUNTIF(E15:H15,"참석")+COUNTIF(E15:H15,"불참")+COUNTIF(J15:L15,"참석")+COUNTIF(J15:L15,"불참")</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="O15" s="49">
-        <f>IF(N15=0,"",M15/N15)</f>
+        <f t="shared" si="2"/>
         <v>0.8571428571428571</v>
       </c>
       <c r="P15" s="48"/>
@@ -7145,15 +7145,15 @@
         <v>173</v>
       </c>
       <c r="M16" s="47">
-        <f>COUNTIF(E16:H16,"참석")+COUNTIF(J16:L16,"참석")</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="N16" s="47">
-        <f>COUNTIF(E16:H16,"참석")+COUNTIF(E16:H16,"불참")+COUNTIF(J16:L16,"참석")+COUNTIF(J16:L16,"불참")</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="O16" s="49">
-        <f>IF(N16=0,"",M16/N16)</f>
+        <f t="shared" si="2"/>
         <v>0.42857142857142855</v>
       </c>
     </row>
@@ -7193,15 +7193,15 @@
         <v>173</v>
       </c>
       <c r="M17" s="47">
-        <f>COUNTIF(E17:H17,"참석")+COUNTIF(J17:L17,"참석")</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="N17" s="47">
-        <f>COUNTIF(E17:H17,"참석")+COUNTIF(E17:H17,"불참")+COUNTIF(J17:L17,"참석")+COUNTIF(J17:L17,"불참")</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="O17" s="49">
-        <f>IF(N17=0,"",M17/N17)</f>
+        <f t="shared" si="2"/>
         <v>0.7142857142857143</v>
       </c>
     </row>
@@ -7241,15 +7241,15 @@
         <v>234</v>
       </c>
       <c r="M18" s="47">
-        <f>COUNTIF(E18:H18,"참석")+COUNTIF(J18:L18,"참석")</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="N18" s="47">
-        <f>COUNTIF(E18:H18,"참석")+COUNTIF(E18:H18,"불참")+COUNTIF(J18:L18,"참석")+COUNTIF(J18:L18,"불참")</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="O18" s="49">
-        <f>IF(N18=0,"",M18/N18)</f>
+        <f t="shared" si="2"/>
         <v>0.42857142857142855</v>
       </c>
     </row>
@@ -7289,15 +7289,15 @@
         <v>234</v>
       </c>
       <c r="M19" s="47">
-        <f>COUNTIF(E19:H19,"참석")+COUNTIF(J19:L19,"참석")</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="N19" s="47">
-        <f>COUNTIF(E19:H19,"참석")+COUNTIF(E19:H19,"불참")+COUNTIF(J19:L19,"참석")+COUNTIF(J19:L19,"불참")</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="O19" s="49">
-        <f>IF(N19=0,"",M19/N19)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="P19" s="46" t="s">
@@ -7340,15 +7340,15 @@
         <v>173</v>
       </c>
       <c r="M20" s="47">
-        <f>COUNTIF(E20:H20,"참석")+COUNTIF(J20:L20,"참석")</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="N20" s="47">
-        <f>COUNTIF(E20:H20,"참석")+COUNTIF(E20:H20,"불참")+COUNTIF(J20:L20,"참석")+COUNTIF(J20:L20,"불참")</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="O20" s="49">
-        <f>IF(N20=0,"",M20/N20)</f>
+        <f t="shared" si="2"/>
         <v>0.7142857142857143</v>
       </c>
     </row>
@@ -7388,15 +7388,15 @@
         <v>234</v>
       </c>
       <c r="M21" s="47">
-        <f>COUNTIF(E21:H21,"참석")+COUNTIF(J21:L21,"참석")</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="N21" s="47">
-        <f>COUNTIF(E21:H21,"참석")+COUNTIF(E21:H21,"불참")+COUNTIF(J21:L21,"참석")+COUNTIF(J21:L21,"불참")</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="O21" s="49">
-        <f>IF(N21=0,"",M21/N21)</f>
+        <f t="shared" si="2"/>
         <v>0.8571428571428571</v>
       </c>
     </row>
@@ -7436,15 +7436,15 @@
         <v>173</v>
       </c>
       <c r="M22" s="47">
-        <f>COUNTIF(E22:H22,"참석")+COUNTIF(J22:L22,"참석")</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="N22" s="47">
-        <f>COUNTIF(E22:H22,"참석")+COUNTIF(E22:H22,"불참")+COUNTIF(J22:L22,"참석")+COUNTIF(J22:L22,"불참")</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="O22" s="49">
-        <f>IF(N22=0,"",M22/N22)</f>
+        <f t="shared" si="2"/>
         <v>0.42857142857142855</v>
       </c>
     </row>
@@ -7484,15 +7484,15 @@
         <v>234</v>
       </c>
       <c r="M23" s="47">
-        <f>COUNTIF(E23:H23,"참석")+COUNTIF(J23:L23,"참석")</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="N23" s="47">
-        <f>COUNTIF(E23:H23,"참석")+COUNTIF(E23:H23,"불참")+COUNTIF(J23:L23,"참석")+COUNTIF(J23:L23,"불참")</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="O23" s="49">
-        <f>IF(N23=0,"",M23/N23)</f>
+        <f t="shared" si="2"/>
         <v>0.7142857142857143</v>
       </c>
     </row>
@@ -7534,15 +7534,15 @@
         <v>173</v>
       </c>
       <c r="M24" s="47">
-        <f>COUNTIF(E24:H24,"참석")+COUNTIF(J24:L24,"참석")</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="N24" s="47">
-        <f>COUNTIF(E24:H24,"참석")+COUNTIF(E24:H24,"불참")+COUNTIF(J24:L24,"참석")+COUNTIF(J24:L24,"불참")</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="O24" s="49">
-        <f>IF(N24=0,"",M24/N24)</f>
+        <f t="shared" si="2"/>
         <v>0.2857142857142857</v>
       </c>
     </row>
@@ -7582,15 +7582,15 @@
         <v>234</v>
       </c>
       <c r="M25" s="47">
-        <f>COUNTIF(E25:H25,"참석")+COUNTIF(J25:L25,"참석")</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="N25" s="47">
-        <f>COUNTIF(E25:H25,"참석")+COUNTIF(E25:H25,"불참")+COUNTIF(J25:L25,"참석")+COUNTIF(J25:L25,"불참")</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="O25" s="49">
-        <f>IF(N25=0,"",M25/N25)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -7630,15 +7630,15 @@
         <v>173</v>
       </c>
       <c r="M26" s="47">
-        <f>COUNTIF(E26:H26,"참석")+COUNTIF(J26:L26,"참석")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="N26" s="47">
-        <f>COUNTIF(E26:H26,"참석")+COUNTIF(E26:H26,"불참")+COUNTIF(J26:L26,"참석")+COUNTIF(J26:L26,"불참")</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="O26" s="49">
-        <f>IF(N26=0,"",M26/N26)</f>
+        <f t="shared" si="2"/>
         <v>0.14285714285714285</v>
       </c>
     </row>
@@ -7678,15 +7678,15 @@
         <v>234</v>
       </c>
       <c r="M27" s="47">
-        <f>COUNTIF(E27:H27,"참석")+COUNTIF(J27:L27,"참석")</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="N27" s="47">
-        <f>COUNTIF(E27:H27,"참석")+COUNTIF(E27:H27,"불참")+COUNTIF(J27:L27,"참석")+COUNTIF(J27:L27,"불참")</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="O27" s="49">
-        <f>IF(N27=0,"",M27/N27)</f>
+        <f t="shared" si="2"/>
         <v>0.8571428571428571</v>
       </c>
     </row>
@@ -7726,15 +7726,15 @@
         <v>234</v>
       </c>
       <c r="M28" s="47">
-        <f>COUNTIF(E28:H28,"참석")+COUNTIF(J28:L28,"참석")</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="N28" s="47">
-        <f>COUNTIF(E28:H28,"참석")+COUNTIF(E28:H28,"불참")+COUNTIF(J28:L28,"참석")+COUNTIF(J28:L28,"불참")</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="O28" s="49">
-        <f>IF(N28=0,"",M28/N28)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -7774,15 +7774,15 @@
         <v>173</v>
       </c>
       <c r="M29" s="47">
-        <f>COUNTIF(E29:H29,"참석")+COUNTIF(J29:L29,"참석")</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="N29" s="47">
-        <f>COUNTIF(E29:H29,"참석")+COUNTIF(E29:H29,"불참")+COUNTIF(J29:L29,"참석")+COUNTIF(J29:L29,"불참")</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="O29" s="49">
-        <f>IF(N29=0,"",M29/N29)</f>
+        <f t="shared" si="2"/>
         <v>0.2857142857142857</v>
       </c>
     </row>
@@ -7819,15 +7819,15 @@
         <v>173</v>
       </c>
       <c r="M30" s="47">
-        <f>COUNTIF(E30:H30,"참석")+COUNTIF(J30:L30,"참석")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="N30" s="47">
-        <f>COUNTIF(E30:H30,"참석")+COUNTIF(E30:H30,"불참")+COUNTIF(J30:L30,"참석")+COUNTIF(J30:L30,"불참")</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="O30" s="49">
-        <f>IF(N30=0,"",M30/N30)</f>
+        <f t="shared" si="2"/>
         <v>0.14285714285714285</v>
       </c>
     </row>
@@ -7845,7 +7845,7 @@
         <v>19</v>
       </c>
       <c r="O31" s="49" t="str">
-        <f t="shared" ref="O31" si="0">IF(N31=0,"",M31/N31)</f>
+        <f t="shared" ref="O31" si="3">IF(N31=0,"",M31/N31)</f>
         <v/>
       </c>
     </row>

--- a/4기차세대경영자과정/차경 4기 정산서.xlsx
+++ b/4기차세대경영자과정/차경 4기 정산서.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Innobiz\Documents\innobiz-nextgen\4기차세대경영자과정\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D52EA5E7-A981-4E32-91EF-F23ED3CE7924}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5BE5548-6C2A-421B-9B10-B8EE084E9AB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{404CE508-8F71-4CA4-99F0-0EFB79DB1227}"/>
   </bookViews>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="B5" s="23">
         <f>SUM(지출세부내역서!B11:B14)</f>
-        <v>3411500</v>
+        <v>2411500</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>114</v>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="B15" s="23">
         <f>SUM(B4:B14)</f>
-        <v>14563500</v>
+        <v>13563500</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="25"/>
@@ -5402,7 +5402,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="44">
-        <v>3000000</v>
+        <v>2000000</v>
       </c>
       <c r="C14" s="36">
         <v>46156</v>

--- a/4기차세대경영자과정/차경 4기 정산서.xlsx
+++ b/4기차세대경영자과정/차경 4기 정산서.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Innobiz\Documents\innobiz-nextgen\4기차세대경영자과정\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5BE5548-6C2A-421B-9B10-B8EE084E9AB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB72138A-2308-4D72-9A59-6B03D6FA01E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{404CE508-8F71-4CA4-99F0-0EFB79DB1227}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{404CE508-8F71-4CA4-99F0-0EFB79DB1227}"/>
   </bookViews>
   <sheets>
     <sheet name="항목별(피벗)" sheetId="9" r:id="rId1"/>
@@ -23,7 +23,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">실수입내역!$A$3:$C$46</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">지출세부내역서!$A$3:$G$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'회차별 출석현황'!$A$1:$P$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'회차별 출석현황'!$A$1:$R$31</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1517,7 +1517,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="319">
   <si>
     <t>번호</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -2617,6 +2617,45 @@
   </si>
   <si>
     <t>8주(2026-06-25)</t>
+  </si>
+  <si>
+    <t>회의실 사용료(07/02, 냉방사용료 포함)</t>
+  </si>
+  <si>
+    <t>운영비</t>
+  </si>
+  <si>
+    <t>이노밸리</t>
+  </si>
+  <si>
+    <t>강사비(한웅)</t>
+  </si>
+  <si>
+    <t>코맥스</t>
+  </si>
+  <si>
+    <t>진행비(유일한) *세금계산서 처리</t>
+  </si>
+  <si>
+    <t>주식회사 스마트에이엘</t>
+  </si>
+  <si>
+    <t>식비(정원)</t>
+  </si>
+  <si>
+    <t>정원</t>
+  </si>
+  <si>
+    <t>다과비(무지커피)</t>
+  </si>
+  <si>
+    <t>무지커피 판교더블유시티점</t>
+  </si>
+  <si>
+    <t>9주(2026-07-02)</t>
+  </si>
+  <si>
+    <t>10주(2026-07-10~11, 졸업여행)</t>
   </si>
 </sst>
 </file>
@@ -5111,7 +5150,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{959FEF70-8578-4918-8CDC-E1B4AA8967DB}">
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="7.125" customWidth="1"/>
@@ -6136,6 +6175,121 @@
       </c>
       <c r="G45" s="2" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46">
+        <v>43</v>
+      </c>
+      <c r="B46" s="71">
+        <v>550000</v>
+      </c>
+      <c r="C46" s="35">
+        <v>46205</v>
+      </c>
+      <c r="D46" s="34" t="s">
+        <v>306</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="F46" s="34" t="s">
+        <v>308</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47">
+        <v>44</v>
+      </c>
+      <c r="B47" s="71">
+        <v>1000000</v>
+      </c>
+      <c r="C47" s="35">
+        <v>46205</v>
+      </c>
+      <c r="D47" s="34" t="s">
+        <v>309</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="F47" s="34" t="s">
+        <v>310</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48">
+        <v>45</v>
+      </c>
+      <c r="B48" s="71">
+        <v>1000000</v>
+      </c>
+      <c r="C48" s="35">
+        <v>46205</v>
+      </c>
+      <c r="D48" s="34" t="s">
+        <v>311</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="F48" s="34" t="s">
+        <v>312</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49">
+        <v>46</v>
+      </c>
+      <c r="B49" s="71">
+        <v>356000</v>
+      </c>
+      <c r="C49" s="35">
+        <v>46205</v>
+      </c>
+      <c r="D49" s="34" t="s">
+        <v>313</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="F49" s="34" t="s">
+        <v>314</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50">
+        <v>47</v>
+      </c>
+      <c r="B50" s="71">
+        <v>48800</v>
+      </c>
+      <c r="C50" s="35">
+        <v>46205</v>
+      </c>
+      <c r="D50" s="34" t="s">
+        <v>315</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="F50" s="34" t="s">
+        <v>316</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -6344,20 +6498,20 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0625D6E-2678-482C-88B1-4B31BC9434B5}">
-  <dimension ref="A1:P31"/>
+  <dimension ref="A1:R31"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="8" style="46" customWidth="1"/>
     <col min="2" max="2" width="34" style="46" customWidth="1"/>
     <col min="3" max="4" width="12" style="46" customWidth="1"/>
-    <col min="5" max="12" width="16" style="46" customWidth="1"/>
-    <col min="13" max="14" width="12" style="46" customWidth="1"/>
-    <col min="15" max="15" width="10" style="46" customWidth="1"/>
-    <col min="16" max="16" width="30" style="46" customWidth="1"/>
-    <col min="17" max="16384" width="9" style="46"/>
+    <col min="5" max="14" width="16" style="46" customWidth="1"/>
+    <col min="15" max="16" width="12" style="46" customWidth="1"/>
+    <col min="17" max="17" width="10" style="46" customWidth="1"/>
+    <col min="18" max="18" width="30" style="46" customWidth="1"/>
+    <col min="19" max="16384" width="9" style="46"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15">
+    <row r="1" spans="1:18" ht="15">
       <c r="A1" s="45" t="s">
         <v>149</v>
       </c>
@@ -6395,19 +6549,25 @@
         <v>305</v>
       </c>
       <c r="M1" s="45" t="s">
+        <v>317</v>
+      </c>
+      <c r="N1" s="45" t="s">
+        <v>318</v>
+      </c>
+      <c r="O1" s="45" t="s">
         <v>156</v>
       </c>
-      <c r="N1" s="45" t="s">
+      <c r="P1" s="45" t="s">
         <v>157</v>
       </c>
-      <c r="O1" s="45" t="s">
+      <c r="Q1" s="45" t="s">
         <v>158</v>
       </c>
-      <c r="P1" s="45" t="s">
+      <c r="R1" s="45" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="16.5">
+    <row r="2" spans="1:18" ht="16.5">
       <c r="A2" s="47">
         <v>1</v>
       </c>
@@ -6444,21 +6604,27 @@
       <c r="L2" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="M2" s="47">
-        <f t="shared" ref="M2:M30" si="0">COUNTIF(E2:H2,"참석")+COUNTIF(J2:L2,"참석")</f>
-        <v>7</v>
-      </c>
-      <c r="N2" s="47">
-        <f t="shared" ref="N2:N30" si="1">COUNTIF(E2:H2,"참석")+COUNTIF(E2:H2,"불참")+COUNTIF(J2:L2,"참석")+COUNTIF(J2:L2,"불참")</f>
-        <v>7</v>
-      </c>
-      <c r="O2" s="49">
-        <f t="shared" ref="O2:O30" si="2">IF(N2=0,"",M2/N2)</f>
+      <c r="M2" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="N2" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="O2" s="47">
+        <f>COUNTIF(E2:H2,"참석")+COUNTIF(J2:N2,"참석")</f>
+        <v>9</v>
+      </c>
+      <c r="P2" s="47">
+        <f>COUNTIF(E2:H2,"참석")+COUNTIF(E2:H2,"불참")+COUNTIF(J2:N2,"참석")+COUNTIF(J2:N2,"불참")</f>
+        <v>9</v>
+      </c>
+      <c r="Q2" s="49">
+        <f>IF(P2=0,"",O2/P2)</f>
         <v>1</v>
       </c>
-      <c r="P2" s="48"/>
-    </row>
-    <row r="3" spans="1:16" ht="16.5">
+      <c r="R2" s="48"/>
+    </row>
+    <row r="3" spans="1:18" ht="16.5">
       <c r="A3" s="47">
         <v>2</v>
       </c>
@@ -6495,21 +6661,27 @@
       <c r="L3" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="M3" s="47">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="N3" s="47">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="O3" s="49">
-        <f t="shared" si="2"/>
+      <c r="M3" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="N3" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="O3" s="47">
+        <f>COUNTIF(E3:H3,"참석")+COUNTIF(J3:N3,"참석")</f>
+        <v>9</v>
+      </c>
+      <c r="P3" s="47">
+        <f>COUNTIF(E3:H3,"참석")+COUNTIF(E3:H3,"불참")+COUNTIF(J3:N3,"참석")+COUNTIF(J3:N3,"불참")</f>
+        <v>9</v>
+      </c>
+      <c r="Q3" s="49">
+        <f>IF(P3=0,"",O3/P3)</f>
         <v>1</v>
       </c>
-      <c r="P3" s="48"/>
-    </row>
-    <row r="4" spans="1:16" ht="16.5">
+      <c r="R3" s="48"/>
+    </row>
+    <row r="4" spans="1:18" ht="16.5">
       <c r="A4" s="47">
         <v>3</v>
       </c>
@@ -6546,21 +6718,27 @@
       <c r="L4" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="M4" s="47">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="N4" s="47">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="O4" s="49">
-        <f t="shared" si="2"/>
+      <c r="M4" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="N4" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="O4" s="47">
+        <f>COUNTIF(E4:H4,"참석")+COUNTIF(J4:N4,"참석")</f>
+        <v>9</v>
+      </c>
+      <c r="P4" s="47">
+        <f>COUNTIF(E4:H4,"참석")+COUNTIF(E4:H4,"불참")+COUNTIF(J4:N4,"참석")+COUNTIF(J4:N4,"불참")</f>
+        <v>9</v>
+      </c>
+      <c r="Q4" s="49">
+        <f>IF(P4=0,"",O4/P4)</f>
         <v>1</v>
       </c>
-      <c r="P4" s="48"/>
-    </row>
-    <row r="5" spans="1:16" ht="16.5">
+      <c r="R4" s="48"/>
+    </row>
+    <row r="5" spans="1:18" ht="16.5">
       <c r="A5" s="47">
         <v>4</v>
       </c>
@@ -6595,21 +6773,27 @@
       <c r="L5" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="M5" s="47">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="N5" s="47">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="O5" s="49">
-        <f t="shared" si="2"/>
+      <c r="M5" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="N5" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="O5" s="47">
+        <f>COUNTIF(E5:H5,"참석")+COUNTIF(J5:N5,"참석")</f>
+        <v>9</v>
+      </c>
+      <c r="P5" s="47">
+        <f>COUNTIF(E5:H5,"참석")+COUNTIF(E5:H5,"불참")+COUNTIF(J5:N5,"참석")+COUNTIF(J5:N5,"불참")</f>
+        <v>9</v>
+      </c>
+      <c r="Q5" s="49">
+        <f>IF(P5=0,"",O5/P5)</f>
         <v>1</v>
       </c>
-      <c r="P5" s="48"/>
-    </row>
-    <row r="6" spans="1:16" ht="16.5">
+      <c r="R5" s="48"/>
+    </row>
+    <row r="6" spans="1:18" ht="16.5">
       <c r="A6" s="47">
         <v>5</v>
       </c>
@@ -6646,21 +6830,27 @@
       <c r="L6" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="M6" s="47">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="N6" s="47">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="O6" s="49">
-        <f t="shared" si="2"/>
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="P6" s="48"/>
-    </row>
-    <row r="7" spans="1:16" ht="16.5">
+      <c r="M6" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="N6" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="O6" s="47">
+        <f>COUNTIF(E6:H6,"참석")+COUNTIF(J6:N6,"참석")</f>
+        <v>6</v>
+      </c>
+      <c r="P6" s="47">
+        <f>COUNTIF(E6:H6,"참석")+COUNTIF(E6:H6,"불참")+COUNTIF(J6:N6,"참석")+COUNTIF(J6:N6,"불참")</f>
+        <v>9</v>
+      </c>
+      <c r="Q6" s="49">
+        <f>IF(P6=0,"",O6/P6)</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="R6" s="48"/>
+    </row>
+    <row r="7" spans="1:18" ht="16.5">
       <c r="A7" s="47">
         <v>6</v>
       </c>
@@ -6697,21 +6887,27 @@
       <c r="L7" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="M7" s="47">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="N7" s="47">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="O7" s="49">
-        <f t="shared" si="2"/>
+      <c r="M7" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="N7" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="O7" s="47">
+        <f>COUNTIF(E7:H7,"참석")+COUNTIF(J7:N7,"참석")</f>
+        <v>9</v>
+      </c>
+      <c r="P7" s="47">
+        <f>COUNTIF(E7:H7,"참석")+COUNTIF(E7:H7,"불참")+COUNTIF(J7:N7,"참석")+COUNTIF(J7:N7,"불참")</f>
+        <v>9</v>
+      </c>
+      <c r="Q7" s="49">
+        <f>IF(P7=0,"",O7/P7)</f>
         <v>1</v>
       </c>
-      <c r="P7" s="48"/>
-    </row>
-    <row r="8" spans="1:16" ht="16.5">
+      <c r="R7" s="48"/>
+    </row>
+    <row r="8" spans="1:18" ht="16.5">
       <c r="A8" s="47">
         <v>7</v>
       </c>
@@ -6746,21 +6942,27 @@
       <c r="L8" s="47" t="s">
         <v>173</v>
       </c>
-      <c r="M8" s="47">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="N8" s="47">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="O8" s="49">
-        <f t="shared" si="2"/>
-        <v>0.42857142857142855</v>
-      </c>
-      <c r="P8" s="48"/>
-    </row>
-    <row r="9" spans="1:16" ht="16.5">
+      <c r="M8" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="N8" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="O8" s="47">
+        <f>COUNTIF(E8:H8,"참석")+COUNTIF(J8:N8,"참석")</f>
+        <v>4</v>
+      </c>
+      <c r="P8" s="47">
+        <f>COUNTIF(E8:H8,"참석")+COUNTIF(E8:H8,"불참")+COUNTIF(J8:N8,"참석")+COUNTIF(J8:N8,"불참")</f>
+        <v>9</v>
+      </c>
+      <c r="Q8" s="49">
+        <f>IF(P8=0,"",O8/P8)</f>
+        <v>0.44444444444444442</v>
+      </c>
+      <c r="R8" s="48"/>
+    </row>
+    <row r="9" spans="1:18" ht="16.5">
       <c r="A9" s="47">
         <v>8</v>
       </c>
@@ -6797,23 +6999,29 @@
       <c r="L9" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="M9" s="47">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="N9" s="47">
-        <f t="shared" si="1"/>
+      <c r="M9" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="N9" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="O9" s="47">
+        <f>COUNTIF(E9:H9,"참석")+COUNTIF(J9:N9,"참석")</f>
         <v>5</v>
       </c>
-      <c r="O9" s="49">
-        <f t="shared" si="2"/>
-        <v>0.8</v>
-      </c>
-      <c r="P9" s="48" t="s">
+      <c r="P9" s="47">
+        <f>COUNTIF(E9:H9,"참석")+COUNTIF(E9:H9,"불참")+COUNTIF(J9:N9,"참석")+COUNTIF(J9:N9,"불참")</f>
+        <v>7</v>
+      </c>
+      <c r="Q9" s="49">
+        <f>IF(P9=0,"",O9/P9)</f>
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="R9" s="48" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="16.5">
+    <row r="10" spans="1:18" ht="16.5">
       <c r="A10" s="47">
         <v>9</v>
       </c>
@@ -6848,21 +7056,27 @@
       <c r="L10" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="M10" s="47">
-        <f t="shared" si="0"/>
+      <c r="M10" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="N10" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="O10" s="47">
+        <f>COUNTIF(E10:H10,"참석")+COUNTIF(J10:N10,"참석")</f>
         <v>4</v>
       </c>
-      <c r="N10" s="47">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="O10" s="49">
-        <f t="shared" si="2"/>
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="P10" s="48"/>
-    </row>
-    <row r="11" spans="1:16" ht="16.5">
+      <c r="P10" s="47">
+        <f>COUNTIF(E10:H10,"참석")+COUNTIF(E10:H10,"불참")+COUNTIF(J10:N10,"참석")+COUNTIF(J10:N10,"불참")</f>
+        <v>9</v>
+      </c>
+      <c r="Q10" s="49">
+        <f>IF(P10=0,"",O10/P10)</f>
+        <v>0.44444444444444442</v>
+      </c>
+      <c r="R10" s="48"/>
+    </row>
+    <row r="11" spans="1:18" ht="16.5">
       <c r="A11" s="47">
         <v>10</v>
       </c>
@@ -6897,21 +7111,27 @@
       <c r="L11" s="47" t="s">
         <v>173</v>
       </c>
-      <c r="M11" s="47">
-        <f t="shared" si="0"/>
+      <c r="M11" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="N11" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="O11" s="47">
+        <f>COUNTIF(E11:H11,"참석")+COUNTIF(J11:N11,"참석")</f>
         <v>3</v>
       </c>
-      <c r="N11" s="47">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="O11" s="49">
-        <f t="shared" si="2"/>
-        <v>0.42857142857142855</v>
-      </c>
-      <c r="P11" s="48"/>
-    </row>
-    <row r="12" spans="1:16" ht="16.5">
+      <c r="P11" s="47">
+        <f>COUNTIF(E11:H11,"참석")+COUNTIF(E11:H11,"불참")+COUNTIF(J11:N11,"참석")+COUNTIF(J11:N11,"불참")</f>
+        <v>9</v>
+      </c>
+      <c r="Q11" s="49">
+        <f>IF(P11=0,"",O11/P11)</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="R11" s="48"/>
+    </row>
+    <row r="12" spans="1:18" ht="16.5">
       <c r="A12" s="47">
         <v>11</v>
       </c>
@@ -6946,21 +7166,27 @@
       <c r="L12" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="M12" s="47">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="N12" s="47">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="O12" s="49">
-        <f t="shared" si="2"/>
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="P12" s="48"/>
-    </row>
-    <row r="13" spans="1:16" ht="16.5">
+      <c r="M12" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="N12" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="O12" s="47">
+        <f>COUNTIF(E12:H12,"참석")+COUNTIF(J12:N12,"참석")</f>
+        <v>6</v>
+      </c>
+      <c r="P12" s="47">
+        <f>COUNTIF(E12:H12,"참석")+COUNTIF(E12:H12,"불참")+COUNTIF(J12:N12,"참석")+COUNTIF(J12:N12,"불참")</f>
+        <v>9</v>
+      </c>
+      <c r="Q12" s="49">
+        <f>IF(P12=0,"",O12/P12)</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="R12" s="48"/>
+    </row>
+    <row r="13" spans="1:18" ht="16.5">
       <c r="A13" s="47">
         <v>12</v>
       </c>
@@ -6995,21 +7221,27 @@
       <c r="L13" s="47" t="s">
         <v>173</v>
       </c>
-      <c r="M13" s="47">
-        <f t="shared" si="0"/>
+      <c r="M13" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="N13" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="O13" s="47">
+        <f>COUNTIF(E13:H13,"참석")+COUNTIF(J13:N13,"참석")</f>
         <v>2</v>
       </c>
-      <c r="N13" s="47">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="O13" s="49">
-        <f t="shared" si="2"/>
-        <v>0.2857142857142857</v>
-      </c>
-      <c r="P13" s="48"/>
-    </row>
-    <row r="14" spans="1:16" ht="16.5">
+      <c r="P13" s="47">
+        <f>COUNTIF(E13:H13,"참석")+COUNTIF(E13:H13,"불참")+COUNTIF(J13:N13,"참석")+COUNTIF(J13:N13,"불참")</f>
+        <v>9</v>
+      </c>
+      <c r="Q13" s="49">
+        <f>IF(P13=0,"",O13/P13)</f>
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="R13" s="48"/>
+    </row>
+    <row r="14" spans="1:18" ht="16.5">
       <c r="A14" s="47">
         <v>13</v>
       </c>
@@ -7044,21 +7276,27 @@
       <c r="L14" s="47" t="s">
         <v>173</v>
       </c>
-      <c r="M14" s="47">
-        <f t="shared" si="0"/>
+      <c r="M14" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="N14" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="O14" s="47">
+        <f>COUNTIF(E14:H14,"참석")+COUNTIF(J14:N14,"참석")</f>
         <v>2</v>
       </c>
-      <c r="N14" s="47">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="O14" s="49">
-        <f t="shared" si="2"/>
-        <v>0.2857142857142857</v>
-      </c>
-      <c r="P14" s="48"/>
-    </row>
-    <row r="15" spans="1:16" ht="16.5">
+      <c r="P14" s="47">
+        <f>COUNTIF(E14:H14,"참석")+COUNTIF(E14:H14,"불참")+COUNTIF(J14:N14,"참석")+COUNTIF(J14:N14,"불참")</f>
+        <v>9</v>
+      </c>
+      <c r="Q14" s="49">
+        <f>IF(P14=0,"",O14/P14)</f>
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="R14" s="48"/>
+    </row>
+    <row r="15" spans="1:18" ht="16.5">
       <c r="A15" s="47">
         <v>14</v>
       </c>
@@ -7093,21 +7331,27 @@
       <c r="L15" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="M15" s="47">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="N15" s="47">
-        <f t="shared" si="1"/>
+      <c r="M15" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="N15" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="O15" s="47">
+        <f>COUNTIF(E15:H15,"참석")+COUNTIF(J15:N15,"참석")</f>
         <v>7</v>
       </c>
-      <c r="O15" s="49">
-        <f t="shared" si="2"/>
-        <v>0.8571428571428571</v>
-      </c>
-      <c r="P15" s="48"/>
-    </row>
-    <row r="16" spans="1:16" ht="16.5">
+      <c r="P15" s="47">
+        <f>COUNTIF(E15:H15,"참석")+COUNTIF(E15:H15,"불참")+COUNTIF(J15:N15,"참석")+COUNTIF(J15:N15,"불참")</f>
+        <v>9</v>
+      </c>
+      <c r="Q15" s="49">
+        <f>IF(P15=0,"",O15/P15)</f>
+        <v>0.77777777777777779</v>
+      </c>
+      <c r="R15" s="48"/>
+    </row>
+    <row r="16" spans="1:18" ht="16.5">
       <c r="A16" s="47">
         <v>15</v>
       </c>
@@ -7144,20 +7388,26 @@
       <c r="L16" s="47" t="s">
         <v>173</v>
       </c>
-      <c r="M16" s="47">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="N16" s="47">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="O16" s="49">
-        <f t="shared" si="2"/>
-        <v>0.42857142857142855</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" ht="16.5">
+      <c r="M16" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="N16" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="O16" s="47">
+        <f>COUNTIF(E16:H16,"참석")+COUNTIF(J16:N16,"참석")</f>
+        <v>4</v>
+      </c>
+      <c r="P16" s="47">
+        <f>COUNTIF(E16:H16,"참석")+COUNTIF(E16:H16,"불참")+COUNTIF(J16:N16,"참석")+COUNTIF(J16:N16,"불참")</f>
+        <v>9</v>
+      </c>
+      <c r="Q16" s="49">
+        <f>IF(P16=0,"",O16/P16)</f>
+        <v>0.44444444444444442</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="16.5">
       <c r="A17" s="47">
         <v>16</v>
       </c>
@@ -7192,20 +7442,26 @@
       <c r="L17" s="47" t="s">
         <v>173</v>
       </c>
-      <c r="M17" s="47">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="N17" s="47">
-        <f t="shared" si="1"/>
+      <c r="M17" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="N17" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="O17" s="47">
+        <f>COUNTIF(E17:H17,"참석")+COUNTIF(J17:N17,"참석")</f>
         <v>7</v>
       </c>
-      <c r="O17" s="49">
-        <f t="shared" si="2"/>
-        <v>0.7142857142857143</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" ht="16.5">
+      <c r="P17" s="47">
+        <f>COUNTIF(E17:H17,"참석")+COUNTIF(E17:H17,"불참")+COUNTIF(J17:N17,"참석")+COUNTIF(J17:N17,"불참")</f>
+        <v>9</v>
+      </c>
+      <c r="Q17" s="49">
+        <f>IF(P17=0,"",O17/P17)</f>
+        <v>0.77777777777777779</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="16.5">
       <c r="A18" s="47">
         <v>17</v>
       </c>
@@ -7240,20 +7496,26 @@
       <c r="L18" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="M18" s="47">
-        <f t="shared" si="0"/>
+      <c r="M18" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="N18" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="O18" s="47">
+        <f>COUNTIF(E18:H18,"참석")+COUNTIF(J18:N18,"참석")</f>
         <v>3</v>
       </c>
-      <c r="N18" s="47">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="O18" s="49">
-        <f t="shared" si="2"/>
-        <v>0.42857142857142855</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" ht="16.5">
+      <c r="P18" s="47">
+        <f>COUNTIF(E18:H18,"참석")+COUNTIF(E18:H18,"불참")+COUNTIF(J18:N18,"참석")+COUNTIF(J18:N18,"불참")</f>
+        <v>9</v>
+      </c>
+      <c r="Q18" s="49">
+        <f>IF(P18=0,"",O18/P18)</f>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="16.5">
       <c r="A19" s="47">
         <v>18</v>
       </c>
@@ -7288,23 +7550,29 @@
       <c r="L19" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="M19" s="47">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="N19" s="47">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="O19" s="49">
-        <f t="shared" si="2"/>
+      <c r="M19" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="N19" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="O19" s="47">
+        <f>COUNTIF(E19:H19,"참석")+COUNTIF(J19:N19,"참석")</f>
+        <v>6</v>
+      </c>
+      <c r="P19" s="47">
+        <f>COUNTIF(E19:H19,"참석")+COUNTIF(E19:H19,"불참")+COUNTIF(J19:N19,"참석")+COUNTIF(J19:N19,"불참")</f>
+        <v>6</v>
+      </c>
+      <c r="Q19" s="49">
+        <f>IF(P19=0,"",O19/P19)</f>
         <v>1</v>
       </c>
-      <c r="P19" s="46" t="s">
+      <c r="R19" s="46" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="16.5">
+    <row r="20" spans="1:18" ht="16.5">
       <c r="A20" s="47">
         <v>19</v>
       </c>
@@ -7339,20 +7607,26 @@
       <c r="L20" s="47" t="s">
         <v>173</v>
       </c>
-      <c r="M20" s="47">
-        <f t="shared" si="0"/>
+      <c r="M20" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="N20" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="O20" s="47">
+        <f>COUNTIF(E20:H20,"참석")+COUNTIF(J20:N20,"참석")</f>
         <v>5</v>
       </c>
-      <c r="N20" s="47">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="O20" s="49">
-        <f t="shared" si="2"/>
-        <v>0.7142857142857143</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" ht="16.5">
+      <c r="P20" s="47">
+        <f>COUNTIF(E20:H20,"참석")+COUNTIF(E20:H20,"불참")+COUNTIF(J20:N20,"참석")+COUNTIF(J20:N20,"불참")</f>
+        <v>9</v>
+      </c>
+      <c r="Q20" s="49">
+        <f>IF(P20=0,"",O20/P20)</f>
+        <v>0.55555555555555558</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" ht="16.5">
       <c r="A21" s="47">
         <v>20</v>
       </c>
@@ -7387,20 +7661,26 @@
       <c r="L21" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="M21" s="47">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="N21" s="47">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="O21" s="49">
-        <f t="shared" si="2"/>
-        <v>0.8571428571428571</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" ht="16.5">
+      <c r="M21" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="N21" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="O21" s="47">
+        <f>COUNTIF(E21:H21,"참석")+COUNTIF(J21:N21,"참석")</f>
+        <v>8</v>
+      </c>
+      <c r="P21" s="47">
+        <f>COUNTIF(E21:H21,"참석")+COUNTIF(E21:H21,"불참")+COUNTIF(J21:N21,"참석")+COUNTIF(J21:N21,"불참")</f>
+        <v>9</v>
+      </c>
+      <c r="Q21" s="49">
+        <f>IF(P21=0,"",O21/P21)</f>
+        <v>0.88888888888888884</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" ht="16.5">
       <c r="A22" s="47">
         <v>21</v>
       </c>
@@ -7435,20 +7715,26 @@
       <c r="L22" s="47" t="s">
         <v>173</v>
       </c>
-      <c r="M22" s="47">
-        <f t="shared" si="0"/>
+      <c r="M22" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="N22" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="O22" s="47">
+        <f>COUNTIF(E22:H22,"참석")+COUNTIF(J22:N22,"참석")</f>
         <v>3</v>
       </c>
-      <c r="N22" s="47">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="O22" s="49">
-        <f t="shared" si="2"/>
-        <v>0.42857142857142855</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" ht="16.5">
+      <c r="P22" s="47">
+        <f>COUNTIF(E22:H22,"참석")+COUNTIF(E22:H22,"불참")+COUNTIF(J22:N22,"참석")+COUNTIF(J22:N22,"불참")</f>
+        <v>9</v>
+      </c>
+      <c r="Q22" s="49">
+        <f>IF(P22=0,"",O22/P22)</f>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" ht="16.5">
       <c r="A23" s="47">
         <v>22</v>
       </c>
@@ -7483,20 +7769,26 @@
       <c r="L23" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="M23" s="47">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="N23" s="47">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="O23" s="49">
-        <f t="shared" si="2"/>
-        <v>0.7142857142857143</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" ht="16.5">
+      <c r="M23" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="N23" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="O23" s="47">
+        <f>COUNTIF(E23:H23,"참석")+COUNTIF(J23:N23,"참석")</f>
+        <v>6</v>
+      </c>
+      <c r="P23" s="47">
+        <f>COUNTIF(E23:H23,"참석")+COUNTIF(E23:H23,"불참")+COUNTIF(J23:N23,"참석")+COUNTIF(J23:N23,"불참")</f>
+        <v>9</v>
+      </c>
+      <c r="Q23" s="49">
+        <f>IF(P23=0,"",O23/P23)</f>
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" ht="16.5">
       <c r="A24" s="47">
         <v>23</v>
       </c>
@@ -7533,20 +7825,26 @@
       <c r="L24" s="47" t="s">
         <v>173</v>
       </c>
-      <c r="M24" s="47">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="N24" s="47">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="O24" s="49">
-        <f t="shared" si="2"/>
-        <v>0.2857142857142857</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" ht="16.5">
+      <c r="M24" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="N24" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="O24" s="47">
+        <f>COUNTIF(E24:H24,"참석")+COUNTIF(J24:N24,"참석")</f>
+        <v>3</v>
+      </c>
+      <c r="P24" s="47">
+        <f>COUNTIF(E24:H24,"참석")+COUNTIF(E24:H24,"불참")+COUNTIF(J24:N24,"참석")+COUNTIF(J24:N24,"불참")</f>
+        <v>9</v>
+      </c>
+      <c r="Q24" s="49">
+        <f>IF(P24=0,"",O24/P24)</f>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" ht="16.5">
       <c r="A25" s="47">
         <v>24</v>
       </c>
@@ -7581,20 +7879,26 @@
       <c r="L25" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="M25" s="47">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="N25" s="47">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="O25" s="49">
-        <f t="shared" si="2"/>
+      <c r="M25" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="N25" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="O25" s="47">
+        <f>COUNTIF(E25:H25,"참석")+COUNTIF(J25:N25,"참석")</f>
+        <v>9</v>
+      </c>
+      <c r="P25" s="47">
+        <f>COUNTIF(E25:H25,"참석")+COUNTIF(E25:H25,"불참")+COUNTIF(J25:N25,"참석")+COUNTIF(J25:N25,"불참")</f>
+        <v>9</v>
+      </c>
+      <c r="Q25" s="49">
+        <f>IF(P25=0,"",O25/P25)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="16.5">
+    <row r="26" spans="1:18" ht="16.5">
       <c r="A26" s="47">
         <v>25</v>
       </c>
@@ -7629,20 +7933,26 @@
       <c r="L26" s="47" t="s">
         <v>173</v>
       </c>
-      <c r="M26" s="47">
-        <f t="shared" si="0"/>
+      <c r="M26" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="N26" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="O26" s="47">
+        <f>COUNTIF(E26:H26,"참석")+COUNTIF(J26:N26,"참석")</f>
         <v>1</v>
       </c>
-      <c r="N26" s="47">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="O26" s="49">
-        <f t="shared" si="2"/>
-        <v>0.14285714285714285</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" ht="16.5">
+      <c r="P26" s="47">
+        <f>COUNTIF(E26:H26,"참석")+COUNTIF(E26:H26,"불참")+COUNTIF(J26:N26,"참석")+COUNTIF(J26:N26,"불참")</f>
+        <v>9</v>
+      </c>
+      <c r="Q26" s="49">
+        <f>IF(P26=0,"",O26/P26)</f>
+        <v>0.1111111111111111</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" ht="16.5">
       <c r="A27" s="47">
         <v>26</v>
       </c>
@@ -7677,20 +7987,26 @@
       <c r="L27" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="M27" s="47">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="N27" s="47">
-        <f t="shared" si="1"/>
+      <c r="M27" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="N27" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="O27" s="47">
+        <f>COUNTIF(E27:H27,"참석")+COUNTIF(J27:N27,"참석")</f>
         <v>7</v>
       </c>
-      <c r="O27" s="49">
-        <f t="shared" si="2"/>
-        <v>0.8571428571428571</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" ht="16.5">
+      <c r="P27" s="47">
+        <f>COUNTIF(E27:H27,"참석")+COUNTIF(E27:H27,"불참")+COUNTIF(J27:N27,"참석")+COUNTIF(J27:N27,"불참")</f>
+        <v>9</v>
+      </c>
+      <c r="Q27" s="49">
+        <f>IF(P27=0,"",O27/P27)</f>
+        <v>0.77777777777777779</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" ht="16.5">
       <c r="A28" s="47">
         <v>27</v>
       </c>
@@ -7725,20 +8041,26 @@
       <c r="L28" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="M28" s="47">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="N28" s="47">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="O28" s="49">
-        <f t="shared" si="2"/>
+      <c r="M28" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="N28" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="O28" s="47">
+        <f>COUNTIF(E28:H28,"참석")+COUNTIF(J28:N28,"참석")</f>
+        <v>9</v>
+      </c>
+      <c r="P28" s="47">
+        <f>COUNTIF(E28:H28,"참석")+COUNTIF(E28:H28,"불참")+COUNTIF(J28:N28,"참석")+COUNTIF(J28:N28,"불참")</f>
+        <v>9</v>
+      </c>
+      <c r="Q28" s="49">
+        <f>IF(P28=0,"",O28/P28)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="16.5">
+    <row r="29" spans="1:18" ht="16.5">
       <c r="A29" s="47">
         <v>28</v>
       </c>
@@ -7773,20 +8095,26 @@
       <c r="L29" s="47" t="s">
         <v>173</v>
       </c>
-      <c r="M29" s="47">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="N29" s="47">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="O29" s="49">
-        <f t="shared" si="2"/>
-        <v>0.2857142857142857</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" ht="16.5">
+      <c r="M29" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="N29" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="O29" s="47">
+        <f>COUNTIF(E29:H29,"참석")+COUNTIF(J29:N29,"참석")</f>
+        <v>3</v>
+      </c>
+      <c r="P29" s="47">
+        <f>COUNTIF(E29:H29,"참석")+COUNTIF(E29:H29,"불참")+COUNTIF(J29:N29,"참석")+COUNTIF(J29:N29,"불참")</f>
+        <v>9</v>
+      </c>
+      <c r="Q29" s="49">
+        <f>IF(P29=0,"",O29/P29)</f>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" ht="16.5">
       <c r="A30" s="47">
         <v>29</v>
       </c>
@@ -7818,20 +8146,26 @@
       <c r="L30" s="47" t="s">
         <v>173</v>
       </c>
-      <c r="M30" s="47">
-        <f t="shared" si="0"/>
+      <c r="M30" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="N30" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="O30" s="47">
+        <f>COUNTIF(E30:H30,"참석")+COUNTIF(J30:N30,"참석")</f>
         <v>1</v>
       </c>
-      <c r="N30" s="47">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="O30" s="49">
-        <f t="shared" si="2"/>
-        <v>0.14285714285714285</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" ht="16.5">
+      <c r="P30" s="47">
+        <f>COUNTIF(E30:H30,"참석")+COUNTIF(E30:H30,"불참")+COUNTIF(J30:N30,"참석")+COUNTIF(J30:N30,"불참")</f>
+        <v>9</v>
+      </c>
+      <c r="Q30" s="49">
+        <f>IF(P30=0,"",O30/P30)</f>
+        <v>0.1111111111111111</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" ht="16.5">
       <c r="E31" s="46">
         <f>COUNTIF(E2:E29,"참석")</f>
         <v>19</v>
@@ -7844,14 +8178,14 @@
         <f>COUNTIF(G2:G29,"참석")</f>
         <v>19</v>
       </c>
-      <c r="O31" s="49" t="str">
-        <f t="shared" ref="O31" si="3">IF(N31=0,"",M31/N31)</f>
+      <c r="Q31" s="49" t="str">
+        <f t="shared" ref="Q31" si="0">IF(P31=0,"",O31/P31)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P31" xr:uid="{C0625D6E-2678-482C-88B1-4B31BC9434B5}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P31">
+  <autoFilter ref="A1:R31" xr:uid="{C0625D6E-2678-482C-88B1-4B31BC9434B5}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R31">
       <sortCondition ref="C1:C31"/>
     </sortState>
   </autoFilter>

--- a/4기차세대경영자과정/차경 4기 정산서.xlsx
+++ b/4기차세대경영자과정/차경 4기 정산서.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Innobiz\Documents\innobiz-nextgen\4기차세대경영자과정\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB72138A-2308-4D72-9A59-6B03D6FA01E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5483A506-B3C5-438D-B2C2-725AB09541D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{404CE508-8F71-4CA4-99F0-0EFB79DB1227}"/>
   </bookViews>
@@ -6205,7 +6205,7 @@
         <v>44</v>
       </c>
       <c r="B47" s="71">
-        <v>1000000</v>
+        <v>500000</v>
       </c>
       <c r="C47" s="35">
         <v>46205</v>
@@ -6611,15 +6611,15 @@
         <v>234</v>
       </c>
       <c r="O2" s="47">
-        <f>COUNTIF(E2:H2,"참석")+COUNTIF(J2:N2,"참석")</f>
+        <f t="shared" ref="O2:O30" si="0">COUNTIF(E2:H2,"참석")+COUNTIF(J2:N2,"참석")</f>
         <v>9</v>
       </c>
       <c r="P2" s="47">
-        <f>COUNTIF(E2:H2,"참석")+COUNTIF(E2:H2,"불참")+COUNTIF(J2:N2,"참석")+COUNTIF(J2:N2,"불참")</f>
+        <f t="shared" ref="P2:P30" si="1">COUNTIF(E2:H2,"참석")+COUNTIF(E2:H2,"불참")+COUNTIF(J2:N2,"참석")+COUNTIF(J2:N2,"불참")</f>
         <v>9</v>
       </c>
       <c r="Q2" s="49">
-        <f>IF(P2=0,"",O2/P2)</f>
+        <f t="shared" ref="Q2:Q30" si="2">IF(P2=0,"",O2/P2)</f>
         <v>1</v>
       </c>
       <c r="R2" s="48"/>
@@ -6668,15 +6668,15 @@
         <v>234</v>
       </c>
       <c r="O3" s="47">
-        <f>COUNTIF(E3:H3,"참석")+COUNTIF(J3:N3,"참석")</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="P3" s="47">
-        <f>COUNTIF(E3:H3,"참석")+COUNTIF(E3:H3,"불참")+COUNTIF(J3:N3,"참석")+COUNTIF(J3:N3,"불참")</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="Q3" s="49">
-        <f>IF(P3=0,"",O3/P3)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="R3" s="48"/>
@@ -6725,15 +6725,15 @@
         <v>234</v>
       </c>
       <c r="O4" s="47">
-        <f>COUNTIF(E4:H4,"참석")+COUNTIF(J4:N4,"참석")</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="P4" s="47">
-        <f>COUNTIF(E4:H4,"참석")+COUNTIF(E4:H4,"불참")+COUNTIF(J4:N4,"참석")+COUNTIF(J4:N4,"불참")</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="Q4" s="49">
-        <f>IF(P4=0,"",O4/P4)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="R4" s="48"/>
@@ -6780,15 +6780,15 @@
         <v>234</v>
       </c>
       <c r="O5" s="47">
-        <f>COUNTIF(E5:H5,"참석")+COUNTIF(J5:N5,"참석")</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="P5" s="47">
-        <f>COUNTIF(E5:H5,"참석")+COUNTIF(E5:H5,"불참")+COUNTIF(J5:N5,"참석")+COUNTIF(J5:N5,"불참")</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="Q5" s="49">
-        <f>IF(P5=0,"",O5/P5)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="R5" s="48"/>
@@ -6837,15 +6837,15 @@
         <v>234</v>
       </c>
       <c r="O6" s="47">
-        <f>COUNTIF(E6:H6,"참석")+COUNTIF(J6:N6,"참석")</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="P6" s="47">
-        <f>COUNTIF(E6:H6,"참석")+COUNTIF(E6:H6,"불참")+COUNTIF(J6:N6,"참석")+COUNTIF(J6:N6,"불참")</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="Q6" s="49">
-        <f>IF(P6=0,"",O6/P6)</f>
+        <f t="shared" si="2"/>
         <v>0.66666666666666663</v>
       </c>
       <c r="R6" s="48"/>
@@ -6894,15 +6894,15 @@
         <v>234</v>
       </c>
       <c r="O7" s="47">
-        <f>COUNTIF(E7:H7,"참석")+COUNTIF(J7:N7,"참석")</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="P7" s="47">
-        <f>COUNTIF(E7:H7,"참석")+COUNTIF(E7:H7,"불참")+COUNTIF(J7:N7,"참석")+COUNTIF(J7:N7,"불참")</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="Q7" s="49">
-        <f>IF(P7=0,"",O7/P7)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="R7" s="48"/>
@@ -6949,15 +6949,15 @@
         <v>234</v>
       </c>
       <c r="O8" s="47">
-        <f>COUNTIF(E8:H8,"참석")+COUNTIF(J8:N8,"참석")</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="P8" s="47">
-        <f>COUNTIF(E8:H8,"참석")+COUNTIF(E8:H8,"불참")+COUNTIF(J8:N8,"참석")+COUNTIF(J8:N8,"불참")</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="Q8" s="49">
-        <f>IF(P8=0,"",O8/P8)</f>
+        <f t="shared" si="2"/>
         <v>0.44444444444444442</v>
       </c>
       <c r="R8" s="48"/>
@@ -7006,15 +7006,15 @@
         <v>234</v>
       </c>
       <c r="O9" s="47">
-        <f>COUNTIF(E9:H9,"참석")+COUNTIF(J9:N9,"참석")</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="P9" s="47">
-        <f>COUNTIF(E9:H9,"참석")+COUNTIF(E9:H9,"불참")+COUNTIF(J9:N9,"참석")+COUNTIF(J9:N9,"불참")</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="Q9" s="49">
-        <f>IF(P9=0,"",O9/P9)</f>
+        <f t="shared" si="2"/>
         <v>0.7142857142857143</v>
       </c>
       <c r="R9" s="48" t="s">
@@ -7063,15 +7063,15 @@
         <v>173</v>
       </c>
       <c r="O10" s="47">
-        <f>COUNTIF(E10:H10,"참석")+COUNTIF(J10:N10,"참석")</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="P10" s="47">
-        <f>COUNTIF(E10:H10,"참석")+COUNTIF(E10:H10,"불참")+COUNTIF(J10:N10,"참석")+COUNTIF(J10:N10,"불참")</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="Q10" s="49">
-        <f>IF(P10=0,"",O10/P10)</f>
+        <f t="shared" si="2"/>
         <v>0.44444444444444442</v>
       </c>
       <c r="R10" s="48"/>
@@ -7118,15 +7118,15 @@
         <v>173</v>
       </c>
       <c r="O11" s="47">
-        <f>COUNTIF(E11:H11,"참석")+COUNTIF(J11:N11,"참석")</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="P11" s="47">
-        <f>COUNTIF(E11:H11,"참석")+COUNTIF(E11:H11,"불참")+COUNTIF(J11:N11,"참석")+COUNTIF(J11:N11,"불참")</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="Q11" s="49">
-        <f>IF(P11=0,"",O11/P11)</f>
+        <f t="shared" si="2"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="R11" s="48"/>
@@ -7173,15 +7173,15 @@
         <v>234</v>
       </c>
       <c r="O12" s="47">
-        <f>COUNTIF(E12:H12,"참석")+COUNTIF(J12:N12,"참석")</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="P12" s="47">
-        <f>COUNTIF(E12:H12,"참석")+COUNTIF(E12:H12,"불참")+COUNTIF(J12:N12,"참석")+COUNTIF(J12:N12,"불참")</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="Q12" s="49">
-        <f>IF(P12=0,"",O12/P12)</f>
+        <f t="shared" si="2"/>
         <v>0.66666666666666663</v>
       </c>
       <c r="R12" s="48"/>
@@ -7228,15 +7228,15 @@
         <v>173</v>
       </c>
       <c r="O13" s="47">
-        <f>COUNTIF(E13:H13,"참석")+COUNTIF(J13:N13,"참석")</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="P13" s="47">
-        <f>COUNTIF(E13:H13,"참석")+COUNTIF(E13:H13,"불참")+COUNTIF(J13:N13,"참석")+COUNTIF(J13:N13,"불참")</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="Q13" s="49">
-        <f>IF(P13=0,"",O13/P13)</f>
+        <f t="shared" si="2"/>
         <v>0.22222222222222221</v>
       </c>
       <c r="R13" s="48"/>
@@ -7283,15 +7283,15 @@
         <v>173</v>
       </c>
       <c r="O14" s="47">
-        <f>COUNTIF(E14:H14,"참석")+COUNTIF(J14:N14,"참석")</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="P14" s="47">
-        <f>COUNTIF(E14:H14,"참석")+COUNTIF(E14:H14,"불참")+COUNTIF(J14:N14,"참석")+COUNTIF(J14:N14,"불참")</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="Q14" s="49">
-        <f>IF(P14=0,"",O14/P14)</f>
+        <f t="shared" si="2"/>
         <v>0.22222222222222221</v>
       </c>
       <c r="R14" s="48"/>
@@ -7338,15 +7338,15 @@
         <v>234</v>
       </c>
       <c r="O15" s="47">
-        <f>COUNTIF(E15:H15,"참석")+COUNTIF(J15:N15,"참석")</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="P15" s="47">
-        <f>COUNTIF(E15:H15,"참석")+COUNTIF(E15:H15,"불참")+COUNTIF(J15:N15,"참석")+COUNTIF(J15:N15,"불참")</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="Q15" s="49">
-        <f>IF(P15=0,"",O15/P15)</f>
+        <f t="shared" si="2"/>
         <v>0.77777777777777779</v>
       </c>
       <c r="R15" s="48"/>
@@ -7395,15 +7395,15 @@
         <v>234</v>
       </c>
       <c r="O16" s="47">
-        <f>COUNTIF(E16:H16,"참석")+COUNTIF(J16:N16,"참석")</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="P16" s="47">
-        <f>COUNTIF(E16:H16,"참석")+COUNTIF(E16:H16,"불참")+COUNTIF(J16:N16,"참석")+COUNTIF(J16:N16,"불참")</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="Q16" s="49">
-        <f>IF(P16=0,"",O16/P16)</f>
+        <f t="shared" si="2"/>
         <v>0.44444444444444442</v>
       </c>
     </row>
@@ -7449,15 +7449,15 @@
         <v>234</v>
       </c>
       <c r="O17" s="47">
-        <f>COUNTIF(E17:H17,"참석")+COUNTIF(J17:N17,"참석")</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="P17" s="47">
-        <f>COUNTIF(E17:H17,"참석")+COUNTIF(E17:H17,"불참")+COUNTIF(J17:N17,"참석")+COUNTIF(J17:N17,"불참")</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="Q17" s="49">
-        <f>IF(P17=0,"",O17/P17)</f>
+        <f t="shared" si="2"/>
         <v>0.77777777777777779</v>
       </c>
     </row>
@@ -7503,15 +7503,15 @@
         <v>173</v>
       </c>
       <c r="O18" s="47">
-        <f>COUNTIF(E18:H18,"참석")+COUNTIF(J18:N18,"참석")</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="P18" s="47">
-        <f>COUNTIF(E18:H18,"참석")+COUNTIF(E18:H18,"불참")+COUNTIF(J18:N18,"참석")+COUNTIF(J18:N18,"불참")</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="Q18" s="49">
-        <f>IF(P18=0,"",O18/P18)</f>
+        <f t="shared" si="2"/>
         <v>0.33333333333333331</v>
       </c>
     </row>
@@ -7557,15 +7557,15 @@
         <v>234</v>
       </c>
       <c r="O19" s="47">
-        <f>COUNTIF(E19:H19,"참석")+COUNTIF(J19:N19,"참석")</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="P19" s="47">
-        <f>COUNTIF(E19:H19,"참석")+COUNTIF(E19:H19,"불참")+COUNTIF(J19:N19,"참석")+COUNTIF(J19:N19,"불참")</f>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="Q19" s="49">
-        <f>IF(P19=0,"",O19/P19)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="R19" s="46" t="s">
@@ -7614,15 +7614,15 @@
         <v>173</v>
       </c>
       <c r="O20" s="47">
-        <f>COUNTIF(E20:H20,"참석")+COUNTIF(J20:N20,"참석")</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="P20" s="47">
-        <f>COUNTIF(E20:H20,"참석")+COUNTIF(E20:H20,"불참")+COUNTIF(J20:N20,"참석")+COUNTIF(J20:N20,"불참")</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="Q20" s="49">
-        <f>IF(P20=0,"",O20/P20)</f>
+        <f t="shared" si="2"/>
         <v>0.55555555555555558</v>
       </c>
     </row>
@@ -7668,15 +7668,15 @@
         <v>234</v>
       </c>
       <c r="O21" s="47">
-        <f>COUNTIF(E21:H21,"참석")+COUNTIF(J21:N21,"참석")</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="P21" s="47">
-        <f>COUNTIF(E21:H21,"참석")+COUNTIF(E21:H21,"불참")+COUNTIF(J21:N21,"참석")+COUNTIF(J21:N21,"불참")</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="Q21" s="49">
-        <f>IF(P21=0,"",O21/P21)</f>
+        <f t="shared" si="2"/>
         <v>0.88888888888888884</v>
       </c>
     </row>
@@ -7722,15 +7722,15 @@
         <v>173</v>
       </c>
       <c r="O22" s="47">
-        <f>COUNTIF(E22:H22,"참석")+COUNTIF(J22:N22,"참석")</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="P22" s="47">
-        <f>COUNTIF(E22:H22,"참석")+COUNTIF(E22:H22,"불참")+COUNTIF(J22:N22,"참석")+COUNTIF(J22:N22,"불참")</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="Q22" s="49">
-        <f>IF(P22=0,"",O22/P22)</f>
+        <f t="shared" si="2"/>
         <v>0.33333333333333331</v>
       </c>
     </row>
@@ -7776,15 +7776,15 @@
         <v>234</v>
       </c>
       <c r="O23" s="47">
-        <f>COUNTIF(E23:H23,"참석")+COUNTIF(J23:N23,"참석")</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="P23" s="47">
-        <f>COUNTIF(E23:H23,"참석")+COUNTIF(E23:H23,"불참")+COUNTIF(J23:N23,"참석")+COUNTIF(J23:N23,"불참")</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="Q23" s="49">
-        <f>IF(P23=0,"",O23/P23)</f>
+        <f t="shared" si="2"/>
         <v>0.66666666666666663</v>
       </c>
     </row>
@@ -7832,15 +7832,15 @@
         <v>234</v>
       </c>
       <c r="O24" s="47">
-        <f>COUNTIF(E24:H24,"참석")+COUNTIF(J24:N24,"참석")</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="P24" s="47">
-        <f>COUNTIF(E24:H24,"참석")+COUNTIF(E24:H24,"불참")+COUNTIF(J24:N24,"참석")+COUNTIF(J24:N24,"불참")</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="Q24" s="49">
-        <f>IF(P24=0,"",O24/P24)</f>
+        <f t="shared" si="2"/>
         <v>0.33333333333333331</v>
       </c>
     </row>
@@ -7886,15 +7886,15 @@
         <v>234</v>
       </c>
       <c r="O25" s="47">
-        <f>COUNTIF(E25:H25,"참석")+COUNTIF(J25:N25,"참석")</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="P25" s="47">
-        <f>COUNTIF(E25:H25,"참석")+COUNTIF(E25:H25,"불참")+COUNTIF(J25:N25,"참석")+COUNTIF(J25:N25,"불참")</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="Q25" s="49">
-        <f>IF(P25=0,"",O25/P25)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -7940,15 +7940,15 @@
         <v>173</v>
       </c>
       <c r="O26" s="47">
-        <f>COUNTIF(E26:H26,"참석")+COUNTIF(J26:N26,"참석")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="P26" s="47">
-        <f>COUNTIF(E26:H26,"참석")+COUNTIF(E26:H26,"불참")+COUNTIF(J26:N26,"참석")+COUNTIF(J26:N26,"불참")</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="Q26" s="49">
-        <f>IF(P26=0,"",O26/P26)</f>
+        <f t="shared" si="2"/>
         <v>0.1111111111111111</v>
       </c>
     </row>
@@ -7994,15 +7994,15 @@
         <v>234</v>
       </c>
       <c r="O27" s="47">
-        <f>COUNTIF(E27:H27,"참석")+COUNTIF(J27:N27,"참석")</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="P27" s="47">
-        <f>COUNTIF(E27:H27,"참석")+COUNTIF(E27:H27,"불참")+COUNTIF(J27:N27,"참석")+COUNTIF(J27:N27,"불참")</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="Q27" s="49">
-        <f>IF(P27=0,"",O27/P27)</f>
+        <f t="shared" si="2"/>
         <v>0.77777777777777779</v>
       </c>
     </row>
@@ -8048,15 +8048,15 @@
         <v>234</v>
       </c>
       <c r="O28" s="47">
-        <f>COUNTIF(E28:H28,"참석")+COUNTIF(J28:N28,"참석")</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="P28" s="47">
-        <f>COUNTIF(E28:H28,"참석")+COUNTIF(E28:H28,"불참")+COUNTIF(J28:N28,"참석")+COUNTIF(J28:N28,"불참")</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="Q28" s="49">
-        <f>IF(P28=0,"",O28/P28)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -8102,15 +8102,15 @@
         <v>234</v>
       </c>
       <c r="O29" s="47">
-        <f>COUNTIF(E29:H29,"참석")+COUNTIF(J29:N29,"참석")</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="P29" s="47">
-        <f>COUNTIF(E29:H29,"참석")+COUNTIF(E29:H29,"불참")+COUNTIF(J29:N29,"참석")+COUNTIF(J29:N29,"불참")</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="Q29" s="49">
-        <f>IF(P29=0,"",O29/P29)</f>
+        <f t="shared" si="2"/>
         <v>0.33333333333333331</v>
       </c>
     </row>
@@ -8153,15 +8153,15 @@
         <v>173</v>
       </c>
       <c r="O30" s="47">
-        <f>COUNTIF(E30:H30,"참석")+COUNTIF(J30:N30,"참석")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="P30" s="47">
-        <f>COUNTIF(E30:H30,"참석")+COUNTIF(E30:H30,"불참")+COUNTIF(J30:N30,"참석")+COUNTIF(J30:N30,"불참")</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="Q30" s="49">
-        <f>IF(P30=0,"",O30/P30)</f>
+        <f t="shared" si="2"/>
         <v>0.1111111111111111</v>
       </c>
     </row>
@@ -8179,7 +8179,7 @@
         <v>19</v>
       </c>
       <c r="Q31" s="49" t="str">
-        <f t="shared" ref="Q31" si="0">IF(P31=0,"",O31/P31)</f>
+        <f t="shared" ref="Q31" si="3">IF(P31=0,"",O31/P31)</f>
         <v/>
       </c>
     </row>

--- a/4기차세대경영자과정/차경 4기 정산서.xlsx
+++ b/4기차세대경영자과정/차경 4기 정산서.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Innobiz\Documents\innobiz-nextgen\4기차세대경영자과정\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5483A506-B3C5-438D-B2C2-725AB09541D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{757EDFC4-078B-4945-B66D-F93B2455052F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{404CE508-8F71-4CA4-99F0-0EFB79DB1227}"/>
   </bookViews>
@@ -1517,7 +1517,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="322">
   <si>
     <t>번호</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -2656,6 +2656,15 @@
   </si>
   <si>
     <t>10주(2026-07-10~11, 졸업여행)</t>
+  </si>
+  <si>
+    <t>상하이 전시회(NEPCON,SIA) 운영 용역 잔금 30%</t>
+  </si>
+  <si>
+    <t>해외전시</t>
+  </si>
+  <si>
+    <t>(주)인터메세항공</t>
   </si>
 </sst>
 </file>
@@ -5150,7 +5159,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{959FEF70-8578-4918-8CDC-E1B4AA8967DB}">
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="7.125" customWidth="1"/>
@@ -6290,6 +6299,29 @@
       </c>
       <c r="G50" s="2" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51">
+        <v>48</v>
+      </c>
+      <c r="B51" s="71">
+        <v>5472080</v>
+      </c>
+      <c r="C51" s="35">
+        <v>46209</v>
+      </c>
+      <c r="D51" s="34" t="s">
+        <v>319</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="F51" s="34" t="s">
+        <v>321</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/4기차세대경영자과정/차경 4기 정산서.xlsx
+++ b/4기차세대경영자과정/차경 4기 정산서.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Innobiz\Documents\innobiz-nextgen\4기차세대경영자과정\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{757EDFC4-078B-4945-B66D-F93B2455052F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30C695B9-A2B9-4AC0-A5E3-3CB40185F0FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{404CE508-8F71-4CA4-99F0-0EFB79DB1227}"/>
+    <workbookView xWindow="29310" yWindow="840" windowWidth="25500" windowHeight="14640" activeTab="3" xr2:uid="{404CE508-8F71-4CA4-99F0-0EFB79DB1227}"/>
   </bookViews>
   <sheets>
     <sheet name="항목별(피벗)" sheetId="9" r:id="rId1"/>
@@ -1517,7 +1517,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="323">
   <si>
     <t>번호</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -2665,6 +2665,10 @@
   </si>
   <si>
     <t>(주)인터메세항공</t>
+  </si>
+  <si>
+    <t>참석</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -7529,14 +7533,14 @@
         <v>234</v>
       </c>
       <c r="M18" s="47" t="s">
-        <v>173</v>
+        <v>322</v>
       </c>
       <c r="N18" s="47" t="s">
         <v>173</v>
       </c>
       <c r="O18" s="47">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P18" s="47">
         <f t="shared" si="1"/>
@@ -7544,7 +7548,7 @@
       </c>
       <c r="Q18" s="49">
         <f t="shared" si="2"/>
-        <v>0.33333333333333331</v>
+        <v>0.44444444444444442</v>
       </c>
     </row>
     <row r="19" spans="1:18" ht="16.5">

--- a/4기차세대경영자과정/차경 4기 정산서.xlsx
+++ b/4기차세대경영자과정/차경 4기 정산서.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Innobiz\Documents\innobiz-nextgen\4기차세대경영자과정\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30C695B9-A2B9-4AC0-A5E3-3CB40185F0FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1C7A3CB-92E9-4014-8AC6-064E766AA87B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29310" yWindow="840" windowWidth="25500" windowHeight="14640" activeTab="3" xr2:uid="{404CE508-8F71-4CA4-99F0-0EFB79DB1227}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{404CE508-8F71-4CA4-99F0-0EFB79DB1227}"/>
   </bookViews>
   <sheets>
     <sheet name="항목별(피벗)" sheetId="9" r:id="rId1"/>
@@ -23,7 +23,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">실수입내역!$A$3:$C$46</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">지출세부내역서!$A$3:$G$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'회차별 출석현황'!$A$1:$R$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'회차별 출석현황'!$A$1:$S$31</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1517,7 +1517,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="336">
   <si>
     <t>번호</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -2669,6 +2669,45 @@
   <si>
     <t>참석</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>강사비(김대식)</t>
+  </si>
+  <si>
+    <t>스타잇</t>
+  </si>
+  <si>
+    <t>진행비(김은정)</t>
+  </si>
+  <si>
+    <t>김은정</t>
+  </si>
+  <si>
+    <t>수료식 기념품(선물세트 60개)</t>
+  </si>
+  <si>
+    <t>기념품</t>
+  </si>
+  <si>
+    <t>(주)파르팜</t>
+  </si>
+  <si>
+    <t>식비(삼겹살두루치기)</t>
+  </si>
+  <si>
+    <t>삼겹살두루치기</t>
+  </si>
+  <si>
+    <t>수료식 현수막, 수료증 인쇄</t>
+  </si>
+  <si>
+    <t>다과비(카페두레브)</t>
+  </si>
+  <si>
+    <t>카페두레브</t>
+  </si>
+  <si>
+    <t>11주(2026-07-16, 수료식)</t>
   </si>
 </sst>
 </file>
@@ -5163,7 +5202,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{959FEF70-8578-4918-8CDC-E1B4AA8967DB}">
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="7.125" customWidth="1"/>
@@ -6326,6 +6365,167 @@
       </c>
       <c r="G51" s="2" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52">
+        <v>49</v>
+      </c>
+      <c r="B52" s="71">
+        <v>3300000</v>
+      </c>
+      <c r="C52" s="35">
+        <v>46219</v>
+      </c>
+      <c r="D52" s="34" t="s">
+        <v>323</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="F52" s="34" t="s">
+        <v>324</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53">
+        <v>50</v>
+      </c>
+      <c r="B53" s="71">
+        <v>500000</v>
+      </c>
+      <c r="C53" s="35">
+        <v>46219</v>
+      </c>
+      <c r="D53" s="34" t="s">
+        <v>325</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="F53" s="34" t="s">
+        <v>326</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54">
+        <v>51</v>
+      </c>
+      <c r="B54" s="71">
+        <v>2310000</v>
+      </c>
+      <c r="C54" s="35">
+        <v>46219</v>
+      </c>
+      <c r="D54" s="34" t="s">
+        <v>327</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="F54" s="34" t="s">
+        <v>329</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55">
+        <v>52</v>
+      </c>
+      <c r="B55" s="71">
+        <v>932000</v>
+      </c>
+      <c r="C55" s="35">
+        <v>46219</v>
+      </c>
+      <c r="D55" s="34" t="s">
+        <v>330</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="F55" s="34" t="s">
+        <v>331</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56">
+        <v>53</v>
+      </c>
+      <c r="B56" s="71">
+        <v>467500</v>
+      </c>
+      <c r="C56" s="35">
+        <v>46223</v>
+      </c>
+      <c r="D56" s="34" t="s">
+        <v>332</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F56" s="34" t="s">
+        <v>299</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57">
+        <v>54</v>
+      </c>
+      <c r="B57" s="71">
+        <v>200700</v>
+      </c>
+      <c r="C57" s="35">
+        <v>46217</v>
+      </c>
+      <c r="D57" s="34" t="s">
+        <v>333</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="F57" s="34" t="s">
+        <v>334</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58">
+        <v>55</v>
+      </c>
+      <c r="B58" s="71">
+        <v>160400</v>
+      </c>
+      <c r="C58" s="35">
+        <v>46219</v>
+      </c>
+      <c r="D58" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="F58" s="34" t="s">
+        <v>301</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -6534,20 +6734,20 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0625D6E-2678-482C-88B1-4B31BC9434B5}">
-  <dimension ref="A1:R31"/>
+  <dimension ref="A1:S31"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="8" style="46" customWidth="1"/>
     <col min="2" max="2" width="34" style="46" customWidth="1"/>
     <col min="3" max="4" width="12" style="46" customWidth="1"/>
-    <col min="5" max="14" width="16" style="46" customWidth="1"/>
-    <col min="15" max="16" width="12" style="46" customWidth="1"/>
-    <col min="17" max="17" width="10" style="46" customWidth="1"/>
-    <col min="18" max="18" width="30" style="46" customWidth="1"/>
-    <col min="19" max="16384" width="9" style="46"/>
+    <col min="5" max="15" width="16" style="46" customWidth="1"/>
+    <col min="16" max="17" width="12" style="46" customWidth="1"/>
+    <col min="18" max="18" width="10" style="46" customWidth="1"/>
+    <col min="19" max="19" width="30" style="46" customWidth="1"/>
+    <col min="20" max="16384" width="9" style="46"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="15">
+    <row r="1" spans="1:19" ht="15">
       <c r="A1" s="45" t="s">
         <v>149</v>
       </c>
@@ -6591,19 +6791,22 @@
         <v>318</v>
       </c>
       <c r="O1" s="45" t="s">
+        <v>335</v>
+      </c>
+      <c r="P1" s="45" t="s">
         <v>156</v>
       </c>
-      <c r="P1" s="45" t="s">
+      <c r="Q1" s="45" t="s">
         <v>157</v>
       </c>
-      <c r="Q1" s="45" t="s">
+      <c r="R1" s="45" t="s">
         <v>158</v>
       </c>
-      <c r="R1" s="45" t="s">
+      <c r="S1" s="45" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="16.5">
+    <row r="2" spans="1:19" ht="16.5">
       <c r="A2" s="47">
         <v>1</v>
       </c>
@@ -6646,21 +6849,24 @@
       <c r="N2" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="O2" s="47">
-        <f t="shared" ref="O2:O30" si="0">COUNTIF(E2:H2,"참석")+COUNTIF(J2:N2,"참석")</f>
-        <v>9</v>
+      <c r="O2" s="47" t="s">
+        <v>234</v>
       </c>
       <c r="P2" s="47">
-        <f t="shared" ref="P2:P30" si="1">COUNTIF(E2:H2,"참석")+COUNTIF(E2:H2,"불참")+COUNTIF(J2:N2,"참석")+COUNTIF(J2:N2,"불참")</f>
-        <v>9</v>
-      </c>
-      <c r="Q2" s="49">
-        <f t="shared" ref="Q2:Q30" si="2">IF(P2=0,"",O2/P2)</f>
+        <f>COUNTIF(E2:H2,"참석")+COUNTIF(J2:O2,"참석")</f>
+        <v>10</v>
+      </c>
+      <c r="Q2" s="47">
+        <f>COUNTIF(E2:H2,"참석")+COUNTIF(E2:H2,"불참")+COUNTIF(J2:O2,"참석")+COUNTIF(J2:O2,"불참")</f>
+        <v>10</v>
+      </c>
+      <c r="R2" s="49">
+        <f>IF(Q2=0,"",P2/Q2)</f>
         <v>1</v>
       </c>
-      <c r="R2" s="48"/>
-    </row>
-    <row r="3" spans="1:18" ht="16.5">
+      <c r="S2" s="48"/>
+    </row>
+    <row r="3" spans="1:19" ht="16.5">
       <c r="A3" s="47">
         <v>2</v>
       </c>
@@ -6703,21 +6909,24 @@
       <c r="N3" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="O3" s="47">
-        <f t="shared" si="0"/>
-        <v>9</v>
+      <c r="O3" s="47" t="s">
+        <v>234</v>
       </c>
       <c r="P3" s="47">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="Q3" s="49">
-        <f t="shared" si="2"/>
+        <f>COUNTIF(E3:H3,"참석")+COUNTIF(J3:O3,"참석")</f>
+        <v>10</v>
+      </c>
+      <c r="Q3" s="47">
+        <f>COUNTIF(E3:H3,"참석")+COUNTIF(E3:H3,"불참")+COUNTIF(J3:O3,"참석")+COUNTIF(J3:O3,"불참")</f>
+        <v>10</v>
+      </c>
+      <c r="R3" s="49">
+        <f>IF(Q3=0,"",P3/Q3)</f>
         <v>1</v>
       </c>
-      <c r="R3" s="48"/>
-    </row>
-    <row r="4" spans="1:18" ht="16.5">
+      <c r="S3" s="48"/>
+    </row>
+    <row r="4" spans="1:19" ht="16.5">
       <c r="A4" s="47">
         <v>3</v>
       </c>
@@ -6760,21 +6969,24 @@
       <c r="N4" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="O4" s="47">
-        <f t="shared" si="0"/>
-        <v>9</v>
+      <c r="O4" s="47" t="s">
+        <v>234</v>
       </c>
       <c r="P4" s="47">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="Q4" s="49">
-        <f t="shared" si="2"/>
+        <f>COUNTIF(E4:H4,"참석")+COUNTIF(J4:O4,"참석")</f>
+        <v>10</v>
+      </c>
+      <c r="Q4" s="47">
+        <f>COUNTIF(E4:H4,"참석")+COUNTIF(E4:H4,"불참")+COUNTIF(J4:O4,"참석")+COUNTIF(J4:O4,"불참")</f>
+        <v>10</v>
+      </c>
+      <c r="R4" s="49">
+        <f>IF(Q4=0,"",P4/Q4)</f>
         <v>1</v>
       </c>
-      <c r="R4" s="48"/>
-    </row>
-    <row r="5" spans="1:18" ht="16.5">
+      <c r="S4" s="48"/>
+    </row>
+    <row r="5" spans="1:19" ht="16.5">
       <c r="A5" s="47">
         <v>4</v>
       </c>
@@ -6815,21 +7027,24 @@
       <c r="N5" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="O5" s="47">
-        <f t="shared" si="0"/>
-        <v>9</v>
+      <c r="O5" s="47" t="s">
+        <v>234</v>
       </c>
       <c r="P5" s="47">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="Q5" s="49">
-        <f t="shared" si="2"/>
+        <f>COUNTIF(E5:H5,"참석")+COUNTIF(J5:O5,"참석")</f>
+        <v>10</v>
+      </c>
+      <c r="Q5" s="47">
+        <f>COUNTIF(E5:H5,"참석")+COUNTIF(E5:H5,"불참")+COUNTIF(J5:O5,"참석")+COUNTIF(J5:O5,"불참")</f>
+        <v>10</v>
+      </c>
+      <c r="R5" s="49">
+        <f>IF(Q5=0,"",P5/Q5)</f>
         <v>1</v>
       </c>
-      <c r="R5" s="48"/>
-    </row>
-    <row r="6" spans="1:18" ht="16.5">
+      <c r="S5" s="48"/>
+    </row>
+    <row r="6" spans="1:19" ht="16.5">
       <c r="A6" s="47">
         <v>5</v>
       </c>
@@ -6872,21 +7087,24 @@
       <c r="N6" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="O6" s="47">
-        <f t="shared" si="0"/>
-        <v>6</v>
+      <c r="O6" s="47" t="s">
+        <v>234</v>
       </c>
       <c r="P6" s="47">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="Q6" s="49">
-        <f t="shared" si="2"/>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="R6" s="48"/>
-    </row>
-    <row r="7" spans="1:18" ht="16.5">
+        <f>COUNTIF(E6:H6,"참석")+COUNTIF(J6:O6,"참석")</f>
+        <v>7</v>
+      </c>
+      <c r="Q6" s="47">
+        <f>COUNTIF(E6:H6,"참석")+COUNTIF(E6:H6,"불참")+COUNTIF(J6:O6,"참석")+COUNTIF(J6:O6,"불참")</f>
+        <v>10</v>
+      </c>
+      <c r="R6" s="49">
+        <f>IF(Q6=0,"",P6/Q6)</f>
+        <v>0.7</v>
+      </c>
+      <c r="S6" s="48"/>
+    </row>
+    <row r="7" spans="1:19" ht="16.5">
       <c r="A7" s="47">
         <v>6</v>
       </c>
@@ -6929,21 +7147,24 @@
       <c r="N7" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="O7" s="47">
-        <f t="shared" si="0"/>
-        <v>9</v>
+      <c r="O7" s="47" t="s">
+        <v>234</v>
       </c>
       <c r="P7" s="47">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="Q7" s="49">
-        <f t="shared" si="2"/>
+        <f>COUNTIF(E7:H7,"참석")+COUNTIF(J7:O7,"참석")</f>
+        <v>10</v>
+      </c>
+      <c r="Q7" s="47">
+        <f>COUNTIF(E7:H7,"참석")+COUNTIF(E7:H7,"불참")+COUNTIF(J7:O7,"참석")+COUNTIF(J7:O7,"불참")</f>
+        <v>10</v>
+      </c>
+      <c r="R7" s="49">
+        <f>IF(Q7=0,"",P7/Q7)</f>
         <v>1</v>
       </c>
-      <c r="R7" s="48"/>
-    </row>
-    <row r="8" spans="1:18" ht="16.5">
+      <c r="S7" s="48"/>
+    </row>
+    <row r="8" spans="1:19" ht="16.5">
       <c r="A8" s="47">
         <v>7</v>
       </c>
@@ -6984,21 +7205,24 @@
       <c r="N8" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="O8" s="47">
-        <f t="shared" si="0"/>
+      <c r="O8" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="P8" s="47">
+        <f>COUNTIF(E8:H8,"참석")+COUNTIF(J8:O8,"참석")</f>
         <v>4</v>
       </c>
-      <c r="P8" s="47">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="Q8" s="49">
-        <f t="shared" si="2"/>
-        <v>0.44444444444444442</v>
-      </c>
-      <c r="R8" s="48"/>
-    </row>
-    <row r="9" spans="1:18" ht="16.5">
+      <c r="Q8" s="47">
+        <f>COUNTIF(E8:H8,"참석")+COUNTIF(E8:H8,"불참")+COUNTIF(J8:O8,"참석")+COUNTIF(J8:O8,"불참")</f>
+        <v>10</v>
+      </c>
+      <c r="R8" s="49">
+        <f>IF(Q8=0,"",P8/Q8)</f>
+        <v>0.4</v>
+      </c>
+      <c r="S8" s="48"/>
+    </row>
+    <row r="9" spans="1:19" ht="16.5">
       <c r="A9" s="47">
         <v>8</v>
       </c>
@@ -7041,23 +7265,26 @@
       <c r="N9" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="O9" s="47">
-        <f t="shared" si="0"/>
-        <v>5</v>
+      <c r="O9" s="47" t="s">
+        <v>234</v>
       </c>
       <c r="P9" s="47">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="Q9" s="49">
-        <f t="shared" si="2"/>
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="R9" s="48" t="s">
+        <f>COUNTIF(E9:H9,"참석")+COUNTIF(J9:O9,"참석")</f>
+        <v>6</v>
+      </c>
+      <c r="Q9" s="47">
+        <f>COUNTIF(E9:H9,"참석")+COUNTIF(E9:H9,"불참")+COUNTIF(J9:O9,"참석")+COUNTIF(J9:O9,"불참")</f>
+        <v>8</v>
+      </c>
+      <c r="R9" s="49">
+        <f>IF(Q9=0,"",P9/Q9)</f>
+        <v>0.75</v>
+      </c>
+      <c r="S9" s="48" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="16.5">
+    <row r="10" spans="1:19" ht="16.5">
       <c r="A10" s="47">
         <v>9</v>
       </c>
@@ -7098,21 +7325,24 @@
       <c r="N10" s="47" t="s">
         <v>173</v>
       </c>
-      <c r="O10" s="47">
-        <f t="shared" si="0"/>
+      <c r="O10" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="P10" s="47">
+        <f>COUNTIF(E10:H10,"참석")+COUNTIF(J10:O10,"참석")</f>
         <v>4</v>
       </c>
-      <c r="P10" s="47">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="Q10" s="49">
-        <f t="shared" si="2"/>
-        <v>0.44444444444444442</v>
-      </c>
-      <c r="R10" s="48"/>
-    </row>
-    <row r="11" spans="1:18" ht="16.5">
+      <c r="Q10" s="47">
+        <f>COUNTIF(E10:H10,"참석")+COUNTIF(E10:H10,"불참")+COUNTIF(J10:O10,"참석")+COUNTIF(J10:O10,"불참")</f>
+        <v>10</v>
+      </c>
+      <c r="R10" s="49">
+        <f>IF(Q10=0,"",P10/Q10)</f>
+        <v>0.4</v>
+      </c>
+      <c r="S10" s="48"/>
+    </row>
+    <row r="11" spans="1:19" ht="16.5">
       <c r="A11" s="47">
         <v>10</v>
       </c>
@@ -7153,21 +7383,24 @@
       <c r="N11" s="47" t="s">
         <v>173</v>
       </c>
-      <c r="O11" s="47">
-        <f t="shared" si="0"/>
+      <c r="O11" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="P11" s="47">
+        <f>COUNTIF(E11:H11,"참석")+COUNTIF(J11:O11,"참석")</f>
         <v>3</v>
       </c>
-      <c r="P11" s="47">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="Q11" s="49">
-        <f t="shared" si="2"/>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="R11" s="48"/>
-    </row>
-    <row r="12" spans="1:18" ht="16.5">
+      <c r="Q11" s="47">
+        <f>COUNTIF(E11:H11,"참석")+COUNTIF(E11:H11,"불참")+COUNTIF(J11:O11,"참석")+COUNTIF(J11:O11,"불참")</f>
+        <v>10</v>
+      </c>
+      <c r="R11" s="49">
+        <f>IF(Q11=0,"",P11/Q11)</f>
+        <v>0.3</v>
+      </c>
+      <c r="S11" s="48"/>
+    </row>
+    <row r="12" spans="1:19" ht="16.5">
       <c r="A12" s="47">
         <v>11</v>
       </c>
@@ -7208,21 +7441,24 @@
       <c r="N12" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="O12" s="47">
-        <f t="shared" si="0"/>
-        <v>6</v>
+      <c r="O12" s="47" t="s">
+        <v>234</v>
       </c>
       <c r="P12" s="47">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="Q12" s="49">
-        <f t="shared" si="2"/>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="R12" s="48"/>
-    </row>
-    <row r="13" spans="1:18" ht="16.5">
+        <f>COUNTIF(E12:H12,"참석")+COUNTIF(J12:O12,"참석")</f>
+        <v>7</v>
+      </c>
+      <c r="Q12" s="47">
+        <f>COUNTIF(E12:H12,"참석")+COUNTIF(E12:H12,"불참")+COUNTIF(J12:O12,"참석")+COUNTIF(J12:O12,"불참")</f>
+        <v>10</v>
+      </c>
+      <c r="R12" s="49">
+        <f>IF(Q12=0,"",P12/Q12)</f>
+        <v>0.7</v>
+      </c>
+      <c r="S12" s="48"/>
+    </row>
+    <row r="13" spans="1:19" ht="16.5">
       <c r="A13" s="47">
         <v>12</v>
       </c>
@@ -7263,21 +7499,24 @@
       <c r="N13" s="47" t="s">
         <v>173</v>
       </c>
-      <c r="O13" s="47">
-        <f t="shared" si="0"/>
-        <v>2</v>
+      <c r="O13" s="47" t="s">
+        <v>234</v>
       </c>
       <c r="P13" s="47">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="Q13" s="49">
-        <f t="shared" si="2"/>
-        <v>0.22222222222222221</v>
-      </c>
-      <c r="R13" s="48"/>
-    </row>
-    <row r="14" spans="1:18" ht="16.5">
+        <f>COUNTIF(E13:H13,"참석")+COUNTIF(J13:O13,"참석")</f>
+        <v>3</v>
+      </c>
+      <c r="Q13" s="47">
+        <f>COUNTIF(E13:H13,"참석")+COUNTIF(E13:H13,"불참")+COUNTIF(J13:O13,"참석")+COUNTIF(J13:O13,"불참")</f>
+        <v>10</v>
+      </c>
+      <c r="R13" s="49">
+        <f>IF(Q13=0,"",P13/Q13)</f>
+        <v>0.3</v>
+      </c>
+      <c r="S13" s="48"/>
+    </row>
+    <row r="14" spans="1:19" ht="16.5">
       <c r="A14" s="47">
         <v>13</v>
       </c>
@@ -7318,21 +7557,24 @@
       <c r="N14" s="47" t="s">
         <v>173</v>
       </c>
-      <c r="O14" s="47">
-        <f t="shared" si="0"/>
+      <c r="O14" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="P14" s="47">
+        <f>COUNTIF(E14:H14,"참석")+COUNTIF(J14:O14,"참석")</f>
         <v>2</v>
       </c>
-      <c r="P14" s="47">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="Q14" s="49">
-        <f t="shared" si="2"/>
-        <v>0.22222222222222221</v>
-      </c>
-      <c r="R14" s="48"/>
-    </row>
-    <row r="15" spans="1:18" ht="16.5">
+      <c r="Q14" s="47">
+        <f>COUNTIF(E14:H14,"참석")+COUNTIF(E14:H14,"불참")+COUNTIF(J14:O14,"참석")+COUNTIF(J14:O14,"불참")</f>
+        <v>10</v>
+      </c>
+      <c r="R14" s="49">
+        <f>IF(Q14=0,"",P14/Q14)</f>
+        <v>0.2</v>
+      </c>
+      <c r="S14" s="48"/>
+    </row>
+    <row r="15" spans="1:19" ht="16.5">
       <c r="A15" s="47">
         <v>14</v>
       </c>
@@ -7373,21 +7615,24 @@
       <c r="N15" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="O15" s="47">
-        <f t="shared" si="0"/>
-        <v>7</v>
+      <c r="O15" s="47" t="s">
+        <v>234</v>
       </c>
       <c r="P15" s="47">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="Q15" s="49">
-        <f t="shared" si="2"/>
-        <v>0.77777777777777779</v>
-      </c>
-      <c r="R15" s="48"/>
-    </row>
-    <row r="16" spans="1:18" ht="16.5">
+        <f>COUNTIF(E15:H15,"참석")+COUNTIF(J15:O15,"참석")</f>
+        <v>8</v>
+      </c>
+      <c r="Q15" s="47">
+        <f>COUNTIF(E15:H15,"참석")+COUNTIF(E15:H15,"불참")+COUNTIF(J15:O15,"참석")+COUNTIF(J15:O15,"불참")</f>
+        <v>10</v>
+      </c>
+      <c r="R15" s="49">
+        <f>IF(Q15=0,"",P15/Q15)</f>
+        <v>0.8</v>
+      </c>
+      <c r="S15" s="48"/>
+    </row>
+    <row r="16" spans="1:19" ht="16.5">
       <c r="A16" s="47">
         <v>15</v>
       </c>
@@ -7430,20 +7675,23 @@
       <c r="N16" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="O16" s="47">
-        <f t="shared" si="0"/>
+      <c r="O16" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="P16" s="47">
+        <f>COUNTIF(E16:H16,"참석")+COUNTIF(J16:O16,"참석")</f>
         <v>4</v>
       </c>
-      <c r="P16" s="47">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="Q16" s="49">
-        <f t="shared" si="2"/>
-        <v>0.44444444444444442</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" ht="16.5">
+      <c r="Q16" s="47">
+        <f>COUNTIF(E16:H16,"참석")+COUNTIF(E16:H16,"불참")+COUNTIF(J16:O16,"참석")+COUNTIF(J16:O16,"불참")</f>
+        <v>10</v>
+      </c>
+      <c r="R16" s="49">
+        <f>IF(Q16=0,"",P16/Q16)</f>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" ht="16.5">
       <c r="A17" s="47">
         <v>16</v>
       </c>
@@ -7484,20 +7732,23 @@
       <c r="N17" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="O17" s="47">
-        <f t="shared" si="0"/>
-        <v>7</v>
+      <c r="O17" s="47" t="s">
+        <v>234</v>
       </c>
       <c r="P17" s="47">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="Q17" s="49">
-        <f t="shared" si="2"/>
-        <v>0.77777777777777779</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" ht="16.5">
+        <f>COUNTIF(E17:H17,"참석")+COUNTIF(J17:O17,"참석")</f>
+        <v>8</v>
+      </c>
+      <c r="Q17" s="47">
+        <f>COUNTIF(E17:H17,"참석")+COUNTIF(E17:H17,"불참")+COUNTIF(J17:O17,"참석")+COUNTIF(J17:O17,"불참")</f>
+        <v>10</v>
+      </c>
+      <c r="R17" s="49">
+        <f>IF(Q17=0,"",P17/Q17)</f>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" ht="16.5">
       <c r="A18" s="47">
         <v>17</v>
       </c>
@@ -7538,20 +7789,23 @@
       <c r="N18" s="47" t="s">
         <v>173</v>
       </c>
-      <c r="O18" s="47">
-        <f t="shared" si="0"/>
+      <c r="O18" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="P18" s="47">
+        <f>COUNTIF(E18:H18,"참석")+COUNTIF(J18:O18,"참석")</f>
         <v>4</v>
       </c>
-      <c r="P18" s="47">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="Q18" s="49">
-        <f t="shared" si="2"/>
-        <v>0.44444444444444442</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" ht="16.5">
+      <c r="Q18" s="47">
+        <f>COUNTIF(E18:H18,"참석")+COUNTIF(E18:H18,"불참")+COUNTIF(J18:O18,"참석")+COUNTIF(J18:O18,"불참")</f>
+        <v>10</v>
+      </c>
+      <c r="R18" s="49">
+        <f>IF(Q18=0,"",P18/Q18)</f>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" ht="16.5">
       <c r="A19" s="47">
         <v>18</v>
       </c>
@@ -7592,23 +7846,26 @@
       <c r="N19" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="O19" s="47">
-        <f t="shared" si="0"/>
-        <v>6</v>
+      <c r="O19" s="47" t="s">
+        <v>234</v>
       </c>
       <c r="P19" s="47">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="Q19" s="49">
-        <f t="shared" si="2"/>
+        <f>COUNTIF(E19:H19,"참석")+COUNTIF(J19:O19,"참석")</f>
+        <v>7</v>
+      </c>
+      <c r="Q19" s="47">
+        <f>COUNTIF(E19:H19,"참석")+COUNTIF(E19:H19,"불참")+COUNTIF(J19:O19,"참석")+COUNTIF(J19:O19,"불참")</f>
+        <v>7</v>
+      </c>
+      <c r="R19" s="49">
+        <f>IF(Q19=0,"",P19/Q19)</f>
         <v>1</v>
       </c>
-      <c r="R19" s="46" t="s">
+      <c r="S19" s="46" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="16.5">
+    <row r="20" spans="1:19" ht="16.5">
       <c r="A20" s="47">
         <v>19</v>
       </c>
@@ -7649,20 +7906,23 @@
       <c r="N20" s="47" t="s">
         <v>173</v>
       </c>
-      <c r="O20" s="47">
-        <f t="shared" si="0"/>
+      <c r="O20" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="P20" s="47">
+        <f>COUNTIF(E20:H20,"참석")+COUNTIF(J20:O20,"참석")</f>
         <v>5</v>
       </c>
-      <c r="P20" s="47">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="Q20" s="49">
-        <f t="shared" si="2"/>
-        <v>0.55555555555555558</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" ht="16.5">
+      <c r="Q20" s="47">
+        <f>COUNTIF(E20:H20,"참석")+COUNTIF(E20:H20,"불참")+COUNTIF(J20:O20,"참석")+COUNTIF(J20:O20,"불참")</f>
+        <v>10</v>
+      </c>
+      <c r="R20" s="49">
+        <f>IF(Q20=0,"",P20/Q20)</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" ht="16.5">
       <c r="A21" s="47">
         <v>20</v>
       </c>
@@ -7703,20 +7963,23 @@
       <c r="N21" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="O21" s="47">
-        <f t="shared" si="0"/>
-        <v>8</v>
+      <c r="O21" s="47" t="s">
+        <v>234</v>
       </c>
       <c r="P21" s="47">
-        <f t="shared" si="1"/>
+        <f>COUNTIF(E21:H21,"참석")+COUNTIF(J21:O21,"참석")</f>
         <v>9</v>
       </c>
-      <c r="Q21" s="49">
-        <f t="shared" si="2"/>
-        <v>0.88888888888888884</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" ht="16.5">
+      <c r="Q21" s="47">
+        <f>COUNTIF(E21:H21,"참석")+COUNTIF(E21:H21,"불참")+COUNTIF(J21:O21,"참석")+COUNTIF(J21:O21,"불참")</f>
+        <v>10</v>
+      </c>
+      <c r="R21" s="49">
+        <f>IF(Q21=0,"",P21/Q21)</f>
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" ht="16.5">
       <c r="A22" s="47">
         <v>21</v>
       </c>
@@ -7757,20 +8020,23 @@
       <c r="N22" s="47" t="s">
         <v>173</v>
       </c>
-      <c r="O22" s="47">
-        <f t="shared" si="0"/>
-        <v>3</v>
+      <c r="O22" s="47" t="s">
+        <v>234</v>
       </c>
       <c r="P22" s="47">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="Q22" s="49">
-        <f t="shared" si="2"/>
-        <v>0.33333333333333331</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" ht="16.5">
+        <f>COUNTIF(E22:H22,"참석")+COUNTIF(J22:O22,"참석")</f>
+        <v>4</v>
+      </c>
+      <c r="Q22" s="47">
+        <f>COUNTIF(E22:H22,"참석")+COUNTIF(E22:H22,"불참")+COUNTIF(J22:O22,"참석")+COUNTIF(J22:O22,"불참")</f>
+        <v>10</v>
+      </c>
+      <c r="R22" s="49">
+        <f>IF(Q22=0,"",P22/Q22)</f>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" ht="16.5">
       <c r="A23" s="47">
         <v>22</v>
       </c>
@@ -7811,20 +8077,23 @@
       <c r="N23" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="O23" s="47">
-        <f t="shared" si="0"/>
-        <v>6</v>
+      <c r="O23" s="47" t="s">
+        <v>234</v>
       </c>
       <c r="P23" s="47">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="Q23" s="49">
-        <f t="shared" si="2"/>
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" ht="16.5">
+        <f>COUNTIF(E23:H23,"참석")+COUNTIF(J23:O23,"참석")</f>
+        <v>7</v>
+      </c>
+      <c r="Q23" s="47">
+        <f>COUNTIF(E23:H23,"참석")+COUNTIF(E23:H23,"불참")+COUNTIF(J23:O23,"참석")+COUNTIF(J23:O23,"불참")</f>
+        <v>10</v>
+      </c>
+      <c r="R23" s="49">
+        <f>IF(Q23=0,"",P23/Q23)</f>
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" ht="16.5">
       <c r="A24" s="47">
         <v>23</v>
       </c>
@@ -7867,20 +8136,23 @@
       <c r="N24" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="O24" s="47">
-        <f t="shared" si="0"/>
-        <v>3</v>
+      <c r="O24" s="47" t="s">
+        <v>234</v>
       </c>
       <c r="P24" s="47">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="Q24" s="49">
-        <f t="shared" si="2"/>
-        <v>0.33333333333333331</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" ht="16.5">
+        <f>COUNTIF(E24:H24,"참석")+COUNTIF(J24:O24,"참석")</f>
+        <v>4</v>
+      </c>
+      <c r="Q24" s="47">
+        <f>COUNTIF(E24:H24,"참석")+COUNTIF(E24:H24,"불참")+COUNTIF(J24:O24,"참석")+COUNTIF(J24:O24,"불참")</f>
+        <v>10</v>
+      </c>
+      <c r="R24" s="49">
+        <f>IF(Q24=0,"",P24/Q24)</f>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" ht="16.5">
       <c r="A25" s="47">
         <v>24</v>
       </c>
@@ -7921,20 +8193,23 @@
       <c r="N25" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="O25" s="47">
-        <f t="shared" si="0"/>
-        <v>9</v>
+      <c r="O25" s="47" t="s">
+        <v>234</v>
       </c>
       <c r="P25" s="47">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="Q25" s="49">
-        <f t="shared" si="2"/>
+        <f>COUNTIF(E25:H25,"참석")+COUNTIF(J25:O25,"참석")</f>
+        <v>10</v>
+      </c>
+      <c r="Q25" s="47">
+        <f>COUNTIF(E25:H25,"참석")+COUNTIF(E25:H25,"불참")+COUNTIF(J25:O25,"참석")+COUNTIF(J25:O25,"불참")</f>
+        <v>10</v>
+      </c>
+      <c r="R25" s="49">
+        <f>IF(Q25=0,"",P25/Q25)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="16.5">
+    <row r="26" spans="1:19" ht="16.5">
       <c r="A26" s="47">
         <v>25</v>
       </c>
@@ -7975,20 +8250,23 @@
       <c r="N26" s="47" t="s">
         <v>173</v>
       </c>
-      <c r="O26" s="47">
-        <f t="shared" si="0"/>
+      <c r="O26" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="P26" s="47">
+        <f>COUNTIF(E26:H26,"참석")+COUNTIF(J26:O26,"참석")</f>
         <v>1</v>
       </c>
-      <c r="P26" s="47">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="Q26" s="49">
-        <f t="shared" si="2"/>
-        <v>0.1111111111111111</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" ht="16.5">
+      <c r="Q26" s="47">
+        <f>COUNTIF(E26:H26,"참석")+COUNTIF(E26:H26,"불참")+COUNTIF(J26:O26,"참석")+COUNTIF(J26:O26,"불참")</f>
+        <v>10</v>
+      </c>
+      <c r="R26" s="49">
+        <f>IF(Q26=0,"",P26/Q26)</f>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" ht="16.5">
       <c r="A27" s="47">
         <v>26</v>
       </c>
@@ -8029,20 +8307,23 @@
       <c r="N27" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="O27" s="47">
-        <f t="shared" si="0"/>
-        <v>7</v>
+      <c r="O27" s="47" t="s">
+        <v>234</v>
       </c>
       <c r="P27" s="47">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="Q27" s="49">
-        <f t="shared" si="2"/>
-        <v>0.77777777777777779</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" ht="16.5">
+        <f>COUNTIF(E27:H27,"참석")+COUNTIF(J27:O27,"참석")</f>
+        <v>8</v>
+      </c>
+      <c r="Q27" s="47">
+        <f>COUNTIF(E27:H27,"참석")+COUNTIF(E27:H27,"불참")+COUNTIF(J27:O27,"참석")+COUNTIF(J27:O27,"불참")</f>
+        <v>10</v>
+      </c>
+      <c r="R27" s="49">
+        <f>IF(Q27=0,"",P27/Q27)</f>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" ht="16.5">
       <c r="A28" s="47">
         <v>27</v>
       </c>
@@ -8083,20 +8364,23 @@
       <c r="N28" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="O28" s="47">
-        <f t="shared" si="0"/>
-        <v>9</v>
+      <c r="O28" s="47" t="s">
+        <v>234</v>
       </c>
       <c r="P28" s="47">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="Q28" s="49">
-        <f t="shared" si="2"/>
+        <f>COUNTIF(E28:H28,"참석")+COUNTIF(J28:O28,"참석")</f>
+        <v>10</v>
+      </c>
+      <c r="Q28" s="47">
+        <f>COUNTIF(E28:H28,"참석")+COUNTIF(E28:H28,"불참")+COUNTIF(J28:O28,"참석")+COUNTIF(J28:O28,"불참")</f>
+        <v>10</v>
+      </c>
+      <c r="R28" s="49">
+        <f>IF(Q28=0,"",P28/Q28)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="16.5">
+    <row r="29" spans="1:19" ht="16.5">
       <c r="A29" s="47">
         <v>28</v>
       </c>
@@ -8137,20 +8421,23 @@
       <c r="N29" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="O29" s="47">
-        <f t="shared" si="0"/>
+      <c r="O29" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="P29" s="47">
+        <f>COUNTIF(E29:H29,"참석")+COUNTIF(J29:O29,"참석")</f>
         <v>3</v>
       </c>
-      <c r="P29" s="47">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="Q29" s="49">
-        <f t="shared" si="2"/>
-        <v>0.33333333333333331</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" ht="16.5">
+      <c r="Q29" s="47">
+        <f>COUNTIF(E29:H29,"참석")+COUNTIF(E29:H29,"불참")+COUNTIF(J29:O29,"참석")+COUNTIF(J29:O29,"불참")</f>
+        <v>10</v>
+      </c>
+      <c r="R29" s="49">
+        <f>IF(Q29=0,"",P29/Q29)</f>
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" ht="16.5">
       <c r="A30" s="47">
         <v>29</v>
       </c>
@@ -8188,20 +8475,23 @@
       <c r="N30" s="47" t="s">
         <v>173</v>
       </c>
-      <c r="O30" s="47">
-        <f t="shared" si="0"/>
+      <c r="O30" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="P30" s="47">
+        <f>COUNTIF(E30:H30,"참석")+COUNTIF(J30:O30,"참석")</f>
         <v>1</v>
       </c>
-      <c r="P30" s="47">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="Q30" s="49">
-        <f t="shared" si="2"/>
-        <v>0.1111111111111111</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" ht="16.5">
+      <c r="Q30" s="47">
+        <f>COUNTIF(E30:H30,"참석")+COUNTIF(E30:H30,"불참")+COUNTIF(J30:O30,"참석")+COUNTIF(J30:O30,"불참")</f>
+        <v>10</v>
+      </c>
+      <c r="R30" s="49">
+        <f>IF(Q30=0,"",P30/Q30)</f>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" ht="16.5">
       <c r="E31" s="46">
         <f>COUNTIF(E2:E29,"참석")</f>
         <v>19</v>
@@ -8214,14 +8504,14 @@
         <f>COUNTIF(G2:G29,"참석")</f>
         <v>19</v>
       </c>
-      <c r="Q31" s="49" t="str">
-        <f t="shared" ref="Q31" si="3">IF(P31=0,"",O31/P31)</f>
+      <c r="R31" s="49" t="str">
+        <f t="shared" ref="R31" si="0">IF(Q31=0,"",P31/Q31)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R31" xr:uid="{C0625D6E-2678-482C-88B1-4B31BC9434B5}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R31">
+  <autoFilter ref="A1:S31" xr:uid="{C0625D6E-2678-482C-88B1-4B31BC9434B5}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S31">
       <sortCondition ref="C1:C31"/>
     </sortState>
   </autoFilter>

--- a/4기차세대경영자과정/차경 4기 정산서.xlsx
+++ b/4기차세대경영자과정/차경 4기 정산서.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Innobiz\Documents\innobiz-nextgen\4기차세대경영자과정\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1C7A3CB-92E9-4014-8AC6-064E766AA87B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50D38FF1-D89E-43C5-A62F-83D08A7FC019}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{404CE508-8F71-4CA4-99F0-0EFB79DB1227}"/>
   </bookViews>
@@ -1517,7 +1517,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="338">
   <si>
     <t>번호</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -2708,6 +2708,12 @@
   </si>
   <si>
     <t>11주(2026-07-16, 수료식)</t>
+  </si>
+  <si>
+    <t>식비(졸업여행 중식)</t>
+  </si>
+  <si>
+    <t>(주)올리에프앤비</t>
   </si>
 </sst>
 </file>
@@ -5202,7 +5208,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{959FEF70-8578-4918-8CDC-E1B4AA8967DB}">
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="7.125" customWidth="1"/>
@@ -6526,6 +6532,29 @@
       </c>
       <c r="G58" s="2" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59">
+        <v>56</v>
+      </c>
+      <c r="B59" s="71">
+        <v>274000</v>
+      </c>
+      <c r="C59" s="35">
+        <v>46213</v>
+      </c>
+      <c r="D59" s="34" t="s">
+        <v>336</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="F59" s="34" t="s">
+        <v>337</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -6853,15 +6882,15 @@
         <v>234</v>
       </c>
       <c r="P2" s="47">
-        <f>COUNTIF(E2:H2,"참석")+COUNTIF(J2:O2,"참석")</f>
+        <f t="shared" ref="P2:P30" si="0">COUNTIF(E2:H2,"참석")+COUNTIF(J2:O2,"참석")</f>
         <v>10</v>
       </c>
       <c r="Q2" s="47">
-        <f>COUNTIF(E2:H2,"참석")+COUNTIF(E2:H2,"불참")+COUNTIF(J2:O2,"참석")+COUNTIF(J2:O2,"불참")</f>
+        <f t="shared" ref="Q2:Q30" si="1">COUNTIF(E2:H2,"참석")+COUNTIF(E2:H2,"불참")+COUNTIF(J2:O2,"참석")+COUNTIF(J2:O2,"불참")</f>
         <v>10</v>
       </c>
       <c r="R2" s="49">
-        <f>IF(Q2=0,"",P2/Q2)</f>
+        <f t="shared" ref="R2:R30" si="2">IF(Q2=0,"",P2/Q2)</f>
         <v>1</v>
       </c>
       <c r="S2" s="48"/>
@@ -6913,15 +6942,15 @@
         <v>234</v>
       </c>
       <c r="P3" s="47">
-        <f>COUNTIF(E3:H3,"참석")+COUNTIF(J3:O3,"참석")</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="Q3" s="47">
-        <f>COUNTIF(E3:H3,"참석")+COUNTIF(E3:H3,"불참")+COUNTIF(J3:O3,"참석")+COUNTIF(J3:O3,"불참")</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="R3" s="49">
-        <f>IF(Q3=0,"",P3/Q3)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="S3" s="48"/>
@@ -6973,15 +7002,15 @@
         <v>234</v>
       </c>
       <c r="P4" s="47">
-        <f>COUNTIF(E4:H4,"참석")+COUNTIF(J4:O4,"참석")</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="Q4" s="47">
-        <f>COUNTIF(E4:H4,"참석")+COUNTIF(E4:H4,"불참")+COUNTIF(J4:O4,"참석")+COUNTIF(J4:O4,"불참")</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="R4" s="49">
-        <f>IF(Q4=0,"",P4/Q4)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="S4" s="48"/>
@@ -7031,15 +7060,15 @@
         <v>234</v>
       </c>
       <c r="P5" s="47">
-        <f>COUNTIF(E5:H5,"참석")+COUNTIF(J5:O5,"참석")</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="Q5" s="47">
-        <f>COUNTIF(E5:H5,"참석")+COUNTIF(E5:H5,"불참")+COUNTIF(J5:O5,"참석")+COUNTIF(J5:O5,"불참")</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="R5" s="49">
-        <f>IF(Q5=0,"",P5/Q5)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="S5" s="48"/>
@@ -7091,15 +7120,15 @@
         <v>234</v>
       </c>
       <c r="P6" s="47">
-        <f>COUNTIF(E6:H6,"참석")+COUNTIF(J6:O6,"참석")</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="Q6" s="47">
-        <f>COUNTIF(E6:H6,"참석")+COUNTIF(E6:H6,"불참")+COUNTIF(J6:O6,"참석")+COUNTIF(J6:O6,"불참")</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="R6" s="49">
-        <f>IF(Q6=0,"",P6/Q6)</f>
+        <f t="shared" si="2"/>
         <v>0.7</v>
       </c>
       <c r="S6" s="48"/>
@@ -7151,15 +7180,15 @@
         <v>234</v>
       </c>
       <c r="P7" s="47">
-        <f>COUNTIF(E7:H7,"참석")+COUNTIF(J7:O7,"참석")</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="Q7" s="47">
-        <f>COUNTIF(E7:H7,"참석")+COUNTIF(E7:H7,"불참")+COUNTIF(J7:O7,"참석")+COUNTIF(J7:O7,"불참")</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="R7" s="49">
-        <f>IF(Q7=0,"",P7/Q7)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="S7" s="48"/>
@@ -7209,15 +7238,15 @@
         <v>173</v>
       </c>
       <c r="P8" s="47">
-        <f>COUNTIF(E8:H8,"참석")+COUNTIF(J8:O8,"참석")</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="Q8" s="47">
-        <f>COUNTIF(E8:H8,"참석")+COUNTIF(E8:H8,"불참")+COUNTIF(J8:O8,"참석")+COUNTIF(J8:O8,"불참")</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="R8" s="49">
-        <f>IF(Q8=0,"",P8/Q8)</f>
+        <f t="shared" si="2"/>
         <v>0.4</v>
       </c>
       <c r="S8" s="48"/>
@@ -7269,15 +7298,15 @@
         <v>234</v>
       </c>
       <c r="P9" s="47">
-        <f>COUNTIF(E9:H9,"참석")+COUNTIF(J9:O9,"참석")</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="Q9" s="47">
-        <f>COUNTIF(E9:H9,"참석")+COUNTIF(E9:H9,"불참")+COUNTIF(J9:O9,"참석")+COUNTIF(J9:O9,"불참")</f>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="R9" s="49">
-        <f>IF(Q9=0,"",P9/Q9)</f>
+        <f t="shared" si="2"/>
         <v>0.75</v>
       </c>
       <c r="S9" s="48" t="s">
@@ -7329,15 +7358,15 @@
         <v>173</v>
       </c>
       <c r="P10" s="47">
-        <f>COUNTIF(E10:H10,"참석")+COUNTIF(J10:O10,"참석")</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="Q10" s="47">
-        <f>COUNTIF(E10:H10,"참석")+COUNTIF(E10:H10,"불참")+COUNTIF(J10:O10,"참석")+COUNTIF(J10:O10,"불참")</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="R10" s="49">
-        <f>IF(Q10=0,"",P10/Q10)</f>
+        <f t="shared" si="2"/>
         <v>0.4</v>
       </c>
       <c r="S10" s="48"/>
@@ -7387,15 +7416,15 @@
         <v>173</v>
       </c>
       <c r="P11" s="47">
-        <f>COUNTIF(E11:H11,"참석")+COUNTIF(J11:O11,"참석")</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="Q11" s="47">
-        <f>COUNTIF(E11:H11,"참석")+COUNTIF(E11:H11,"불참")+COUNTIF(J11:O11,"참석")+COUNTIF(J11:O11,"불참")</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="R11" s="49">
-        <f>IF(Q11=0,"",P11/Q11)</f>
+        <f t="shared" si="2"/>
         <v>0.3</v>
       </c>
       <c r="S11" s="48"/>
@@ -7445,15 +7474,15 @@
         <v>234</v>
       </c>
       <c r="P12" s="47">
-        <f>COUNTIF(E12:H12,"참석")+COUNTIF(J12:O12,"참석")</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="Q12" s="47">
-        <f>COUNTIF(E12:H12,"참석")+COUNTIF(E12:H12,"불참")+COUNTIF(J12:O12,"참석")+COUNTIF(J12:O12,"불참")</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="R12" s="49">
-        <f>IF(Q12=0,"",P12/Q12)</f>
+        <f t="shared" si="2"/>
         <v>0.7</v>
       </c>
       <c r="S12" s="48"/>
@@ -7503,15 +7532,15 @@
         <v>234</v>
       </c>
       <c r="P13" s="47">
-        <f>COUNTIF(E13:H13,"참석")+COUNTIF(J13:O13,"참석")</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="Q13" s="47">
-        <f>COUNTIF(E13:H13,"참석")+COUNTIF(E13:H13,"불참")+COUNTIF(J13:O13,"참석")+COUNTIF(J13:O13,"불참")</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="R13" s="49">
-        <f>IF(Q13=0,"",P13/Q13)</f>
+        <f t="shared" si="2"/>
         <v>0.3</v>
       </c>
       <c r="S13" s="48"/>
@@ -7561,15 +7590,15 @@
         <v>173</v>
       </c>
       <c r="P14" s="47">
-        <f>COUNTIF(E14:H14,"참석")+COUNTIF(J14:O14,"참석")</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="Q14" s="47">
-        <f>COUNTIF(E14:H14,"참석")+COUNTIF(E14:H14,"불참")+COUNTIF(J14:O14,"참석")+COUNTIF(J14:O14,"불참")</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="R14" s="49">
-        <f>IF(Q14=0,"",P14/Q14)</f>
+        <f t="shared" si="2"/>
         <v>0.2</v>
       </c>
       <c r="S14" s="48"/>
@@ -7619,15 +7648,15 @@
         <v>234</v>
       </c>
       <c r="P15" s="47">
-        <f>COUNTIF(E15:H15,"참석")+COUNTIF(J15:O15,"참석")</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="Q15" s="47">
-        <f>COUNTIF(E15:H15,"참석")+COUNTIF(E15:H15,"불참")+COUNTIF(J15:O15,"참석")+COUNTIF(J15:O15,"불참")</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="R15" s="49">
-        <f>IF(Q15=0,"",P15/Q15)</f>
+        <f t="shared" si="2"/>
         <v>0.8</v>
       </c>
       <c r="S15" s="48"/>
@@ -7679,15 +7708,15 @@
         <v>173</v>
       </c>
       <c r="P16" s="47">
-        <f>COUNTIF(E16:H16,"참석")+COUNTIF(J16:O16,"참석")</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="Q16" s="47">
-        <f>COUNTIF(E16:H16,"참석")+COUNTIF(E16:H16,"불참")+COUNTIF(J16:O16,"참석")+COUNTIF(J16:O16,"불참")</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="R16" s="49">
-        <f>IF(Q16=0,"",P16/Q16)</f>
+        <f t="shared" si="2"/>
         <v>0.4</v>
       </c>
     </row>
@@ -7736,15 +7765,15 @@
         <v>234</v>
       </c>
       <c r="P17" s="47">
-        <f>COUNTIF(E17:H17,"참석")+COUNTIF(J17:O17,"참석")</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="Q17" s="47">
-        <f>COUNTIF(E17:H17,"참석")+COUNTIF(E17:H17,"불참")+COUNTIF(J17:O17,"참석")+COUNTIF(J17:O17,"불참")</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="R17" s="49">
-        <f>IF(Q17=0,"",P17/Q17)</f>
+        <f t="shared" si="2"/>
         <v>0.8</v>
       </c>
     </row>
@@ -7793,15 +7822,15 @@
         <v>173</v>
       </c>
       <c r="P18" s="47">
-        <f>COUNTIF(E18:H18,"참석")+COUNTIF(J18:O18,"참석")</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="Q18" s="47">
-        <f>COUNTIF(E18:H18,"참석")+COUNTIF(E18:H18,"불참")+COUNTIF(J18:O18,"참석")+COUNTIF(J18:O18,"불참")</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="R18" s="49">
-        <f>IF(Q18=0,"",P18/Q18)</f>
+        <f t="shared" si="2"/>
         <v>0.4</v>
       </c>
     </row>
@@ -7850,15 +7879,15 @@
         <v>234</v>
       </c>
       <c r="P19" s="47">
-        <f>COUNTIF(E19:H19,"참석")+COUNTIF(J19:O19,"참석")</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="Q19" s="47">
-        <f>COUNTIF(E19:H19,"참석")+COUNTIF(E19:H19,"불참")+COUNTIF(J19:O19,"참석")+COUNTIF(J19:O19,"불참")</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="R19" s="49">
-        <f>IF(Q19=0,"",P19/Q19)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="S19" s="46" t="s">
@@ -7910,15 +7939,15 @@
         <v>173</v>
       </c>
       <c r="P20" s="47">
-        <f>COUNTIF(E20:H20,"참석")+COUNTIF(J20:O20,"참석")</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="Q20" s="47">
-        <f>COUNTIF(E20:H20,"참석")+COUNTIF(E20:H20,"불참")+COUNTIF(J20:O20,"참석")+COUNTIF(J20:O20,"불참")</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="R20" s="49">
-        <f>IF(Q20=0,"",P20/Q20)</f>
+        <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
     </row>
@@ -7967,15 +7996,15 @@
         <v>234</v>
       </c>
       <c r="P21" s="47">
-        <f>COUNTIF(E21:H21,"참석")+COUNTIF(J21:O21,"참석")</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="Q21" s="47">
-        <f>COUNTIF(E21:H21,"참석")+COUNTIF(E21:H21,"불참")+COUNTIF(J21:O21,"참석")+COUNTIF(J21:O21,"불참")</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="R21" s="49">
-        <f>IF(Q21=0,"",P21/Q21)</f>
+        <f t="shared" si="2"/>
         <v>0.9</v>
       </c>
     </row>
@@ -8024,15 +8053,15 @@
         <v>234</v>
       </c>
       <c r="P22" s="47">
-        <f>COUNTIF(E22:H22,"참석")+COUNTIF(J22:O22,"참석")</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="Q22" s="47">
-        <f>COUNTIF(E22:H22,"참석")+COUNTIF(E22:H22,"불참")+COUNTIF(J22:O22,"참석")+COUNTIF(J22:O22,"불참")</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="R22" s="49">
-        <f>IF(Q22=0,"",P22/Q22)</f>
+        <f t="shared" si="2"/>
         <v>0.4</v>
       </c>
     </row>
@@ -8081,15 +8110,15 @@
         <v>234</v>
       </c>
       <c r="P23" s="47">
-        <f>COUNTIF(E23:H23,"참석")+COUNTIF(J23:O23,"참석")</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="Q23" s="47">
-        <f>COUNTIF(E23:H23,"참석")+COUNTIF(E23:H23,"불참")+COUNTIF(J23:O23,"참석")+COUNTIF(J23:O23,"불참")</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="R23" s="49">
-        <f>IF(Q23=0,"",P23/Q23)</f>
+        <f t="shared" si="2"/>
         <v>0.7</v>
       </c>
     </row>
@@ -8140,15 +8169,15 @@
         <v>234</v>
       </c>
       <c r="P24" s="47">
-        <f>COUNTIF(E24:H24,"참석")+COUNTIF(J24:O24,"참석")</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="Q24" s="47">
-        <f>COUNTIF(E24:H24,"참석")+COUNTIF(E24:H24,"불참")+COUNTIF(J24:O24,"참석")+COUNTIF(J24:O24,"불참")</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="R24" s="49">
-        <f>IF(Q24=0,"",P24/Q24)</f>
+        <f t="shared" si="2"/>
         <v>0.4</v>
       </c>
     </row>
@@ -8197,15 +8226,15 @@
         <v>234</v>
       </c>
       <c r="P25" s="47">
-        <f>COUNTIF(E25:H25,"참석")+COUNTIF(J25:O25,"참석")</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="Q25" s="47">
-        <f>COUNTIF(E25:H25,"참석")+COUNTIF(E25:H25,"불참")+COUNTIF(J25:O25,"참석")+COUNTIF(J25:O25,"불참")</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="R25" s="49">
-        <f>IF(Q25=0,"",P25/Q25)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -8254,15 +8283,15 @@
         <v>173</v>
       </c>
       <c r="P26" s="47">
-        <f>COUNTIF(E26:H26,"참석")+COUNTIF(J26:O26,"참석")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="Q26" s="47">
-        <f>COUNTIF(E26:H26,"참석")+COUNTIF(E26:H26,"불참")+COUNTIF(J26:O26,"참석")+COUNTIF(J26:O26,"불참")</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="R26" s="49">
-        <f>IF(Q26=0,"",P26/Q26)</f>
+        <f t="shared" si="2"/>
         <v>0.1</v>
       </c>
     </row>
@@ -8311,15 +8340,15 @@
         <v>234</v>
       </c>
       <c r="P27" s="47">
-        <f>COUNTIF(E27:H27,"참석")+COUNTIF(J27:O27,"참석")</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="Q27" s="47">
-        <f>COUNTIF(E27:H27,"참석")+COUNTIF(E27:H27,"불참")+COUNTIF(J27:O27,"참석")+COUNTIF(J27:O27,"불참")</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="R27" s="49">
-        <f>IF(Q27=0,"",P27/Q27)</f>
+        <f t="shared" si="2"/>
         <v>0.8</v>
       </c>
     </row>
@@ -8368,15 +8397,15 @@
         <v>234</v>
       </c>
       <c r="P28" s="47">
-        <f>COUNTIF(E28:H28,"참석")+COUNTIF(J28:O28,"참석")</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="Q28" s="47">
-        <f>COUNTIF(E28:H28,"참석")+COUNTIF(E28:H28,"불참")+COUNTIF(J28:O28,"참석")+COUNTIF(J28:O28,"불참")</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="R28" s="49">
-        <f>IF(Q28=0,"",P28/Q28)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -8425,15 +8454,15 @@
         <v>173</v>
       </c>
       <c r="P29" s="47">
-        <f>COUNTIF(E29:H29,"참석")+COUNTIF(J29:O29,"참석")</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="Q29" s="47">
-        <f>COUNTIF(E29:H29,"참석")+COUNTIF(E29:H29,"불참")+COUNTIF(J29:O29,"참석")+COUNTIF(J29:O29,"불참")</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="R29" s="49">
-        <f>IF(Q29=0,"",P29/Q29)</f>
+        <f t="shared" si="2"/>
         <v>0.3</v>
       </c>
     </row>
@@ -8479,15 +8508,15 @@
         <v>173</v>
       </c>
       <c r="P30" s="47">
-        <f>COUNTIF(E30:H30,"참석")+COUNTIF(J30:O30,"참석")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="Q30" s="47">
-        <f>COUNTIF(E30:H30,"참석")+COUNTIF(E30:H30,"불참")+COUNTIF(J30:O30,"참석")+COUNTIF(J30:O30,"불참")</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="R30" s="49">
-        <f>IF(Q30=0,"",P30/Q30)</f>
+        <f t="shared" si="2"/>
         <v>0.1</v>
       </c>
     </row>
@@ -8505,7 +8534,7 @@
         <v>19</v>
       </c>
       <c r="R31" s="49" t="str">
-        <f t="shared" ref="R31" si="0">IF(Q31=0,"",P31/Q31)</f>
+        <f t="shared" ref="R31" si="3">IF(Q31=0,"",P31/Q31)</f>
         <v/>
       </c>
     </row>

--- a/4기차세대경영자과정/차경 4기 정산서.xlsx
+++ b/4기차세대경영자과정/차경 4기 정산서.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Innobiz\Documents\innobiz-nextgen\4기차세대경영자과정\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50D38FF1-D89E-43C5-A62F-83D08A7FC019}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02B8E31D-FF2F-4952-9C35-51E591C639DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{404CE508-8F71-4CA4-99F0-0EFB79DB1227}"/>
   </bookViews>
@@ -2619,15 +2619,9 @@
     <t>8주(2026-06-25)</t>
   </si>
   <si>
-    <t>회의실 사용료(07/02, 냉방사용료 포함)</t>
-  </si>
-  <si>
     <t>운영비</t>
   </si>
   <si>
-    <t>이노밸리</t>
-  </si>
-  <si>
     <t>강사비(한웅)</t>
   </si>
   <si>
@@ -2713,7 +2707,16 @@
     <t>식비(졸업여행 중식)</t>
   </si>
   <si>
-    <t>(주)올리에프앤비</t>
+    <t>회의실 임차료(보증금 및 사용료)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>판교이노밸리6블럭관리단</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>해물꾼조태산</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -6240,19 +6243,19 @@
         <v>43</v>
       </c>
       <c r="B46" s="71">
-        <v>550000</v>
+        <v>750000</v>
       </c>
       <c r="C46" s="35">
-        <v>46205</v>
+        <v>46190</v>
       </c>
       <c r="D46" s="34" t="s">
+        <v>335</v>
+      </c>
+      <c r="E46" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="E46" s="2" t="s">
-        <v>307</v>
-      </c>
       <c r="F46" s="34" t="s">
-        <v>308</v>
+        <v>336</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>12</v>
@@ -6269,13 +6272,13 @@
         <v>46205</v>
       </c>
       <c r="D47" s="34" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>293</v>
       </c>
       <c r="F47" s="34" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>12</v>
@@ -6292,13 +6295,13 @@
         <v>46205</v>
       </c>
       <c r="D48" s="34" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>296</v>
       </c>
       <c r="F48" s="34" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>12</v>
@@ -6315,13 +6318,13 @@
         <v>46205</v>
       </c>
       <c r="D49" s="34" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>303</v>
       </c>
       <c r="F49" s="34" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>12</v>
@@ -6338,13 +6341,13 @@
         <v>46205</v>
       </c>
       <c r="D50" s="34" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>300</v>
       </c>
       <c r="F50" s="34" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>12</v>
@@ -6361,13 +6364,13 @@
         <v>46209</v>
       </c>
       <c r="D51" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="F51" s="34" t="s">
         <v>319</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="F51" s="34" t="s">
-        <v>321</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>8</v>
@@ -6384,13 +6387,13 @@
         <v>46219</v>
       </c>
       <c r="D52" s="34" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>293</v>
       </c>
       <c r="F52" s="34" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>14</v>
@@ -6407,13 +6410,13 @@
         <v>46219</v>
       </c>
       <c r="D53" s="34" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>296</v>
       </c>
       <c r="F53" s="34" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>14</v>
@@ -6430,13 +6433,13 @@
         <v>46219</v>
       </c>
       <c r="D54" s="34" t="s">
+        <v>325</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="F54" s="34" t="s">
         <v>327</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="F54" s="34" t="s">
-        <v>329</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>14</v>
@@ -6453,13 +6456,13 @@
         <v>46219</v>
       </c>
       <c r="D55" s="34" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>303</v>
       </c>
       <c r="F55" s="34" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>14</v>
@@ -6476,7 +6479,7 @@
         <v>46223</v>
       </c>
       <c r="D56" s="34" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>24</v>
@@ -6499,13 +6502,13 @@
         <v>46217</v>
       </c>
       <c r="D57" s="34" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>300</v>
       </c>
       <c r="F57" s="34" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>14</v>
@@ -6545,7 +6548,7 @@
         <v>46213</v>
       </c>
       <c r="D59" s="34" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>303</v>
@@ -6814,13 +6817,13 @@
         <v>305</v>
       </c>
       <c r="M1" s="45" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="N1" s="45" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="O1" s="45" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="P1" s="45" t="s">
         <v>156</v>
@@ -7813,7 +7816,7 @@
         <v>234</v>
       </c>
       <c r="M18" s="47" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="N18" s="47" t="s">
         <v>173</v>

--- a/4기차세대경영자과정/차경 4기 정산서.xlsx
+++ b/4기차세대경영자과정/차경 4기 정산서.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Innobiz\Documents\innobiz-nextgen\4기차세대경영자과정\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02B8E31D-FF2F-4952-9C35-51E591C639DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3692BC73-51E1-447A-8C82-3E4E4D7C7886}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{404CE508-8F71-4CA4-99F0-0EFB79DB1227}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{404CE508-8F71-4CA4-99F0-0EFB79DB1227}"/>
   </bookViews>
   <sheets>
     <sheet name="항목별(피벗)" sheetId="9" r:id="rId1"/>
@@ -1517,7 +1517,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="342">
   <si>
     <t>번호</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -2716,6 +2716,20 @@
   </si>
   <si>
     <t>해물꾼조태산</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>대관료</t>
+  </si>
+  <si>
+    <t>이노비즈협회</t>
+  </si>
+  <si>
+    <t>대관료(지하1층 대회의실, 5시간)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>대관료(7층 공용회의실, 9시간)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -5211,7 +5225,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{959FEF70-8578-4918-8CDC-E1B4AA8967DB}">
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="7.125" customWidth="1"/>
@@ -6558,6 +6572,167 @@
       </c>
       <c r="G59" s="2" t="s">
         <v>13</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60">
+        <v>57</v>
+      </c>
+      <c r="B60" s="71">
+        <v>200000</v>
+      </c>
+      <c r="C60" s="35">
+        <v>46149</v>
+      </c>
+      <c r="D60" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="F60" s="34" t="s">
+        <v>339</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61">
+        <v>58</v>
+      </c>
+      <c r="B61" s="71">
+        <v>90000</v>
+      </c>
+      <c r="C61" s="35">
+        <v>46156</v>
+      </c>
+      <c r="D61" s="34" t="s">
+        <v>341</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="F61" s="34" t="s">
+        <v>339</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62">
+        <v>59</v>
+      </c>
+      <c r="B62" s="71">
+        <v>90000</v>
+      </c>
+      <c r="C62" s="35">
+        <v>46163</v>
+      </c>
+      <c r="D62" s="34" t="s">
+        <v>341</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="F62" s="34" t="s">
+        <v>339</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63">
+        <v>60</v>
+      </c>
+      <c r="B63" s="71">
+        <v>90000</v>
+      </c>
+      <c r="C63" s="35">
+        <v>46170</v>
+      </c>
+      <c r="D63" s="34" t="s">
+        <v>341</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="F63" s="34" t="s">
+        <v>339</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64">
+        <v>61</v>
+      </c>
+      <c r="B64" s="71">
+        <v>90000</v>
+      </c>
+      <c r="C64" s="35">
+        <v>46184</v>
+      </c>
+      <c r="D64" s="34" t="s">
+        <v>341</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="F64" s="34" t="s">
+        <v>339</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="A65">
+        <v>62</v>
+      </c>
+      <c r="B65" s="71">
+        <v>90000</v>
+      </c>
+      <c r="C65" s="35">
+        <v>46191</v>
+      </c>
+      <c r="D65" s="34" t="s">
+        <v>341</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="F65" s="34" t="s">
+        <v>339</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
+      <c r="A66">
+        <v>63</v>
+      </c>
+      <c r="B66" s="71">
+        <v>200000</v>
+      </c>
+      <c r="C66" s="35">
+        <v>46219</v>
+      </c>
+      <c r="D66" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="F66" s="34" t="s">
+        <v>339</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/4기차세대경영자과정/차경 4기 정산서.xlsx
+++ b/4기차세대경영자과정/차경 4기 정산서.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Innobiz\Documents\innobiz-nextgen\4기차세대경영자과정\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3692BC73-51E1-447A-8C82-3E4E4D7C7886}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F7892E5-2F79-4DD5-B0F7-239EF1DD53F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{404CE508-8F71-4CA4-99F0-0EFB79DB1227}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{404CE508-8F71-4CA4-99F0-0EFB79DB1227}"/>
   </bookViews>
   <sheets>
     <sheet name="항목별(피벗)" sheetId="9" r:id="rId1"/>
@@ -1517,7 +1517,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="344">
   <si>
     <t>번호</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -2731,6 +2731,12 @@
   <si>
     <t>대관료(7층 공용회의실, 9시간)</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>주차비(관리비 정산)</t>
+  </si>
+  <si>
+    <t>판교이노밸리6블럭관리단</t>
   </si>
 </sst>
 </file>
@@ -5225,7 +5231,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{959FEF70-8578-4918-8CDC-E1B4AA8967DB}">
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:G75"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="7.125" customWidth="1"/>
@@ -6732,6 +6738,213 @@
         <v>339</v>
       </c>
       <c r="G66" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
+      <c r="A67">
+        <v>64</v>
+      </c>
+      <c r="B67" s="71">
+        <v>333000</v>
+      </c>
+      <c r="C67" s="35">
+        <v>46149</v>
+      </c>
+      <c r="D67" s="34" t="s">
+        <v>342</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F67" s="34" t="s">
+        <v>343</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
+      <c r="A68">
+        <v>65</v>
+      </c>
+      <c r="B68" s="71">
+        <v>280000</v>
+      </c>
+      <c r="C68" s="35">
+        <v>46156</v>
+      </c>
+      <c r="D68" s="34" t="s">
+        <v>342</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F68" s="34" t="s">
+        <v>343</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
+      <c r="A69">
+        <v>66</v>
+      </c>
+      <c r="B69" s="71">
+        <v>96500</v>
+      </c>
+      <c r="C69" s="35">
+        <v>46163</v>
+      </c>
+      <c r="D69" s="34" t="s">
+        <v>342</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F69" s="34" t="s">
+        <v>343</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7">
+      <c r="A70">
+        <v>67</v>
+      </c>
+      <c r="B70" s="71">
+        <v>145500</v>
+      </c>
+      <c r="C70" s="35">
+        <v>46170</v>
+      </c>
+      <c r="D70" s="34" t="s">
+        <v>342</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F70" s="34" t="s">
+        <v>343</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7">
+      <c r="A71">
+        <v>68</v>
+      </c>
+      <c r="B71" s="71">
+        <v>132000</v>
+      </c>
+      <c r="C71" s="35">
+        <v>46184</v>
+      </c>
+      <c r="D71" s="34" t="s">
+        <v>342</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F71" s="34" t="s">
+        <v>343</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
+      <c r="A72">
+        <v>69</v>
+      </c>
+      <c r="B72" s="71">
+        <v>78000</v>
+      </c>
+      <c r="C72" s="35">
+        <v>46191</v>
+      </c>
+      <c r="D72" s="34" t="s">
+        <v>342</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F72" s="34" t="s">
+        <v>343</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
+      <c r="A73">
+        <v>70</v>
+      </c>
+      <c r="B73" s="71">
+        <v>55500</v>
+      </c>
+      <c r="C73" s="35">
+        <v>46198</v>
+      </c>
+      <c r="D73" s="34" t="s">
+        <v>342</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F73" s="34" t="s">
+        <v>343</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7">
+      <c r="A74">
+        <v>71</v>
+      </c>
+      <c r="B74" s="71">
+        <v>66000</v>
+      </c>
+      <c r="C74" s="35">
+        <v>46205</v>
+      </c>
+      <c r="D74" s="34" t="s">
+        <v>342</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F74" s="34" t="s">
+        <v>343</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7">
+      <c r="A75">
+        <v>72</v>
+      </c>
+      <c r="B75" s="71">
+        <v>380000</v>
+      </c>
+      <c r="C75" s="35">
+        <v>46219</v>
+      </c>
+      <c r="D75" s="34" t="s">
+        <v>342</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F75" s="34" t="s">
+        <v>343</v>
+      </c>
+      <c r="G75" s="2" t="s">
         <v>14</v>
       </c>
     </row>

--- a/4기차세대경영자과정/차경 4기 정산서.xlsx
+++ b/4기차세대경영자과정/차경 4기 정산서.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Innobiz\Documents\innobiz-nextgen\4기차세대경영자과정\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F7892E5-2F79-4DD5-B0F7-239EF1DD53F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00169B03-190F-4E94-A723-A42375AD6B34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{404CE508-8F71-4CA4-99F0-0EFB79DB1227}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{404CE508-8F71-4CA4-99F0-0EFB79DB1227}"/>
   </bookViews>
   <sheets>
     <sheet name="항목별(피벗)" sheetId="9" r:id="rId1"/>
@@ -1517,7 +1517,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="904" uniqueCount="347">
   <si>
     <t>번호</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -2737,6 +2737,15 @@
   </si>
   <si>
     <t>판교이노밸리6블럭관리단</t>
+  </si>
+  <si>
+    <t>원우회 홈페이지 웹호스팅비(1년, 2026-08-07~2027-08-06)</t>
+  </si>
+  <si>
+    <t>사이트관리비</t>
+  </si>
+  <si>
+    <t>(주)슈빅</t>
   </si>
 </sst>
 </file>
@@ -5231,7 +5240,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{959FEF70-8578-4918-8CDC-E1B4AA8967DB}">
-  <dimension ref="A1:G75"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="7.125" customWidth="1"/>
@@ -6945,6 +6954,29 @@
         <v>343</v>
       </c>
       <c r="G75" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7">
+      <c r="A76">
+        <v>73</v>
+      </c>
+      <c r="B76" s="71">
+        <v>132000</v>
+      </c>
+      <c r="C76" s="35">
+        <v>46240</v>
+      </c>
+      <c r="D76" s="34" t="s">
+        <v>344</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="F76" s="34" t="s">
+        <v>346</v>
+      </c>
+      <c r="G76" s="2" t="s">
         <v>14</v>
       </c>
     </row>

--- a/4기차세대경영자과정/차경 4기 정산서.xlsx
+++ b/4기차세대경영자과정/차경 4기 정산서.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Innobiz\Documents\innobiz-nextgen\4기차세대경영자과정\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00169B03-190F-4E94-A723-A42375AD6B34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9285691-3816-4A3F-B46E-36B4AFDF3231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{404CE508-8F71-4CA4-99F0-0EFB79DB1227}"/>
   </bookViews>
@@ -2739,13 +2739,14 @@
     <t>판교이노밸리6블럭관리단</t>
   </si>
   <si>
-    <t>원우회 홈페이지 웹호스팅비(1년, 2026-08-07~2027-08-06)</t>
-  </si>
-  <si>
     <t>사이트관리비</t>
   </si>
   <si>
     <t>(주)슈빅</t>
+  </si>
+  <si>
+    <t>이노비즈 차경 원우회 온라인 수첩 사이트 유지비(웹호스팅 1년)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -6968,13 +6969,13 @@
         <v>46240</v>
       </c>
       <c r="D76" s="34" t="s">
+        <v>346</v>
+      </c>
+      <c r="E76" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="E76" s="2" t="s">
+      <c r="F76" s="34" t="s">
         <v>345</v>
-      </c>
-      <c r="F76" s="34" t="s">
-        <v>346</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>14</v>

--- a/4기차세대경영자과정/차경 4기 정산서.xlsx
+++ b/4기차세대경영자과정/차경 4기 정산서.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Innobiz\Documents\innobiz-nextgen\4기차세대경영자과정\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9285691-3816-4A3F-B46E-36B4AFDF3231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A149AA81-3A6A-4C05-A1DF-AC4B603BE38B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{404CE508-8F71-4CA4-99F0-0EFB79DB1227}"/>
   </bookViews>
@@ -2739,13 +2739,14 @@
     <t>판교이노밸리6블럭관리단</t>
   </si>
   <si>
-    <t>사이트관리비</t>
-  </si>
-  <si>
     <t>(주)슈빅</t>
   </si>
   <si>
     <t>이노비즈 차경 원우회 온라인 수첩 사이트 유지비(웹호스팅 1년)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>운영비</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -6969,13 +6970,13 @@
         <v>46240</v>
       </c>
       <c r="D76" s="34" t="s">
+        <v>345</v>
+      </c>
+      <c r="E76" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="E76" s="2" t="s">
+      <c r="F76" s="34" t="s">
         <v>344</v>
-      </c>
-      <c r="F76" s="34" t="s">
-        <v>345</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>14</v>

--- a/4기차세대경영자과정/차경 4기 정산서.xlsx
+++ b/4기차세대경영자과정/차경 4기 정산서.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Innobiz\Documents\innobiz-nextgen\4기차세대경영자과정\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A149AA81-3A6A-4C05-A1DF-AC4B603BE38B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2BD87A5-1825-443E-BD84-47EE692605B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{404CE508-8F71-4CA4-99F0-0EFB79DB1227}"/>
+    <workbookView xWindow="30495" yWindow="915" windowWidth="25500" windowHeight="14565" activeTab="3" xr2:uid="{404CE508-8F71-4CA4-99F0-0EFB79DB1227}"/>
   </bookViews>
   <sheets>
     <sheet name="항목별(피벗)" sheetId="9" r:id="rId1"/>
@@ -2729,10 +2729,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>대관료(7층 공용회의실, 9시간)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>주차비(관리비 정산)</t>
   </si>
   <si>
@@ -2747,6 +2743,10 @@
   </si>
   <si>
     <t>운영비</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>대관료(7층 공용회의실, 5시간 13:00~18:00)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -6619,13 +6619,13 @@
         <v>58</v>
       </c>
       <c r="B61" s="71">
-        <v>90000</v>
+        <v>50000</v>
       </c>
       <c r="C61" s="35">
         <v>46156</v>
       </c>
       <c r="D61" s="34" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>338</v>
@@ -6642,13 +6642,13 @@
         <v>59</v>
       </c>
       <c r="B62" s="71">
-        <v>90000</v>
+        <v>50000</v>
       </c>
       <c r="C62" s="35">
         <v>46163</v>
       </c>
       <c r="D62" s="34" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>338</v>
@@ -6665,13 +6665,13 @@
         <v>60</v>
       </c>
       <c r="B63" s="71">
-        <v>90000</v>
+        <v>50000</v>
       </c>
       <c r="C63" s="35">
         <v>46170</v>
       </c>
       <c r="D63" s="34" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>338</v>
@@ -6688,13 +6688,13 @@
         <v>61</v>
       </c>
       <c r="B64" s="71">
-        <v>90000</v>
+        <v>50000</v>
       </c>
       <c r="C64" s="35">
         <v>46184</v>
       </c>
       <c r="D64" s="34" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>338</v>
@@ -6711,13 +6711,13 @@
         <v>62</v>
       </c>
       <c r="B65" s="71">
-        <v>90000</v>
+        <v>50000</v>
       </c>
       <c r="C65" s="35">
         <v>46191</v>
       </c>
       <c r="D65" s="34" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>338</v>
@@ -6763,13 +6763,13 @@
         <v>46149</v>
       </c>
       <c r="D67" s="34" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>27</v>
       </c>
       <c r="F67" s="34" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>29</v>
@@ -6786,13 +6786,13 @@
         <v>46156</v>
       </c>
       <c r="D68" s="34" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>27</v>
       </c>
       <c r="F68" s="34" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>6</v>
@@ -6809,13 +6809,13 @@
         <v>46163</v>
       </c>
       <c r="D69" s="34" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>27</v>
       </c>
       <c r="F69" s="34" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>4</v>
@@ -6832,13 +6832,13 @@
         <v>46170</v>
       </c>
       <c r="D70" s="34" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>27</v>
       </c>
       <c r="F70" s="34" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>7</v>
@@ -6855,13 +6855,13 @@
         <v>46184</v>
       </c>
       <c r="D71" s="34" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>27</v>
       </c>
       <c r="F71" s="34" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>9</v>
@@ -6878,13 +6878,13 @@
         <v>46191</v>
       </c>
       <c r="D72" s="34" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>27</v>
       </c>
       <c r="F72" s="34" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>10</v>
@@ -6901,13 +6901,13 @@
         <v>46198</v>
       </c>
       <c r="D73" s="34" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>27</v>
       </c>
       <c r="F73" s="34" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>11</v>
@@ -6924,13 +6924,13 @@
         <v>46205</v>
       </c>
       <c r="D74" s="34" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>27</v>
       </c>
       <c r="F74" s="34" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>12</v>
@@ -6947,13 +6947,13 @@
         <v>46219</v>
       </c>
       <c r="D75" s="34" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>27</v>
       </c>
       <c r="F75" s="34" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>14</v>
@@ -6970,13 +6970,13 @@
         <v>46240</v>
       </c>
       <c r="D76" s="34" t="s">
+        <v>344</v>
+      </c>
+      <c r="E76" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="E76" s="2" t="s">
-        <v>346</v>
-      </c>
       <c r="F76" s="34" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>14</v>

--- a/4기차세대경영자과정/차경 4기 정산서.xlsx
+++ b/4기차세대경영자과정/차경 4기 정산서.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Innobiz\Documents\innobiz-nextgen\4기차세대경영자과정\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2BD87A5-1825-443E-BD84-47EE692605B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCAC09FA-7009-4AD7-9A6F-C951DECE2431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30495" yWindow="915" windowWidth="25500" windowHeight="14565" activeTab="3" xr2:uid="{404CE508-8F71-4CA4-99F0-0EFB79DB1227}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{404CE508-8F71-4CA4-99F0-0EFB79DB1227}"/>
   </bookViews>
   <sheets>
     <sheet name="항목별(피벗)" sheetId="9" r:id="rId1"/>
@@ -2707,10 +2707,6 @@
     <t>식비(졸업여행 중식)</t>
   </si>
   <si>
-    <t>회의실 임차료(보증금 및 사용료)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>판교이노밸리6블럭관리단</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2747,6 +2743,10 @@
   </si>
   <si>
     <t>대관료(7층 공용회의실, 5시간 13:00~18:00)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>회의실 임차료(사용료, 냉방료 포함- 보증금 20만원 별도)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -6274,19 +6274,19 @@
         <v>43</v>
       </c>
       <c r="B46" s="71">
-        <v>750000</v>
+        <v>550000</v>
       </c>
       <c r="C46" s="35">
         <v>46190</v>
       </c>
       <c r="D46" s="34" t="s">
-        <v>335</v>
+        <v>346</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>306</v>
       </c>
       <c r="F46" s="34" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>12</v>
@@ -6585,7 +6585,7 @@
         <v>303</v>
       </c>
       <c r="F59" s="34" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>13</v>
@@ -6602,13 +6602,13 @@
         <v>46149</v>
       </c>
       <c r="D60" s="34" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E60" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="F60" s="34" t="s">
         <v>338</v>
-      </c>
-      <c r="F60" s="34" t="s">
-        <v>339</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>29</v>
@@ -6625,13 +6625,13 @@
         <v>46156</v>
       </c>
       <c r="D61" s="34" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E61" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="F61" s="34" t="s">
         <v>338</v>
-      </c>
-      <c r="F61" s="34" t="s">
-        <v>339</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>6</v>
@@ -6648,13 +6648,13 @@
         <v>46163</v>
       </c>
       <c r="D62" s="34" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E62" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="F62" s="34" t="s">
         <v>338</v>
-      </c>
-      <c r="F62" s="34" t="s">
-        <v>339</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>4</v>
@@ -6671,13 +6671,13 @@
         <v>46170</v>
       </c>
       <c r="D63" s="34" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E63" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="F63" s="34" t="s">
         <v>338</v>
-      </c>
-      <c r="F63" s="34" t="s">
-        <v>339</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>7</v>
@@ -6694,13 +6694,13 @@
         <v>46184</v>
       </c>
       <c r="D64" s="34" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E64" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="F64" s="34" t="s">
         <v>338</v>
-      </c>
-      <c r="F64" s="34" t="s">
-        <v>339</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>9</v>
@@ -6717,13 +6717,13 @@
         <v>46191</v>
       </c>
       <c r="D65" s="34" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E65" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="F65" s="34" t="s">
         <v>338</v>
-      </c>
-      <c r="F65" s="34" t="s">
-        <v>339</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>10</v>
@@ -6740,13 +6740,13 @@
         <v>46219</v>
       </c>
       <c r="D66" s="34" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E66" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="F66" s="34" t="s">
         <v>338</v>
-      </c>
-      <c r="F66" s="34" t="s">
-        <v>339</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>14</v>
@@ -6763,13 +6763,13 @@
         <v>46149</v>
       </c>
       <c r="D67" s="34" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>27</v>
       </c>
       <c r="F67" s="34" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>29</v>
@@ -6786,13 +6786,13 @@
         <v>46156</v>
       </c>
       <c r="D68" s="34" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>27</v>
       </c>
       <c r="F68" s="34" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>6</v>
@@ -6809,13 +6809,13 @@
         <v>46163</v>
       </c>
       <c r="D69" s="34" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>27</v>
       </c>
       <c r="F69" s="34" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>4</v>
@@ -6832,13 +6832,13 @@
         <v>46170</v>
       </c>
       <c r="D70" s="34" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>27</v>
       </c>
       <c r="F70" s="34" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>7</v>
@@ -6855,13 +6855,13 @@
         <v>46184</v>
       </c>
       <c r="D71" s="34" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>27</v>
       </c>
       <c r="F71" s="34" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>9</v>
@@ -6878,13 +6878,13 @@
         <v>46191</v>
       </c>
       <c r="D72" s="34" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>27</v>
       </c>
       <c r="F72" s="34" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>10</v>
@@ -6901,13 +6901,13 @@
         <v>46198</v>
       </c>
       <c r="D73" s="34" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>27</v>
       </c>
       <c r="F73" s="34" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>11</v>
@@ -6924,13 +6924,13 @@
         <v>46205</v>
       </c>
       <c r="D74" s="34" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>27</v>
       </c>
       <c r="F74" s="34" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>12</v>
@@ -6947,13 +6947,13 @@
         <v>46219</v>
       </c>
       <c r="D75" s="34" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>27</v>
       </c>
       <c r="F75" s="34" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>14</v>
@@ -6970,13 +6970,13 @@
         <v>46240</v>
       </c>
       <c r="D76" s="34" t="s">
+        <v>343</v>
+      </c>
+      <c r="E76" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="E76" s="2" t="s">
-        <v>345</v>
-      </c>
       <c r="F76" s="34" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>14</v>
